--- a/EpiRank_改_Germany/ERA_result_reverse_seqday_d_0.95_loops_310.xlsx
+++ b/EpiRank_改_Germany/ERA_result_reverse_seqday_d_0.95_loops_310.xlsx
@@ -859,10 +859,10 @@
         <v>0.019464</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" s="3" t="n">
         <v>34035</v>
@@ -1858,7 +1858,7 @@
         <v>0.007346</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>-0</v>
@@ -2668,10 +2668,10 @@
         <v>0.004953</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" s="3" t="n">
         <v>4207</v>
@@ -2788,7 +2788,7 @@
         <v>0.004867</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>0</v>
@@ -3148,10 +3148,10 @@
         <v>0.004368</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA20" s="3" t="n">
         <v>4952</v>
@@ -3388,10 +3388,10 @@
         <v>0.004167</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA22" s="3" t="n">
         <v>3606</v>
@@ -3508,10 +3508,10 @@
         <v>0.004559</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA23" s="3" t="n">
         <v>4123</v>
@@ -3748,10 +3748,10 @@
         <v>0.004805</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA25" s="3" t="n">
         <v>1432</v>
@@ -3868,10 +3868,10 @@
         <v>0.003699</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA26" s="3" t="n">
         <v>2262</v>
@@ -4708,10 +4708,10 @@
         <v>0.003865</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA33" s="3" t="n">
         <v>11679</v>
@@ -5428,10 +5428,10 @@
         <v>0.003686</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA39" s="3" t="n">
         <v>3059</v>
@@ -5551,7 +5551,7 @@
         <v>0</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA40" s="3" t="n">
         <v>2060</v>
@@ -5671,7 +5671,7 @@
         <v>0</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA41" s="3" t="n">
         <v>1989</v>
@@ -6388,7 +6388,7 @@
         <v>0.003516</v>
       </c>
       <c r="Y47" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z47" s="3" t="n">
         <v>0</v>
@@ -6748,10 +6748,10 @@
         <v>0.00308</v>
       </c>
       <c r="Y50" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z50" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA50" s="3" t="n">
         <v>1472</v>
@@ -7348,7 +7348,7 @@
         <v>0.003258</v>
       </c>
       <c r="Y55" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z55" s="3" t="n">
         <v>-0</v>
@@ -8191,7 +8191,7 @@
         <v>0</v>
       </c>
       <c r="Z62" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA62" s="3" t="n">
         <v>2142</v>
@@ -8308,7 +8308,7 @@
         <v>0.003147</v>
       </c>
       <c r="Y63" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z63" s="3" t="n">
         <v>0</v>
@@ -8908,10 +8908,10 @@
         <v>0.00306</v>
       </c>
       <c r="Y68" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z68" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA68" s="3" t="n">
         <v>1130</v>
@@ -9508,7 +9508,7 @@
         <v>0.003381</v>
       </c>
       <c r="Y73" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z73" s="3" t="n">
         <v>-0</v>
@@ -10951,7 +10951,7 @@
         <v>0</v>
       </c>
       <c r="Z85" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA85" s="3" t="n">
         <v>765</v>
@@ -12028,7 +12028,7 @@
         <v>0.003001</v>
       </c>
       <c r="Y94" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z94" s="3" t="n">
         <v>-0</v>
@@ -12268,10 +12268,10 @@
         <v>0.002802</v>
       </c>
       <c r="Y96" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z96" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA96" s="3" t="n">
         <v>2203</v>
@@ -12508,7 +12508,7 @@
         <v>0.002646</v>
       </c>
       <c r="Y98" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z98" s="3" t="n">
         <v>-0</v>
@@ -14308,10 +14308,10 @@
         <v>0.002608</v>
       </c>
       <c r="Y113" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z113" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA113" s="3" t="n">
         <v>3508</v>
@@ -14418,7 +14418,7 @@
         <v>0.002503</v>
       </c>
       <c r="Y114" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z114" s="3" t="n">
         <v>0</v>
@@ -14531,7 +14531,7 @@
         <v>0</v>
       </c>
       <c r="Z115" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA115" s="3" t="n">
         <v>2287</v>
@@ -14638,10 +14638,10 @@
         <v>0.002434</v>
       </c>
       <c r="Y116" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z116" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA116" s="3" t="n">
         <v>1796</v>
@@ -14858,10 +14858,10 @@
         <v>0.002517</v>
       </c>
       <c r="Y118" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z118" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA118" s="3" t="n">
         <v>4137</v>
@@ -17058,10 +17058,10 @@
         <v>0.002271</v>
       </c>
       <c r="Y138" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z138" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA138" s="3" t="n">
         <v>5041</v>
@@ -17171,7 +17171,7 @@
         <v>0</v>
       </c>
       <c r="Z139" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA139" s="3" t="n">
         <v>1737</v>
@@ -17391,7 +17391,7 @@
         <v>0</v>
       </c>
       <c r="Z141" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA141" s="3" t="n">
         <v>3546</v>
@@ -17501,7 +17501,7 @@
         <v>0</v>
       </c>
       <c r="Z142" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA142" s="3" t="n">
         <v>828</v>
@@ -18268,7 +18268,7 @@
         <v>0.002226</v>
       </c>
       <c r="Y149" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z149" s="3" t="n">
         <v>0</v>
@@ -18488,10 +18488,10 @@
         <v>0.002324</v>
       </c>
       <c r="Y151" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z151" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA151" s="3" t="n">
         <v>1662</v>
@@ -19038,10 +19038,10 @@
         <v>0.002351</v>
       </c>
       <c r="Y156" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z156" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA156" s="3" t="n">
         <v>1967</v>
@@ -19698,10 +19698,10 @@
         <v>0.002359</v>
       </c>
       <c r="Y162" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z162" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA162" s="3" t="n">
         <v>1949</v>
@@ -20031,7 +20031,7 @@
         <v>0</v>
       </c>
       <c r="Z165" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA165" s="3" t="n">
         <v>1727</v>
@@ -20578,10 +20578,10 @@
         <v>0.002054</v>
       </c>
       <c r="Y170" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z170" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA170" s="3" t="n">
         <v>1712</v>
@@ -20798,10 +20798,10 @@
         <v>0.002328</v>
       </c>
       <c r="Y172" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z172" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA172" s="3" t="n">
         <v>1267</v>
@@ -20911,7 +20911,7 @@
         <v>0</v>
       </c>
       <c r="Z173" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA173" s="3" t="n">
         <v>1316</v>
@@ -21128,10 +21128,10 @@
         <v>0.002174</v>
       </c>
       <c r="Y175" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z175" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA175" s="3" t="n">
         <v>1957</v>
@@ -21348,10 +21348,10 @@
         <v>0.002421</v>
       </c>
       <c r="Y177" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z177" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA177" s="3" t="n">
         <v>857</v>
@@ -21458,10 +21458,10 @@
         <v>0.00214</v>
       </c>
       <c r="Y178" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z178" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA178" s="3" t="n">
         <v>1559</v>
@@ -21898,10 +21898,10 @@
         <v>0.002184</v>
       </c>
       <c r="Y182" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z182" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA182" s="3" t="n">
         <v>1727</v>
@@ -22008,10 +22008,10 @@
         <v>0.002155</v>
       </c>
       <c r="Y183" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z183" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA183" s="3" t="n">
         <v>1407</v>
@@ -22228,10 +22228,10 @@
         <v>0.001842</v>
       </c>
       <c r="Y185" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z185" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA185" s="3" t="n">
         <v>1124</v>
@@ -23111,7 +23111,7 @@
         <v>0</v>
       </c>
       <c r="Z193" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA193" s="3" t="n">
         <v>1460</v>
@@ -24538,7 +24538,7 @@
         <v>0.002033</v>
       </c>
       <c r="Y206" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z206" s="3" t="n">
         <v>-0</v>
@@ -25088,7 +25088,7 @@
         <v>0.002032</v>
       </c>
       <c r="Y211" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z211" s="3" t="n">
         <v>0</v>
@@ -25198,10 +25198,10 @@
         <v>0.001965</v>
       </c>
       <c r="Y212" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z212" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA212" s="3" t="n">
         <v>3507</v>
@@ -25861,7 +25861,7 @@
         <v>0</v>
       </c>
       <c r="Z218" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA218" s="3" t="n">
         <v>1537</v>
@@ -26408,10 +26408,10 @@
         <v>0.001956</v>
       </c>
       <c r="Y223" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z223" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA223" s="3" t="n">
         <v>2206</v>
@@ -27728,7 +27728,7 @@
         <v>0.001785</v>
       </c>
       <c r="Y235" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z235" s="3" t="n">
         <v>0</v>
@@ -28278,10 +28278,10 @@
         <v>0.00183</v>
       </c>
       <c r="Y240" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z240" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA240" s="3" t="n">
         <v>1611</v>
@@ -28498,7 +28498,7 @@
         <v>0.001919</v>
       </c>
       <c r="Y242" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z242" s="3" t="n">
         <v>-0</v>
@@ -28938,10 +28938,10 @@
         <v>0.001896</v>
       </c>
       <c r="Y246" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z246" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA246" s="3" t="n">
         <v>941</v>
@@ -29268,10 +29268,10 @@
         <v>0.001815</v>
       </c>
       <c r="Y249" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z249" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA249" s="3" t="n">
         <v>1523</v>
@@ -29488,7 +29488,7 @@
         <v>0.001928</v>
       </c>
       <c r="Y251" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z251" s="3" t="n">
         <v>-0</v>
@@ -29598,7 +29598,7 @@
         <v>0.001608</v>
       </c>
       <c r="Y252" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z252" s="3" t="n">
         <v>0</v>
@@ -29818,10 +29818,10 @@
         <v>0.001683</v>
       </c>
       <c r="Y254" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z254" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA254" s="3" t="n">
         <v>3118</v>
@@ -29928,10 +29928,10 @@
         <v>0.001666</v>
       </c>
       <c r="Y255" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z255" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA255" s="3" t="n">
         <v>2005</v>
@@ -30038,10 +30038,10 @@
         <v>0.00163</v>
       </c>
       <c r="Y256" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z256" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA256" s="3" t="n">
         <v>2337</v>
@@ -30258,7 +30258,7 @@
         <v>0.00168</v>
       </c>
       <c r="Y258" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z258" s="3" t="n">
         <v>-0</v>
@@ -30808,10 +30808,10 @@
         <v>0.001707</v>
       </c>
       <c r="Y263" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z263" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA263" s="3" t="n">
         <v>745</v>
@@ -31028,10 +31028,10 @@
         <v>0.001646</v>
       </c>
       <c r="Y265" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z265" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA265" s="3" t="n">
         <v>3450</v>
@@ -31558,7 +31558,7 @@
         <v>0.001717</v>
       </c>
       <c r="Y270" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z270" s="3" t="n">
         <v>-0</v>
@@ -32361,7 +32361,7 @@
         <v>0</v>
       </c>
       <c r="Z278" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA278" s="3" t="n">
         <v>1102</v>
@@ -33158,10 +33158,10 @@
         <v>0.001623</v>
       </c>
       <c r="Y286" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z286" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA286" s="3" t="n">
         <v>841</v>
@@ -34158,7 +34158,7 @@
         <v>0.001619</v>
       </c>
       <c r="Y296" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z296" s="3" t="n">
         <v>-0</v>
@@ -34361,7 +34361,7 @@
         <v>0</v>
       </c>
       <c r="Z298" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA298" s="3" t="n">
         <v>627</v>
@@ -34658,10 +34658,10 @@
         <v>0.001586</v>
       </c>
       <c r="Y301" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z301" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA301" s="3" t="n">
         <v>1482</v>
@@ -34861,7 +34861,7 @@
         <v>0</v>
       </c>
       <c r="Z303" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA303" s="3" t="n">
         <v>1844</v>
@@ -35658,10 +35658,10 @@
         <v>0.001535</v>
       </c>
       <c r="Y311" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z311" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA311" s="3" t="n">
         <v>2054</v>
@@ -36158,7 +36158,7 @@
         <v>0.00142</v>
       </c>
       <c r="Y316" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z316" s="3" t="n">
         <v>0</v>
@@ -36261,7 +36261,7 @@
         <v>0</v>
       </c>
       <c r="Z317" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA317" s="3" t="n">
         <v>1125</v>
@@ -36358,10 +36358,10 @@
         <v>0.001396</v>
       </c>
       <c r="Y318" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z318" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA318" s="3" t="n">
         <v>1150</v>
@@ -36758,10 +36758,10 @@
         <v>0.001423</v>
       </c>
       <c r="Y322" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z322" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA322" s="3" t="n">
         <v>481</v>
@@ -37358,10 +37358,10 @@
         <v>0.001552</v>
       </c>
       <c r="Y328" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z328" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA328" s="3" t="n">
         <v>2839</v>
@@ -37458,10 +37458,10 @@
         <v>0.001464</v>
       </c>
       <c r="Y329" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z329" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA329" s="3" t="n">
         <v>1348</v>
@@ -38361,7 +38361,7 @@
         <v>0</v>
       </c>
       <c r="Z338" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA338" s="3" t="n">
         <v>556</v>
@@ -38458,10 +38458,10 @@
         <v>0.00144</v>
       </c>
       <c r="Y339" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z339" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA339" s="3" t="n">
         <v>622</v>
@@ -39261,7 +39261,7 @@
         <v>0</v>
       </c>
       <c r="Z347" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA347" s="3" t="n">
         <v>849</v>
@@ -40258,7 +40258,7 @@
         <v>0.001242</v>
       </c>
       <c r="Y357" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z357" s="3" t="n">
         <v>0</v>
@@ -40658,10 +40658,10 @@
         <v>0.001262</v>
       </c>
       <c r="Y361" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z361" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA361" s="3" t="n">
         <v>708</v>
@@ -40961,7 +40961,7 @@
         <v>-0</v>
       </c>
       <c r="Z364" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA364" s="3" t="n">
         <v>84</v>
@@ -41658,10 +41658,10 @@
         <v>0.001213</v>
       </c>
       <c r="Y371" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z371" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA371" s="3" t="n">
         <v>343</v>
@@ -42361,7 +42361,7 @@
         <v>0</v>
       </c>
       <c r="Z378" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA378" s="3" t="n">
         <v>607</v>
@@ -42461,7 +42461,7 @@
         <v>0</v>
       </c>
       <c r="Z379" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA379" s="3" t="n">
         <v>1642</v>
@@ -42558,10 +42558,10 @@
         <v>0.001105</v>
       </c>
       <c r="Y380" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z380" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA380" s="3" t="n">
         <v>247</v>
@@ -42761,7 +42761,7 @@
         <v>0</v>
       </c>
       <c r="Z382" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA382" s="3" t="n">
         <v>792</v>
@@ -42858,7 +42858,7 @@
         <v>0.001039</v>
       </c>
       <c r="Y383" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z383" s="3" t="n">
         <v>-0</v>
@@ -43158,10 +43158,10 @@
         <v>0.0009810000000000001</v>
       </c>
       <c r="Y386" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z386" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA386" s="3" t="n">
         <v>562</v>
@@ -43358,7 +43358,7 @@
         <v>0.00098</v>
       </c>
       <c r="Y388" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z388" s="3" t="n">
         <v>-0</v>
@@ -43558,10 +43558,10 @@
         <v>0.000957</v>
       </c>
       <c r="Y390" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z390" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA390" s="3" t="n">
         <v>1161</v>
@@ -43658,10 +43658,10 @@
         <v>0.00102</v>
       </c>
       <c r="Y391" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z391" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA391" s="3" t="n">
         <v>230</v>
@@ -43761,7 +43761,7 @@
         <v>0</v>
       </c>
       <c r="Z392" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA392" s="3" t="n">
         <v>502</v>
@@ -44258,7 +44258,7 @@
         <v>0.00096</v>
       </c>
       <c r="Y397" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z397" s="3" t="n">
         <v>0</v>
@@ -44458,7 +44458,7 @@
         <v>0.000849</v>
       </c>
       <c r="Y399" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z399" s="3" t="n">
         <v>-0</v>
@@ -44558,10 +44558,10 @@
         <v>0.000806</v>
       </c>
       <c r="Y400" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z400" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA400" s="3" t="n">
         <v>643</v>
@@ -44734,10 +44734,10 @@
         <v>0.460874</v>
       </c>
       <c r="Y403" s="3" t="n">
-        <v>0.316563</v>
+        <v>0.281934</v>
       </c>
       <c r="Z403" s="3" t="n">
-        <v>0.304156</v>
+        <v>0.271601</v>
       </c>
       <c r="AB403" s="3" t="n">
         <v>0.504359</v>
@@ -44796,10 +44796,10 @@
         <v>0.58377</v>
       </c>
       <c r="Y405" s="3" t="n">
-        <v>0.157129</v>
+        <v>0.099096</v>
       </c>
       <c r="Z405" s="3" t="n">
-        <v>0.140813</v>
+        <v>0.105628</v>
       </c>
       <c r="AA405" s="3" t="n">
         <v>0.613529</v>
@@ -44834,10 +44834,10 @@
         <v>0.810408</v>
       </c>
       <c r="Y407" s="3" t="n">
-        <v>-0.052214</v>
+        <v>-0.110708</v>
       </c>
       <c r="Z407" s="3" t="n">
-        <v>-0.087516</v>
+        <v>-0.118676</v>
       </c>
       <c r="AC407" s="3" t="n">
         <v>0.872465</v>
@@ -45136,10 +45136,10 @@
         <v>0.467527</v>
       </c>
       <c r="D8" t="n">
-        <v>0.157129</v>
+        <v>0.099096</v>
       </c>
       <c r="E8" t="n">
-        <v>0.105078</v>
+        <v>0.063844</v>
       </c>
       <c r="F8" t="n">
         <v/>
@@ -45166,10 +45166,10 @@
         <v>0.733924</v>
       </c>
       <c r="D9" t="n">
-        <v>0.316563</v>
+        <v>0.281934</v>
       </c>
       <c r="E9" t="n">
-        <v>0.209218</v>
+        <v>0.182144</v>
       </c>
       <c r="F9" t="n">
         <v/>
@@ -45196,10 +45196,10 @@
         <v>0.649212</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.052214</v>
+        <v>-0.110708</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.033409</v>
+        <v>-0.073985</v>
       </c>
       <c r="F10" t="n">
         <v/>
@@ -45226,10 +45226,10 @@
         <v>0.467574</v>
       </c>
       <c r="D11" t="n">
-        <v>0.140813</v>
+        <v>0.105628</v>
       </c>
       <c r="E11" t="n">
-        <v>0.091894</v>
+        <v>0.069309</v>
       </c>
       <c r="F11" t="n">
         <v/>
@@ -45256,10 +45256,10 @@
         <v>0.733855</v>
       </c>
       <c r="D12" t="n">
-        <v>0.304156</v>
+        <v>0.271601</v>
       </c>
       <c r="E12" t="n">
-        <v>0.198438</v>
+        <v>0.174022</v>
       </c>
       <c r="F12" t="n">
         <v/>
@@ -45286,10 +45286,10 @@
         <v>0.649384</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.087516</v>
+        <v>-0.118676</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.058747</v>
+        <v>-0.078747</v>
       </c>
       <c r="F13" t="n">
         <v/>

--- a/EpiRank_改_Germany/ERA_result_reverse_seqday_d_0.95_loops_310.xlsx
+++ b/EpiRank_改_Germany/ERA_result_reverse_seqday_d_0.95_loops_310.xlsx
@@ -720,10 +720,10 @@
         <v>0.9351429999999999</v>
       </c>
       <c r="AA2" s="3" t="n">
-        <v>35664</v>
+        <v>30000</v>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>29116</v>
+        <v>26984</v>
       </c>
       <c r="AC2" s="3" t="n">
         <v>1477017</v>
@@ -859,16 +859,16 @@
         <v>0.019464</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA3" s="3" t="n">
-        <v>34035</v>
+        <v>24659</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>7880</v>
+        <v>7440</v>
       </c>
       <c r="AC3" s="3" t="n">
         <v>736525</v>
@@ -1010,10 +1010,10 @@
         <v>0</v>
       </c>
       <c r="AA4" s="3" t="n">
-        <v>27918</v>
+        <v>23995</v>
       </c>
       <c r="AB4" s="3" t="n">
-        <v>11726</v>
+        <v>11114</v>
       </c>
       <c r="AC4" s="3" t="n">
         <v>828151</v>
@@ -1155,10 +1155,10 @@
         <v>0</v>
       </c>
       <c r="AA5" s="3" t="n">
-        <v>8482</v>
+        <v>6982</v>
       </c>
       <c r="AB5" s="3" t="n">
-        <v>4477</v>
+        <v>4086</v>
       </c>
       <c r="AC5" s="3" t="n">
         <v>549016</v>
@@ -1300,10 +1300,10 @@
         <v>0</v>
       </c>
       <c r="AA6" s="3" t="n">
-        <v>6805</v>
+        <v>5644</v>
       </c>
       <c r="AB6" s="3" t="n">
-        <v>3551</v>
+        <v>3409</v>
       </c>
       <c r="AC6" s="3" t="n">
         <v>341931</v>
@@ -1441,10 +1441,10 @@
         <v>0</v>
       </c>
       <c r="AA7" s="3" t="n">
-        <v>7677</v>
+        <v>6503</v>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>1465</v>
+        <v>1346</v>
       </c>
       <c r="AC7" s="3" t="n">
         <v>263686</v>
@@ -1576,16 +1576,16 @@
         <v>0.009171</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="3" t="n">
-        <v>8532</v>
+        <v>6682</v>
       </c>
       <c r="AB8" s="3" t="n">
-        <v>4129</v>
+        <v>3905</v>
       </c>
       <c r="AC8" s="3" t="n">
         <v>522328</v>
@@ -1723,10 +1723,10 @@
         <v>3e-06</v>
       </c>
       <c r="AA9" s="3" t="n">
-        <v>25337</v>
+        <v>22285</v>
       </c>
       <c r="AB9" s="3" t="n">
-        <v>4683</v>
+        <v>4393</v>
       </c>
       <c r="AC9" s="3" t="n">
         <v>293090</v>
@@ -1864,10 +1864,10 @@
         <v>-0</v>
       </c>
       <c r="AA10" s="3" t="n">
-        <v>6490</v>
+        <v>5323</v>
       </c>
       <c r="AB10" s="3" t="n">
-        <v>2130</v>
+        <v>1950</v>
       </c>
       <c r="AC10" s="3" t="n">
         <v>258750</v>
@@ -2009,10 +2009,10 @@
         <v>0</v>
       </c>
       <c r="AA11" s="3" t="n">
-        <v>1462</v>
+        <v>1195</v>
       </c>
       <c r="AB11" s="3" t="n">
-        <v>2601</v>
+        <v>2481</v>
       </c>
       <c r="AC11" s="3" t="n">
         <v>255121</v>
@@ -2154,10 +2154,10 @@
         <v>0</v>
       </c>
       <c r="AA12" s="3" t="n">
-        <v>7136</v>
+        <v>5711</v>
       </c>
       <c r="AB12" s="3" t="n">
-        <v>2405</v>
+        <v>2222</v>
       </c>
       <c r="AC12" s="3" t="n">
         <v>254011</v>
@@ -2299,10 +2299,10 @@
         <v>0</v>
       </c>
       <c r="AA13" s="3" t="n">
-        <v>13685</v>
+        <v>11216</v>
       </c>
       <c r="AB13" s="3" t="n">
-        <v>4154</v>
+        <v>3839</v>
       </c>
       <c r="AC13" s="3" t="n">
         <v>289842</v>
@@ -2434,10 +2434,10 @@
         <v>0</v>
       </c>
       <c r="AA14" s="3" t="n">
-        <v>4465</v>
+        <v>3321</v>
       </c>
       <c r="AB14" s="3" t="n">
-        <v>2941</v>
+        <v>2746</v>
       </c>
       <c r="AC14" s="3" t="n">
         <v>284086</v>
@@ -2554,10 +2554,10 @@
         <v>0</v>
       </c>
       <c r="AA15" s="3" t="n">
-        <v>1620</v>
+        <v>1298</v>
       </c>
       <c r="AB15" s="3" t="n">
-        <v>2624</v>
+        <v>2502</v>
       </c>
       <c r="AC15" s="3" t="n">
         <v>157291</v>
@@ -2674,10 +2674,10 @@
         <v>-0</v>
       </c>
       <c r="AA16" s="3" t="n">
-        <v>4207</v>
+        <v>3161</v>
       </c>
       <c r="AB16" s="3" t="n">
-        <v>1959</v>
+        <v>1800</v>
       </c>
       <c r="AC16" s="3" t="n">
         <v>247527</v>
@@ -2791,13 +2791,13 @@
         <v>-0</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" s="3" t="n">
-        <v>6813</v>
+        <v>5564</v>
       </c>
       <c r="AB17" s="3" t="n">
-        <v>2250</v>
+        <v>2063</v>
       </c>
       <c r="AC17" s="3" t="n">
         <v>238986</v>
@@ -2914,10 +2914,10 @@
         <v>0</v>
       </c>
       <c r="AA18" s="3" t="n">
-        <v>2380</v>
+        <v>1745</v>
       </c>
       <c r="AB18" s="3" t="n">
-        <v>2684</v>
+        <v>2343</v>
       </c>
       <c r="AC18" s="3" t="n">
         <v>267206</v>
@@ -3031,13 +3031,13 @@
         <v>0</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA19" s="3" t="n">
-        <v>1918</v>
+        <v>1284</v>
       </c>
       <c r="AB19" s="3" t="n">
-        <v>2683</v>
+        <v>2552</v>
       </c>
       <c r="AC19" s="3" t="n">
         <v>235685</v>
@@ -3154,10 +3154,10 @@
         <v>0</v>
       </c>
       <c r="AA20" s="3" t="n">
-        <v>4952</v>
+        <v>3554</v>
       </c>
       <c r="AB20" s="3" t="n">
-        <v>3407</v>
+        <v>3265</v>
       </c>
       <c r="AC20" s="3" t="n">
         <v>269074</v>
@@ -3274,10 +3274,10 @@
         <v>0</v>
       </c>
       <c r="AA21" s="3" t="n">
-        <v>4867</v>
+        <v>4057</v>
       </c>
       <c r="AB21" s="3" t="n">
-        <v>4657</v>
+        <v>4452</v>
       </c>
       <c r="AC21" s="3" t="n">
         <v>211676</v>
@@ -3394,10 +3394,10 @@
         <v>-0</v>
       </c>
       <c r="AA22" s="3" t="n">
-        <v>3606</v>
+        <v>2787</v>
       </c>
       <c r="AB22" s="3" t="n">
-        <v>2623</v>
+        <v>2262</v>
       </c>
       <c r="AC22" s="3" t="n">
         <v>215076</v>
@@ -3508,16 +3508,16 @@
         <v>0.004559</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA23" s="3" t="n">
-        <v>4123</v>
+        <v>3443</v>
       </c>
       <c r="AB23" s="3" t="n">
-        <v>1742</v>
+        <v>1651</v>
       </c>
       <c r="AC23" s="3" t="n">
         <v>214509</v>
@@ -3634,10 +3634,10 @@
         <v>0</v>
       </c>
       <c r="AA24" s="3" t="n">
-        <v>3006</v>
+        <v>2364</v>
       </c>
       <c r="AB24" s="3" t="n">
-        <v>2215</v>
+        <v>2127</v>
       </c>
       <c r="AC24" s="3" t="n">
         <v>139375</v>
@@ -3748,16 +3748,16 @@
         <v>0.004805</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA25" s="3" t="n">
-        <v>1432</v>
+        <v>1048</v>
       </c>
       <c r="AB25" s="3" t="n">
-        <v>1468</v>
+        <v>1301</v>
       </c>
       <c r="AC25" s="3" t="n">
         <v>147675</v>
@@ -3874,10 +3874,10 @@
         <v>-0</v>
       </c>
       <c r="AA26" s="3" t="n">
-        <v>2262</v>
+        <v>1799</v>
       </c>
       <c r="AB26" s="3" t="n">
-        <v>3157</v>
+        <v>3014</v>
       </c>
       <c r="AC26" s="3" t="n">
         <v>262194</v>
@@ -3994,10 +3994,10 @@
         <v>0</v>
       </c>
       <c r="AA27" s="3" t="n">
-        <v>3369</v>
+        <v>2355</v>
       </c>
       <c r="AB27" s="3" t="n">
-        <v>3996</v>
+        <v>3684</v>
       </c>
       <c r="AC27" s="3" t="n">
         <v>254023</v>
@@ -4114,10 +4114,10 @@
         <v>0</v>
       </c>
       <c r="AA28" s="3" t="n">
-        <v>2908</v>
+        <v>2366</v>
       </c>
       <c r="AB28" s="3" t="n">
-        <v>2603</v>
+        <v>2395</v>
       </c>
       <c r="AC28" s="3" t="n">
         <v>159960</v>
@@ -4234,10 +4234,10 @@
         <v>0</v>
       </c>
       <c r="AA29" s="3" t="n">
-        <v>3797</v>
+        <v>2969</v>
       </c>
       <c r="AB29" s="3" t="n">
-        <v>3769</v>
+        <v>3190</v>
       </c>
       <c r="AC29" s="3" t="n">
         <v>83977</v>
@@ -4348,16 +4348,16 @@
         <v>0.004134</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="AA30" s="3" t="n">
-        <v>3860</v>
+        <v>3044</v>
       </c>
       <c r="AB30" s="3" t="n">
-        <v>1551</v>
+        <v>1358</v>
       </c>
       <c r="AC30" s="3" t="n">
         <v>200571</v>
@@ -4468,16 +4468,16 @@
         <v>0.004758</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA31" s="3" t="n">
-        <v>2551</v>
+        <v>2167</v>
       </c>
       <c r="AB31" s="3" t="n">
-        <v>1131</v>
+        <v>1065</v>
       </c>
       <c r="AC31" s="3" t="n">
         <v>133058</v>
@@ -4594,10 +4594,10 @@
         <v>0</v>
       </c>
       <c r="AA32" s="3" t="n">
-        <v>5165</v>
+        <v>3948</v>
       </c>
       <c r="AB32" s="3" t="n">
-        <v>2601</v>
+        <v>2501</v>
       </c>
       <c r="AC32" s="3" t="n">
         <v>218319</v>
@@ -4708,16 +4708,16 @@
         <v>0.003865</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA33" s="3" t="n">
-        <v>11679</v>
+        <v>9262</v>
       </c>
       <c r="AB33" s="3" t="n">
-        <v>1646</v>
+        <v>1539</v>
       </c>
       <c r="AC33" s="3" t="n">
         <v>170202</v>
@@ -4831,13 +4831,13 @@
         <v>-0</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA34" s="3" t="n">
-        <v>3417</v>
+        <v>2634</v>
       </c>
       <c r="AB34" s="3" t="n">
-        <v>1002</v>
+        <v>933</v>
       </c>
       <c r="AC34" s="3" t="n">
         <v>186667</v>
@@ -4948,16 +4948,16 @@
         <v>0.004087</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA35" s="3" t="n">
-        <v>2538</v>
+        <v>1916</v>
       </c>
       <c r="AB35" s="3" t="n">
-        <v>2703</v>
+        <v>2555</v>
       </c>
       <c r="AC35" s="3" t="n">
         <v>167225</v>
@@ -5074,10 +5074,10 @@
         <v>0</v>
       </c>
       <c r="AA36" s="3" t="n">
-        <v>7852</v>
+        <v>6250</v>
       </c>
       <c r="AB36" s="3" t="n">
-        <v>4089</v>
+        <v>3794</v>
       </c>
       <c r="AC36" s="3" t="n">
         <v>151232</v>
@@ -5191,13 +5191,13 @@
         <v>0</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA37" s="3" t="n">
-        <v>2678</v>
+        <v>1832</v>
       </c>
       <c r="AB37" s="3" t="n">
-        <v>1135</v>
+        <v>1050</v>
       </c>
       <c r="AC37" s="3" t="n">
         <v>154363</v>
@@ -5311,13 +5311,13 @@
         <v>0</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA38" s="3" t="n">
-        <v>2893</v>
+        <v>2305</v>
       </c>
       <c r="AB38" s="3" t="n">
-        <v>1704</v>
+        <v>1585</v>
       </c>
       <c r="AC38" s="3" t="n">
         <v>169197</v>
@@ -5428,16 +5428,16 @@
         <v>0.003686</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA39" s="3" t="n">
-        <v>3059</v>
+        <v>2255</v>
       </c>
       <c r="AB39" s="3" t="n">
-        <v>1465</v>
+        <v>1398</v>
       </c>
       <c r="AC39" s="3" t="n">
         <v>132271</v>
@@ -5548,16 +5548,16 @@
         <v>0.003755</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA40" s="3" t="n">
-        <v>2060</v>
+        <v>1545</v>
       </c>
       <c r="AB40" s="3" t="n">
-        <v>1436</v>
+        <v>1348</v>
       </c>
       <c r="AC40" s="3" t="n">
         <v>172067</v>
@@ -5671,13 +5671,13 @@
         <v>0</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA41" s="3" t="n">
-        <v>1989</v>
+        <v>1589</v>
       </c>
       <c r="AB41" s="3" t="n">
-        <v>2578</v>
+        <v>2486</v>
       </c>
       <c r="AC41" s="3" t="n">
         <v>136372</v>
@@ -5794,10 +5794,10 @@
         <v>0</v>
       </c>
       <c r="AA42" s="3" t="n">
-        <v>10878</v>
+        <v>8640</v>
       </c>
       <c r="AB42" s="3" t="n">
-        <v>4308</v>
+        <v>4052</v>
       </c>
       <c r="AC42" s="3" t="n">
         <v>167986</v>
@@ -5914,10 +5914,10 @@
         <v>0</v>
       </c>
       <c r="AA43" s="3" t="n">
-        <v>2064</v>
+        <v>1596</v>
       </c>
       <c r="AB43" s="3" t="n">
-        <v>2076</v>
+        <v>1986</v>
       </c>
       <c r="AC43" s="3" t="n">
         <v>167127</v>
@@ -6034,10 +6034,10 @@
         <v>0</v>
       </c>
       <c r="AA44" s="3" t="n">
-        <v>1117</v>
+        <v>885</v>
       </c>
       <c r="AB44" s="3" t="n">
-        <v>1214</v>
+        <v>1133</v>
       </c>
       <c r="AC44" s="3" t="n">
         <v>113148</v>
@@ -6154,10 +6154,10 @@
         <v>0</v>
       </c>
       <c r="AA45" s="3" t="n">
-        <v>2526</v>
+        <v>1897</v>
       </c>
       <c r="AB45" s="3" t="n">
-        <v>3903</v>
+        <v>3581</v>
       </c>
       <c r="AC45" s="3" t="n">
         <v>238412</v>
@@ -6274,10 +6274,10 @@
         <v>2e-06</v>
       </c>
       <c r="AA46" s="3" t="n">
-        <v>5600</v>
+        <v>4996</v>
       </c>
       <c r="AB46" s="3" t="n">
-        <v>4264</v>
+        <v>4072</v>
       </c>
       <c r="AC46" s="3" t="n">
         <v>93342</v>
@@ -6388,16 +6388,16 @@
         <v>0.003516</v>
       </c>
       <c r="Y47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="Z47" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AA47" s="3" t="n">
-        <v>2752</v>
+        <v>1840</v>
       </c>
       <c r="AB47" s="3" t="n">
-        <v>1378</v>
+        <v>1224</v>
       </c>
       <c r="AC47" s="3" t="n">
         <v>150423</v>
@@ -6514,10 +6514,10 @@
         <v>0</v>
       </c>
       <c r="AA48" s="3" t="n">
-        <v>3379</v>
+        <v>2489</v>
       </c>
       <c r="AB48" s="3" t="n">
-        <v>1949</v>
+        <v>1830</v>
       </c>
       <c r="AC48" s="3" t="n">
         <v>198424</v>
@@ -6631,13 +6631,13 @@
         <v>0</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA49" s="3" t="n">
-        <v>7680</v>
+        <v>5738</v>
       </c>
       <c r="AB49" s="3" t="n">
-        <v>1816</v>
+        <v>1664</v>
       </c>
       <c r="AC49" s="3" t="n">
         <v>107335</v>
@@ -6748,16 +6748,16 @@
         <v>0.00308</v>
       </c>
       <c r="Y50" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z50" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA50" s="3" t="n">
-        <v>1472</v>
+        <v>1112</v>
       </c>
       <c r="AB50" s="3" t="n">
-        <v>897</v>
+        <v>845</v>
       </c>
       <c r="AC50" s="3" t="n">
         <v>126408</v>
@@ -6874,10 +6874,10 @@
         <v>0</v>
       </c>
       <c r="AA51" s="3" t="n">
-        <v>2152</v>
+        <v>1646</v>
       </c>
       <c r="AB51" s="3" t="n">
-        <v>2187</v>
+        <v>2053</v>
       </c>
       <c r="AC51" s="3" t="n">
         <v>204631</v>
@@ -6988,16 +6988,16 @@
         <v>0.003143</v>
       </c>
       <c r="Y52" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z52" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA52" s="3" t="n">
-        <v>2303</v>
+        <v>1654</v>
       </c>
       <c r="AB52" s="3" t="n">
-        <v>2241</v>
+        <v>2155</v>
       </c>
       <c r="AC52" s="3" t="n">
         <v>236874</v>
@@ -7111,13 +7111,13 @@
         <v>0</v>
       </c>
       <c r="Z53" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA53" s="3" t="n">
-        <v>930</v>
+        <v>677</v>
       </c>
       <c r="AB53" s="3" t="n">
-        <v>1093</v>
+        <v>1025</v>
       </c>
       <c r="AC53" s="3" t="n">
         <v>134090</v>
@@ -7234,10 +7234,10 @@
         <v>0</v>
       </c>
       <c r="AA54" s="3" t="n">
-        <v>5461</v>
+        <v>4315</v>
       </c>
       <c r="AB54" s="3" t="n">
-        <v>2706</v>
+        <v>2497</v>
       </c>
       <c r="AC54" s="3" t="n">
         <v>113002</v>
@@ -7348,16 +7348,16 @@
         <v>0.003258</v>
       </c>
       <c r="Y55" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z55" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA55" s="3" t="n">
-        <v>1293</v>
+        <v>990</v>
       </c>
       <c r="AB55" s="3" t="n">
-        <v>1252</v>
+        <v>1150</v>
       </c>
       <c r="AC55" s="3" t="n">
         <v>128863</v>
@@ -7474,10 +7474,10 @@
         <v>0</v>
       </c>
       <c r="AA56" s="3" t="n">
-        <v>4129</v>
+        <v>2982</v>
       </c>
       <c r="AB56" s="3" t="n">
-        <v>1292</v>
+        <v>1207</v>
       </c>
       <c r="AC56" s="3" t="n">
         <v>194254</v>
@@ -7594,10 +7594,10 @@
         <v>0</v>
       </c>
       <c r="AA57" s="3" t="n">
-        <v>2734</v>
+        <v>2042</v>
       </c>
       <c r="AB57" s="3" t="n">
-        <v>1935</v>
+        <v>1840</v>
       </c>
       <c r="AC57" s="3" t="n">
         <v>185793</v>
@@ -7714,10 +7714,10 @@
         <v>0</v>
       </c>
       <c r="AA58" s="3" t="n">
-        <v>2101</v>
+        <v>1747</v>
       </c>
       <c r="AB58" s="3" t="n">
-        <v>1670</v>
+        <v>1554</v>
       </c>
       <c r="AC58" s="3" t="n">
         <v>138620</v>
@@ -7834,10 +7834,10 @@
         <v>0</v>
       </c>
       <c r="AA59" s="3" t="n">
-        <v>2443</v>
+        <v>2054</v>
       </c>
       <c r="AB59" s="3" t="n">
-        <v>2283</v>
+        <v>2129</v>
       </c>
       <c r="AC59" s="3" t="n">
         <v>201013</v>
@@ -7954,10 +7954,10 @@
         <v>0</v>
       </c>
       <c r="AA60" s="3" t="n">
-        <v>2122</v>
+        <v>1633</v>
       </c>
       <c r="AB60" s="3" t="n">
-        <v>2648</v>
+        <v>2495</v>
       </c>
       <c r="AC60" s="3" t="n">
         <v>156360</v>
@@ -8074,10 +8074,10 @@
         <v>0</v>
       </c>
       <c r="AA61" s="3" t="n">
-        <v>11662</v>
+        <v>10064</v>
       </c>
       <c r="AB61" s="3" t="n">
-        <v>3951</v>
+        <v>3703</v>
       </c>
       <c r="AC61" s="3" t="n">
         <v>145072</v>
@@ -8191,13 +8191,13 @@
         <v>0</v>
       </c>
       <c r="Z62" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA62" s="3" t="n">
-        <v>2142</v>
+        <v>1780</v>
       </c>
       <c r="AB62" s="3" t="n">
-        <v>1094</v>
+        <v>1019</v>
       </c>
       <c r="AC62" s="3" t="n">
         <v>133690</v>
@@ -8311,13 +8311,13 @@
         <v>-0</v>
       </c>
       <c r="Z63" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA63" s="3" t="n">
-        <v>3557</v>
+        <v>2901</v>
       </c>
       <c r="AB63" s="3" t="n">
-        <v>1502</v>
+        <v>1344</v>
       </c>
       <c r="AC63" s="3" t="n">
         <v>134853</v>
@@ -8434,10 +8434,10 @@
         <v>0</v>
       </c>
       <c r="AA64" s="3" t="n">
-        <v>3344</v>
+        <v>2678</v>
       </c>
       <c r="AB64" s="3" t="n">
-        <v>1851</v>
+        <v>1759</v>
       </c>
       <c r="AC64" s="3" t="n">
         <v>138200</v>
@@ -8554,10 +8554,10 @@
         <v>0</v>
       </c>
       <c r="AA65" s="3" t="n">
-        <v>4171</v>
+        <v>3701</v>
       </c>
       <c r="AB65" s="3" t="n">
-        <v>2128</v>
+        <v>1881</v>
       </c>
       <c r="AC65" s="3" t="n">
         <v>105697</v>
@@ -8668,16 +8668,16 @@
         <v>0.00324</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA66" s="3" t="n">
-        <v>2524</v>
+        <v>1941</v>
       </c>
       <c r="AB66" s="3" t="n">
-        <v>1620</v>
+        <v>1548</v>
       </c>
       <c r="AC66" s="3" t="n">
         <v>143663</v>
@@ -8794,10 +8794,10 @@
         <v>0</v>
       </c>
       <c r="AA67" s="3" t="n">
-        <v>3819</v>
+        <v>2999</v>
       </c>
       <c r="AB67" s="3" t="n">
-        <v>486</v>
+        <v>434</v>
       </c>
       <c r="AC67" s="3" t="n">
         <v>78578</v>
@@ -8908,16 +8908,16 @@
         <v>0.00306</v>
       </c>
       <c r="Y68" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z68" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA68" s="3" t="n">
-        <v>1130</v>
+        <v>848</v>
       </c>
       <c r="AB68" s="3" t="n">
-        <v>1585</v>
+        <v>1460</v>
       </c>
       <c r="AC68" s="3" t="n">
         <v>104492</v>
@@ -9034,10 +9034,10 @@
         <v>-0</v>
       </c>
       <c r="AA69" s="3" t="n">
-        <v>3171</v>
+        <v>2549</v>
       </c>
       <c r="AB69" s="3" t="n">
-        <v>2624</v>
+        <v>2511</v>
       </c>
       <c r="AC69" s="3" t="n">
         <v>198885</v>
@@ -9154,10 +9154,10 @@
         <v>0</v>
       </c>
       <c r="AA70" s="3" t="n">
-        <v>9844</v>
+        <v>8330</v>
       </c>
       <c r="AB70" s="3" t="n">
-        <v>3710</v>
+        <v>3372</v>
       </c>
       <c r="AC70" s="3" t="n">
         <v>160814</v>
@@ -9274,10 +9274,10 @@
         <v>0</v>
       </c>
       <c r="AA71" s="3" t="n">
-        <v>1701</v>
+        <v>1388</v>
       </c>
       <c r="AB71" s="3" t="n">
-        <v>1694</v>
+        <v>1561</v>
       </c>
       <c r="AC71" s="3" t="n">
         <v>179203</v>
@@ -9394,10 +9394,10 @@
         <v>0</v>
       </c>
       <c r="AA72" s="3" t="n">
-        <v>5618</v>
+        <v>4410</v>
       </c>
       <c r="AB72" s="3" t="n">
-        <v>671</v>
+        <v>612</v>
       </c>
       <c r="AC72" s="3" t="n">
         <v>107984</v>
@@ -9508,16 +9508,16 @@
         <v>0.003381</v>
       </c>
       <c r="Y73" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z73" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA73" s="3" t="n">
-        <v>1306</v>
+        <v>1053</v>
       </c>
       <c r="AB73" s="3" t="n">
-        <v>1738</v>
+        <v>1594</v>
       </c>
       <c r="AC73" s="3" t="n">
         <v>175579</v>
@@ -9634,10 +9634,10 @@
         <v>0</v>
       </c>
       <c r="AA74" s="3" t="n">
-        <v>1868</v>
+        <v>1420</v>
       </c>
       <c r="AB74" s="3" t="n">
-        <v>1859</v>
+        <v>1749</v>
       </c>
       <c r="AC74" s="3" t="n">
         <v>124289</v>
@@ -9754,10 +9754,10 @@
         <v>0</v>
       </c>
       <c r="AA75" s="3" t="n">
-        <v>2678</v>
+        <v>2158</v>
       </c>
       <c r="AB75" s="3" t="n">
-        <v>2266</v>
+        <v>2064</v>
       </c>
       <c r="AC75" s="3" t="n">
         <v>140016</v>
@@ -9874,10 +9874,10 @@
         <v>0</v>
       </c>
       <c r="AA76" s="3" t="n">
-        <v>548</v>
+        <v>448</v>
       </c>
       <c r="AB76" s="3" t="n">
-        <v>905</v>
+        <v>817</v>
       </c>
       <c r="AC76" s="3" t="n">
         <v>90630</v>
@@ -9994,10 +9994,10 @@
         <v>0</v>
       </c>
       <c r="AA77" s="3" t="n">
-        <v>3194</v>
+        <v>2357</v>
       </c>
       <c r="AB77" s="3" t="n">
-        <v>2985</v>
+        <v>2885</v>
       </c>
       <c r="AC77" s="3" t="n">
         <v>149832</v>
@@ -10114,10 +10114,10 @@
         <v>0</v>
       </c>
       <c r="AA78" s="3" t="n">
-        <v>11227</v>
+        <v>10332</v>
       </c>
       <c r="AB78" s="3" t="n">
-        <v>4580</v>
+        <v>4410</v>
       </c>
       <c r="AC78" s="3" t="n">
         <v>113929</v>
@@ -10234,10 +10234,10 @@
         <v>0</v>
       </c>
       <c r="AA79" s="3" t="n">
-        <v>2463</v>
+        <v>2073</v>
       </c>
       <c r="AB79" s="3" t="n">
-        <v>1263</v>
+        <v>1206</v>
       </c>
       <c r="AC79" s="3" t="n">
         <v>115651</v>
@@ -10354,10 +10354,10 @@
         <v>0</v>
       </c>
       <c r="AA80" s="3" t="n">
-        <v>2602</v>
+        <v>2084</v>
       </c>
       <c r="AB80" s="3" t="n">
-        <v>2392</v>
+        <v>2158</v>
       </c>
       <c r="AC80" s="3" t="n">
         <v>173030</v>
@@ -10474,10 +10474,10 @@
         <v>0</v>
       </c>
       <c r="AA81" s="3" t="n">
-        <v>7421</v>
+        <v>6058</v>
       </c>
       <c r="AB81" s="3" t="n">
-        <v>2798</v>
+        <v>2571</v>
       </c>
       <c r="AC81" s="3" t="n">
         <v>113041</v>
@@ -10591,13 +10591,13 @@
         <v>0</v>
       </c>
       <c r="Z82" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA82" s="3" t="n">
-        <v>3690</v>
+        <v>3152</v>
       </c>
       <c r="AB82" s="3" t="n">
-        <v>1638</v>
+        <v>1510</v>
       </c>
       <c r="AC82" s="3" t="n">
         <v>150752</v>
@@ -10714,10 +10714,10 @@
         <v>0</v>
       </c>
       <c r="AA83" s="3" t="n">
-        <v>1694</v>
+        <v>1341</v>
       </c>
       <c r="AB83" s="3" t="n">
-        <v>2091</v>
+        <v>1920</v>
       </c>
       <c r="AC83" s="3" t="n">
         <v>133621</v>
@@ -10834,10 +10834,10 @@
         <v>-0</v>
       </c>
       <c r="AA84" s="3" t="n">
-        <v>1745</v>
+        <v>1340</v>
       </c>
       <c r="AB84" s="3" t="n">
-        <v>710</v>
+        <v>627</v>
       </c>
       <c r="AC84" s="3" t="n">
         <v>114450</v>
@@ -10954,10 +10954,10 @@
         <v>-0</v>
       </c>
       <c r="AA85" s="3" t="n">
-        <v>765</v>
+        <v>570</v>
       </c>
       <c r="AB85" s="3" t="n">
-        <v>870</v>
+        <v>821</v>
       </c>
       <c r="AC85" s="3" t="n">
         <v>122290</v>
@@ -11074,10 +11074,10 @@
         <v>0</v>
       </c>
       <c r="AA86" s="3" t="n">
-        <v>871</v>
+        <v>652</v>
       </c>
       <c r="AB86" s="3" t="n">
-        <v>1073</v>
+        <v>850</v>
       </c>
       <c r="AC86" s="3" t="n">
         <v>134524</v>
@@ -11194,10 +11194,10 @@
         <v>0</v>
       </c>
       <c r="AA87" s="3" t="n">
-        <v>1472</v>
+        <v>1169</v>
       </c>
       <c r="AB87" s="3" t="n">
-        <v>497</v>
+        <v>481</v>
       </c>
       <c r="AC87" s="3" t="n">
         <v>103066</v>
@@ -11314,10 +11314,10 @@
         <v>0</v>
       </c>
       <c r="AA88" s="3" t="n">
-        <v>1537</v>
+        <v>1358</v>
       </c>
       <c r="AB88" s="3" t="n">
-        <v>970</v>
+        <v>878</v>
       </c>
       <c r="AC88" s="3" t="n">
         <v>101231</v>
@@ -11434,10 +11434,10 @@
         <v>0</v>
       </c>
       <c r="AA89" s="3" t="n">
-        <v>2935</v>
+        <v>2400</v>
       </c>
       <c r="AB89" s="3" t="n">
-        <v>569</v>
+        <v>515</v>
       </c>
       <c r="AC89" s="3" t="n">
         <v>86794</v>
@@ -11554,10 +11554,10 @@
         <v>0</v>
       </c>
       <c r="AA90" s="3" t="n">
-        <v>1414</v>
+        <v>1258</v>
       </c>
       <c r="AB90" s="3" t="n">
-        <v>842</v>
+        <v>788</v>
       </c>
       <c r="AC90" s="3" t="n">
         <v>81733</v>
@@ -11674,10 +11674,10 @@
         <v>0</v>
       </c>
       <c r="AA91" s="3" t="n">
-        <v>3818</v>
+        <v>3281</v>
       </c>
       <c r="AB91" s="3" t="n">
-        <v>2938</v>
+        <v>2723</v>
       </c>
       <c r="AC91" s="3" t="n">
         <v>199738</v>
@@ -11788,16 +11788,16 @@
         <v>0.002739</v>
       </c>
       <c r="Y92" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z92" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA92" s="3" t="n">
-        <v>2843</v>
+        <v>2093</v>
       </c>
       <c r="AB92" s="3" t="n">
-        <v>1286</v>
+        <v>1202</v>
       </c>
       <c r="AC92" s="3" t="n">
         <v>94308</v>
@@ -11914,10 +11914,10 @@
         <v>1e-06</v>
       </c>
       <c r="AA93" s="3" t="n">
-        <v>12443</v>
+        <v>11137</v>
       </c>
       <c r="AB93" s="3" t="n">
-        <v>3476</v>
+        <v>3184</v>
       </c>
       <c r="AC93" s="3" t="n">
         <v>134228</v>
@@ -12034,10 +12034,10 @@
         <v>-0</v>
       </c>
       <c r="AA94" s="3" t="n">
-        <v>3835</v>
+        <v>3105</v>
       </c>
       <c r="AB94" s="3" t="n">
-        <v>730</v>
+        <v>671</v>
       </c>
       <c r="AC94" s="3" t="n">
         <v>108098</v>
@@ -12154,10 +12154,10 @@
         <v>0</v>
       </c>
       <c r="AA95" s="3" t="n">
-        <v>5482</v>
+        <v>4626</v>
       </c>
       <c r="AB95" s="3" t="n">
-        <v>2095</v>
+        <v>1988</v>
       </c>
       <c r="AC95" s="3" t="n">
         <v>130239</v>
@@ -12274,10 +12274,10 @@
         <v>0</v>
       </c>
       <c r="AA96" s="3" t="n">
-        <v>2203</v>
+        <v>1472</v>
       </c>
       <c r="AB96" s="3" t="n">
-        <v>941</v>
+        <v>890</v>
       </c>
       <c r="AC96" s="3" t="n">
         <v>101511</v>
@@ -12394,10 +12394,10 @@
         <v>0</v>
       </c>
       <c r="AA97" s="3" t="n">
-        <v>1517</v>
+        <v>1230</v>
       </c>
       <c r="AB97" s="3" t="n">
-        <v>846</v>
+        <v>799</v>
       </c>
       <c r="AC97" s="3" t="n">
         <v>112891</v>
@@ -12514,10 +12514,10 @@
         <v>-0</v>
       </c>
       <c r="AA98" s="3" t="n">
-        <v>4116</v>
+        <v>3335</v>
       </c>
       <c r="AB98" s="3" t="n">
-        <v>1041</v>
+        <v>951</v>
       </c>
       <c r="AC98" s="3" t="n">
         <v>119264</v>
@@ -12634,10 +12634,10 @@
         <v>0</v>
       </c>
       <c r="AA99" s="3" t="n">
-        <v>671</v>
+        <v>544</v>
       </c>
       <c r="AB99" s="3" t="n">
-        <v>544</v>
+        <v>512</v>
       </c>
       <c r="AC99" s="3" t="n">
         <v>81048</v>
@@ -12754,10 +12754,10 @@
         <v>0</v>
       </c>
       <c r="AA100" s="3" t="n">
-        <v>8108</v>
+        <v>7465</v>
       </c>
       <c r="AB100" s="3" t="n">
-        <v>3997</v>
+        <v>3802</v>
       </c>
       <c r="AC100" s="3" t="n">
         <v>98352</v>
@@ -12874,10 +12874,10 @@
         <v>0</v>
       </c>
       <c r="AA101" s="3" t="n">
-        <v>969</v>
+        <v>733</v>
       </c>
       <c r="AB101" s="3" t="n">
-        <v>1423</v>
+        <v>1314</v>
       </c>
       <c r="AC101" s="3" t="n">
         <v>130625</v>
@@ -12994,10 +12994,10 @@
         <v>0</v>
       </c>
       <c r="AA102" s="3" t="n">
-        <v>1151</v>
+        <v>834</v>
       </c>
       <c r="AB102" s="3" t="n">
-        <v>1035</v>
+        <v>1005</v>
       </c>
       <c r="AC102" s="3" t="n">
         <v>70779</v>
@@ -13114,10 +13114,10 @@
         <v>0</v>
       </c>
       <c r="AA103" s="3" t="n">
-        <v>1724</v>
+        <v>1415</v>
       </c>
       <c r="AB103" s="3" t="n">
-        <v>1146</v>
+        <v>1032</v>
       </c>
       <c r="AC103" s="3" t="n">
         <v>125917</v>
@@ -13234,10 +13234,10 @@
         <v>0</v>
       </c>
       <c r="AA104" s="3" t="n">
-        <v>1943</v>
+        <v>1483</v>
       </c>
       <c r="AB104" s="3" t="n">
-        <v>1094</v>
+        <v>1046</v>
       </c>
       <c r="AC104" s="3" t="n">
         <v>98098</v>
@@ -13354,10 +13354,10 @@
         <v>0</v>
       </c>
       <c r="AA105" s="3" t="n">
-        <v>1123</v>
+        <v>840</v>
       </c>
       <c r="AB105" s="3" t="n">
-        <v>4072</v>
+        <v>3589</v>
       </c>
       <c r="AC105" s="3" t="n">
         <v>121897</v>
@@ -13474,10 +13474,10 @@
         <v>0</v>
       </c>
       <c r="AA106" s="3" t="n">
-        <v>3061</v>
+        <v>2613</v>
       </c>
       <c r="AB106" s="3" t="n">
-        <v>3431</v>
+        <v>2936</v>
       </c>
       <c r="AC106" s="3" t="n">
         <v>95398</v>
@@ -13594,10 +13594,10 @@
         <v>0</v>
       </c>
       <c r="AA107" s="3" t="n">
-        <v>1288</v>
+        <v>1074</v>
       </c>
       <c r="AB107" s="3" t="n">
-        <v>454</v>
+        <v>408</v>
       </c>
       <c r="AC107" s="3" t="n">
         <v>70204</v>
@@ -13714,10 +13714,10 @@
         <v>0</v>
       </c>
       <c r="AA108" s="3" t="n">
-        <v>2304</v>
+        <v>1875</v>
       </c>
       <c r="AB108" s="3" t="n">
-        <v>2524</v>
+        <v>2436</v>
       </c>
       <c r="AC108" s="3" t="n">
         <v>98857</v>
@@ -13828,16 +13828,16 @@
         <v>0.002646</v>
       </c>
       <c r="Y109" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z109" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA109" s="3" t="n">
-        <v>2711</v>
+        <v>2324</v>
       </c>
       <c r="AB109" s="3" t="n">
-        <v>1760</v>
+        <v>1673</v>
       </c>
       <c r="AC109" s="3" t="n">
         <v>99164</v>
@@ -13954,10 +13954,10 @@
         <v>0</v>
       </c>
       <c r="AA110" s="3" t="n">
-        <v>5645</v>
+        <v>4286</v>
       </c>
       <c r="AB110" s="3" t="n">
-        <v>1174</v>
+        <v>1011</v>
       </c>
       <c r="AC110" s="3" t="n">
         <v>81009</v>
@@ -14074,10 +14074,10 @@
         <v>0</v>
       </c>
       <c r="AA111" s="3" t="n">
-        <v>5293</v>
+        <v>4289</v>
       </c>
       <c r="AB111" s="3" t="n">
-        <v>1799</v>
+        <v>1708</v>
       </c>
       <c r="AC111" s="3" t="n">
         <v>82617</v>
@@ -14194,10 +14194,10 @@
         <v>0</v>
       </c>
       <c r="AA112" s="3" t="n">
-        <v>1092</v>
+        <v>697</v>
       </c>
       <c r="AB112" s="3" t="n">
-        <v>677</v>
+        <v>645</v>
       </c>
       <c r="AC112" s="3" t="n">
         <v>70552</v>
@@ -14308,16 +14308,16 @@
         <v>0.002608</v>
       </c>
       <c r="Y113" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z113" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA113" s="3" t="n">
-        <v>3508</v>
+        <v>2830</v>
       </c>
       <c r="AB113" s="3" t="n">
-        <v>1384</v>
+        <v>1285</v>
       </c>
       <c r="AC113" s="3" t="n">
         <v>116851</v>
@@ -14418,16 +14418,16 @@
         <v>0.002503</v>
       </c>
       <c r="Y114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z114" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="Z114" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AA114" s="3" t="n">
-        <v>1871</v>
+        <v>1450</v>
       </c>
       <c r="AB114" s="3" t="n">
-        <v>1654</v>
+        <v>1464</v>
       </c>
       <c r="AC114" s="3" t="n">
         <v>102080</v>
@@ -14531,13 +14531,13 @@
         <v>0</v>
       </c>
       <c r="Z115" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA115" s="3" t="n">
-        <v>2287</v>
+        <v>1848</v>
       </c>
       <c r="AB115" s="3" t="n">
-        <v>1744</v>
+        <v>1652</v>
       </c>
       <c r="AC115" s="3" t="n">
         <v>69784</v>
@@ -14638,16 +14638,16 @@
         <v>0.002434</v>
       </c>
       <c r="Y116" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z116" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA116" s="3" t="n">
-        <v>1796</v>
+        <v>1466</v>
       </c>
       <c r="AB116" s="3" t="n">
-        <v>969</v>
+        <v>879</v>
       </c>
       <c r="AC116" s="3" t="n">
         <v>96559</v>
@@ -14754,10 +14754,10 @@
         <v>0</v>
       </c>
       <c r="AA117" s="3" t="n">
-        <v>2127</v>
+        <v>1799</v>
       </c>
       <c r="AB117" s="3" t="n">
-        <v>2482</v>
+        <v>2413</v>
       </c>
       <c r="AC117" s="3" t="n">
         <v>94208</v>
@@ -14858,16 +14858,16 @@
         <v>0.002517</v>
       </c>
       <c r="Y118" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z118" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA118" s="3" t="n">
-        <v>4137</v>
+        <v>3519</v>
       </c>
       <c r="AB118" s="3" t="n">
-        <v>786</v>
+        <v>729</v>
       </c>
       <c r="AC118" s="3" t="n">
         <v>106284</v>
@@ -14974,10 +14974,10 @@
         <v>0</v>
       </c>
       <c r="AA119" s="3" t="n">
-        <v>2453</v>
+        <v>2164</v>
       </c>
       <c r="AB119" s="3" t="n">
-        <v>2124</v>
+        <v>1924</v>
       </c>
       <c r="AC119" s="3" t="n">
         <v>127606</v>
@@ -15084,10 +15084,10 @@
         <v>2.9e-05</v>
       </c>
       <c r="AA120" s="3" t="n">
-        <v>3031</v>
+        <v>2588</v>
       </c>
       <c r="AB120" s="3" t="n">
-        <v>4360</v>
+        <v>4014</v>
       </c>
       <c r="AC120" s="3" t="n">
         <v>99946</v>
@@ -15194,10 +15194,10 @@
         <v>0</v>
       </c>
       <c r="AA121" s="3" t="n">
-        <v>2616</v>
+        <v>2194</v>
       </c>
       <c r="AB121" s="3" t="n">
-        <v>1106</v>
+        <v>1066</v>
       </c>
       <c r="AC121" s="3" t="n">
         <v>107078</v>
@@ -15304,10 +15304,10 @@
         <v>0</v>
       </c>
       <c r="AA122" s="3" t="n">
-        <v>4089</v>
+        <v>2979</v>
       </c>
       <c r="AB122" s="3" t="n">
-        <v>841</v>
+        <v>792</v>
       </c>
       <c r="AC122" s="3" t="n">
         <v>88872</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="AA123" s="3" t="n">
-        <v>1575</v>
+        <v>1263</v>
       </c>
       <c r="AB123" s="3" t="n">
-        <v>543</v>
+        <v>509</v>
       </c>
       <c r="AC123" s="3" t="n">
         <v>83461</v>
@@ -15524,10 +15524,10 @@
         <v>0</v>
       </c>
       <c r="AA124" s="3" t="n">
-        <v>2044</v>
+        <v>1666</v>
       </c>
       <c r="AB124" s="3" t="n">
-        <v>1678</v>
+        <v>1564</v>
       </c>
       <c r="AC124" s="3" t="n">
         <v>136782</v>
@@ -15634,10 +15634,10 @@
         <v>1e-06</v>
       </c>
       <c r="AA125" s="3" t="n">
-        <v>5438</v>
+        <v>4592</v>
       </c>
       <c r="AB125" s="3" t="n">
-        <v>2742</v>
+        <v>2580</v>
       </c>
       <c r="AC125" s="3" t="n">
         <v>122915</v>
@@ -15744,10 +15744,10 @@
         <v>0</v>
       </c>
       <c r="AA126" s="3" t="n">
-        <v>2532</v>
+        <v>2024</v>
       </c>
       <c r="AB126" s="3" t="n">
-        <v>936</v>
+        <v>872</v>
       </c>
       <c r="AC126" s="3" t="n">
         <v>102505</v>
@@ -15854,10 +15854,10 @@
         <v>0</v>
       </c>
       <c r="AA127" s="3" t="n">
-        <v>1776</v>
+        <v>1297</v>
       </c>
       <c r="AB127" s="3" t="n">
-        <v>1041</v>
+        <v>978</v>
       </c>
       <c r="AC127" s="3" t="n">
         <v>87338</v>
@@ -15964,10 +15964,10 @@
         <v>0</v>
       </c>
       <c r="AA128" s="3" t="n">
-        <v>2163</v>
+        <v>1834</v>
       </c>
       <c r="AB128" s="3" t="n">
-        <v>380</v>
+        <v>344</v>
       </c>
       <c r="AC128" s="3" t="n">
         <v>48581</v>
@@ -16074,10 +16074,10 @@
         <v>0</v>
       </c>
       <c r="AA129" s="3" t="n">
-        <v>2260</v>
+        <v>1750</v>
       </c>
       <c r="AB129" s="3" t="n">
-        <v>517</v>
+        <v>475</v>
       </c>
       <c r="AC129" s="3" t="n">
         <v>74485</v>
@@ -16184,10 +16184,10 @@
         <v>0</v>
       </c>
       <c r="AA130" s="3" t="n">
-        <v>2601</v>
+        <v>2101</v>
       </c>
       <c r="AB130" s="3" t="n">
-        <v>726</v>
+        <v>669</v>
       </c>
       <c r="AC130" s="3" t="n">
         <v>67472</v>
@@ -16294,10 +16294,10 @@
         <v>0</v>
       </c>
       <c r="AA131" s="3" t="n">
-        <v>3092</v>
+        <v>2549</v>
       </c>
       <c r="AB131" s="3" t="n">
-        <v>370</v>
+        <v>322</v>
       </c>
       <c r="AC131" s="3" t="n">
         <v>71122</v>
@@ -16404,10 +16404,10 @@
         <v>0</v>
       </c>
       <c r="AA132" s="3" t="n">
-        <v>3242</v>
+        <v>2467</v>
       </c>
       <c r="AB132" s="3" t="n">
-        <v>2055</v>
+        <v>1915</v>
       </c>
       <c r="AC132" s="3" t="n">
         <v>54219</v>
@@ -16514,10 +16514,10 @@
         <v>0</v>
       </c>
       <c r="AA133" s="3" t="n">
-        <v>3944</v>
+        <v>3481</v>
       </c>
       <c r="AB133" s="3" t="n">
-        <v>2409</v>
+        <v>2199</v>
       </c>
       <c r="AC133" s="3" t="n">
         <v>49283</v>
@@ -16624,10 +16624,10 @@
         <v>0</v>
       </c>
       <c r="AA134" s="3" t="n">
-        <v>5101</v>
+        <v>3897</v>
       </c>
       <c r="AB134" s="3" t="n">
-        <v>1026</v>
+        <v>894</v>
       </c>
       <c r="AC134" s="3" t="n">
         <v>62638</v>
@@ -16734,10 +16734,10 @@
         <v>0</v>
       </c>
       <c r="AA135" s="3" t="n">
-        <v>7893</v>
+        <v>6710</v>
       </c>
       <c r="AB135" s="3" t="n">
-        <v>4712</v>
+        <v>4362</v>
       </c>
       <c r="AC135" s="3" t="n">
         <v>115211</v>
@@ -16844,10 +16844,10 @@
         <v>0</v>
       </c>
       <c r="AA136" s="3" t="n">
-        <v>1080</v>
+        <v>891</v>
       </c>
       <c r="AB136" s="3" t="n">
-        <v>1457</v>
+        <v>1376</v>
       </c>
       <c r="AC136" s="3" t="n">
         <v>82227</v>
@@ -16954,10 +16954,10 @@
         <v>0</v>
       </c>
       <c r="AA137" s="3" t="n">
-        <v>1419</v>
+        <v>1235</v>
       </c>
       <c r="AB137" s="3" t="n">
-        <v>1794</v>
+        <v>1654</v>
       </c>
       <c r="AC137" s="3" t="n">
         <v>66996</v>
@@ -17058,16 +17058,16 @@
         <v>0.002271</v>
       </c>
       <c r="Y138" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z138" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA138" s="3" t="n">
-        <v>5041</v>
+        <v>3635</v>
       </c>
       <c r="AB138" s="3" t="n">
-        <v>1673</v>
+        <v>1537</v>
       </c>
       <c r="AC138" s="3" t="n">
         <v>111209</v>
@@ -17174,10 +17174,10 @@
         <v>0</v>
       </c>
       <c r="AA139" s="3" t="n">
-        <v>1737</v>
+        <v>1490</v>
       </c>
       <c r="AB139" s="3" t="n">
-        <v>484</v>
+        <v>462</v>
       </c>
       <c r="AC139" s="3" t="n">
         <v>63576</v>
@@ -17284,10 +17284,10 @@
         <v>0</v>
       </c>
       <c r="AA140" s="3" t="n">
-        <v>980</v>
+        <v>801</v>
       </c>
       <c r="AB140" s="3" t="n">
-        <v>844</v>
+        <v>751</v>
       </c>
       <c r="AC140" s="3" t="n">
         <v>106840</v>
@@ -17394,10 +17394,10 @@
         <v>-0</v>
       </c>
       <c r="AA141" s="3" t="n">
-        <v>3546</v>
+        <v>2679</v>
       </c>
       <c r="AB141" s="3" t="n">
-        <v>1978</v>
+        <v>1791</v>
       </c>
       <c r="AC141" s="3" t="n">
         <v>136770</v>
@@ -17501,13 +17501,13 @@
         <v>0</v>
       </c>
       <c r="Z142" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA142" s="3" t="n">
-        <v>828</v>
+        <v>488</v>
       </c>
       <c r="AB142" s="3" t="n">
-        <v>959</v>
+        <v>936</v>
       </c>
       <c r="AC142" s="3" t="n">
         <v>67674</v>
@@ -17614,10 +17614,10 @@
         <v>1e-06</v>
       </c>
       <c r="AA143" s="3" t="n">
-        <v>4555</v>
+        <v>3936</v>
       </c>
       <c r="AB143" s="3" t="n">
-        <v>3296</v>
+        <v>3088</v>
       </c>
       <c r="AC143" s="3" t="n">
         <v>81994</v>
@@ -17724,10 +17724,10 @@
         <v>0</v>
       </c>
       <c r="AA144" s="3" t="n">
-        <v>2832</v>
+        <v>2529</v>
       </c>
       <c r="AB144" s="3" t="n">
-        <v>4744</v>
+        <v>4549</v>
       </c>
       <c r="AC144" s="3" t="n">
         <v>102793</v>
@@ -17834,10 +17834,10 @@
         <v>0</v>
       </c>
       <c r="AA145" s="3" t="n">
-        <v>1027</v>
+        <v>898</v>
       </c>
       <c r="AB145" s="3" t="n">
-        <v>1803</v>
+        <v>1696</v>
       </c>
       <c r="AC145" s="3" t="n">
         <v>58587</v>
@@ -17944,10 +17944,10 @@
         <v>0</v>
       </c>
       <c r="AA146" s="3" t="n">
-        <v>2904</v>
+        <v>2351</v>
       </c>
       <c r="AB146" s="3" t="n">
-        <v>1084</v>
+        <v>994</v>
       </c>
       <c r="AC146" s="3" t="n">
         <v>122200</v>
@@ -18054,10 +18054,10 @@
         <v>6e-06</v>
       </c>
       <c r="AA147" s="3" t="n">
-        <v>6956</v>
+        <v>6274</v>
       </c>
       <c r="AB147" s="3" t="n">
-        <v>6744</v>
+        <v>6422</v>
       </c>
       <c r="AC147" s="3" t="n">
         <v>111381</v>
@@ -18164,10 +18164,10 @@
         <v>0</v>
       </c>
       <c r="AA148" s="3" t="n">
-        <v>704</v>
+        <v>414</v>
       </c>
       <c r="AB148" s="3" t="n">
-        <v>1924</v>
+        <v>1800</v>
       </c>
       <c r="AC148" s="3" t="n">
         <v>116928</v>
@@ -18268,16 +18268,16 @@
         <v>0.002226</v>
       </c>
       <c r="Y149" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z149" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AA149" s="3" t="n">
-        <v>2856</v>
+        <v>2019</v>
       </c>
       <c r="AB149" s="3" t="n">
-        <v>668</v>
+        <v>613</v>
       </c>
       <c r="AC149" s="3" t="n">
         <v>93034</v>
@@ -18384,10 +18384,10 @@
         <v>2.2e-05</v>
       </c>
       <c r="AA150" s="3" t="n">
-        <v>8054</v>
+        <v>7278</v>
       </c>
       <c r="AB150" s="3" t="n">
-        <v>2646</v>
+        <v>2463</v>
       </c>
       <c r="AC150" s="3" t="n">
         <v>94693</v>
@@ -18494,10 +18494,10 @@
         <v>0</v>
       </c>
       <c r="AA151" s="3" t="n">
-        <v>1662</v>
+        <v>1138</v>
       </c>
       <c r="AB151" s="3" t="n">
-        <v>959</v>
+        <v>922</v>
       </c>
       <c r="AC151" s="3" t="n">
         <v>93168</v>
@@ -18604,10 +18604,10 @@
         <v>0</v>
       </c>
       <c r="AA152" s="3" t="n">
-        <v>2838</v>
+        <v>2238</v>
       </c>
       <c r="AB152" s="3" t="n">
-        <v>554</v>
+        <v>521</v>
       </c>
       <c r="AC152" s="3" t="n">
         <v>70575</v>
@@ -18708,16 +18708,16 @@
         <v>0.002399</v>
       </c>
       <c r="Y153" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z153" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA153" s="3" t="n">
-        <v>2916</v>
+        <v>2222</v>
       </c>
       <c r="AB153" s="3" t="n">
-        <v>1196</v>
+        <v>1143</v>
       </c>
       <c r="AC153" s="3" t="n">
         <v>81086</v>
@@ -18824,10 +18824,10 @@
         <v>0</v>
       </c>
       <c r="AA154" s="3" t="n">
-        <v>3166</v>
+        <v>2516</v>
       </c>
       <c r="AB154" s="3" t="n">
-        <v>2741</v>
+        <v>2621</v>
       </c>
       <c r="AC154" s="3" t="n">
         <v>140340</v>
@@ -18934,10 +18934,10 @@
         <v>0</v>
       </c>
       <c r="AA155" s="3" t="n">
-        <v>1121</v>
+        <v>845</v>
       </c>
       <c r="AB155" s="3" t="n">
-        <v>1316</v>
+        <v>1246</v>
       </c>
       <c r="AC155" s="3" t="n">
         <v>91863</v>
@@ -19038,16 +19038,16 @@
         <v>0.002351</v>
       </c>
       <c r="Y156" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z156" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AA156" s="3" t="n">
-        <v>1967</v>
+        <v>1490</v>
       </c>
       <c r="AB156" s="3" t="n">
-        <v>653</v>
+        <v>625</v>
       </c>
       <c r="AC156" s="3" t="n">
         <v>92961</v>
@@ -19154,10 +19154,10 @@
         <v>0</v>
       </c>
       <c r="AA157" s="3" t="n">
-        <v>5494</v>
+        <v>4722</v>
       </c>
       <c r="AB157" s="3" t="n">
-        <v>5766</v>
+        <v>5408</v>
       </c>
       <c r="AC157" s="3" t="n">
         <v>100593</v>
@@ -19264,10 +19264,10 @@
         <v>0</v>
       </c>
       <c r="AA158" s="3" t="n">
-        <v>609</v>
+        <v>379</v>
       </c>
       <c r="AB158" s="3" t="n">
-        <v>2369</v>
+        <v>2175</v>
       </c>
       <c r="AC158" s="3" t="n">
         <v>49759</v>
@@ -19374,10 +19374,10 @@
         <v>0</v>
       </c>
       <c r="AA159" s="3" t="n">
-        <v>6112</v>
+        <v>4884</v>
       </c>
       <c r="AB159" s="3" t="n">
-        <v>3276</v>
+        <v>2945</v>
       </c>
       <c r="AC159" s="3" t="n">
         <v>129180</v>
@@ -19478,16 +19478,16 @@
         <v>0.001886</v>
       </c>
       <c r="Y160" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z160" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA160" s="3" t="n">
-        <v>1626</v>
+        <v>1043</v>
       </c>
       <c r="AB160" s="3" t="n">
-        <v>1238</v>
+        <v>1165</v>
       </c>
       <c r="AC160" s="3" t="n">
         <v>126695</v>
@@ -19594,10 +19594,10 @@
         <v>0</v>
       </c>
       <c r="AA161" s="3" t="n">
-        <v>796</v>
+        <v>583</v>
       </c>
       <c r="AB161" s="3" t="n">
-        <v>712</v>
+        <v>666</v>
       </c>
       <c r="AC161" s="3" t="n">
         <v>74518</v>
@@ -19698,16 +19698,16 @@
         <v>0.002359</v>
       </c>
       <c r="Y162" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z162" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA162" s="3" t="n">
-        <v>1949</v>
+        <v>1798</v>
       </c>
       <c r="AB162" s="3" t="n">
-        <v>705</v>
+        <v>656</v>
       </c>
       <c r="AC162" s="3" t="n">
         <v>83749</v>
@@ -19814,10 +19814,10 @@
         <v>0</v>
       </c>
       <c r="AA163" s="3" t="n">
-        <v>1844</v>
+        <v>1586</v>
       </c>
       <c r="AB163" s="3" t="n">
-        <v>990</v>
+        <v>888</v>
       </c>
       <c r="AC163" s="3" t="n">
         <v>79850</v>
@@ -19924,10 +19924,10 @@
         <v>0</v>
       </c>
       <c r="AA164" s="3" t="n">
-        <v>5986</v>
+        <v>5173</v>
       </c>
       <c r="AB164" s="3" t="n">
-        <v>3523</v>
+        <v>3366</v>
       </c>
       <c r="AC164" s="3" t="n">
         <v>89170</v>
@@ -20031,13 +20031,13 @@
         <v>0</v>
       </c>
       <c r="Z165" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA165" s="3" t="n">
-        <v>1727</v>
+        <v>1216</v>
       </c>
       <c r="AB165" s="3" t="n">
-        <v>3090</v>
+        <v>2840</v>
       </c>
       <c r="AC165" s="3" t="n">
         <v>134213</v>
@@ -20141,13 +20141,13 @@
         <v>0</v>
       </c>
       <c r="Z166" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA166" s="3" t="n">
-        <v>284</v>
+        <v>198</v>
       </c>
       <c r="AB166" s="3" t="n">
-        <v>375</v>
+        <v>342</v>
       </c>
       <c r="AC166" s="3" t="n">
         <v>72696</v>
@@ -20254,10 +20254,10 @@
         <v>0</v>
       </c>
       <c r="AA167" s="3" t="n">
-        <v>2464</v>
+        <v>1898</v>
       </c>
       <c r="AB167" s="3" t="n">
-        <v>635</v>
+        <v>573</v>
       </c>
       <c r="AC167" s="3" t="n">
         <v>64011</v>
@@ -20364,10 +20364,10 @@
         <v>0</v>
       </c>
       <c r="AA168" s="3" t="n">
-        <v>1141</v>
+        <v>891</v>
       </c>
       <c r="AB168" s="3" t="n">
-        <v>730</v>
+        <v>680</v>
       </c>
       <c r="AC168" s="3" t="n">
         <v>74109</v>
@@ -20474,10 +20474,10 @@
         <v>0</v>
       </c>
       <c r="AA169" s="3" t="n">
-        <v>1147</v>
+        <v>962</v>
       </c>
       <c r="AB169" s="3" t="n">
-        <v>905</v>
+        <v>833</v>
       </c>
       <c r="AC169" s="3" t="n">
         <v>62895</v>
@@ -20578,16 +20578,16 @@
         <v>0.002054</v>
       </c>
       <c r="Y170" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z170" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA170" s="3" t="n">
-        <v>1712</v>
+        <v>1421</v>
       </c>
       <c r="AB170" s="3" t="n">
-        <v>1635</v>
+        <v>1573</v>
       </c>
       <c r="AC170" s="3" t="n">
         <v>134858</v>
@@ -20694,10 +20694,10 @@
         <v>0</v>
       </c>
       <c r="AA171" s="3" t="n">
-        <v>2411</v>
+        <v>1950</v>
       </c>
       <c r="AB171" s="3" t="n">
-        <v>1196</v>
+        <v>1127</v>
       </c>
       <c r="AC171" s="3" t="n">
         <v>50587</v>
@@ -20798,16 +20798,16 @@
         <v>0.002328</v>
       </c>
       <c r="Y172" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z172" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA172" s="3" t="n">
-        <v>1267</v>
+        <v>1038</v>
       </c>
       <c r="AB172" s="3" t="n">
-        <v>441</v>
+        <v>422</v>
       </c>
       <c r="AC172" s="3" t="n">
         <v>45598</v>
@@ -20914,10 +20914,10 @@
         <v>0</v>
       </c>
       <c r="AA173" s="3" t="n">
-        <v>1316</v>
+        <v>1054</v>
       </c>
       <c r="AB173" s="3" t="n">
-        <v>1163</v>
+        <v>1009</v>
       </c>
       <c r="AC173" s="3" t="n">
         <v>108026</v>
@@ -21024,10 +21024,10 @@
         <v>0</v>
       </c>
       <c r="AA174" s="3" t="n">
-        <v>7221</v>
+        <v>6450</v>
       </c>
       <c r="AB174" s="3" t="n">
-        <v>2655</v>
+        <v>2428</v>
       </c>
       <c r="AC174" s="3" t="n">
         <v>92508</v>
@@ -21134,10 +21134,10 @@
         <v>0</v>
       </c>
       <c r="AA175" s="3" t="n">
-        <v>1957</v>
+        <v>1591</v>
       </c>
       <c r="AB175" s="3" t="n">
-        <v>1783</v>
+        <v>1709</v>
       </c>
       <c r="AC175" s="3" t="n">
         <v>118978</v>
@@ -21244,10 +21244,10 @@
         <v>0</v>
       </c>
       <c r="AA176" s="3" t="n">
-        <v>1209</v>
+        <v>981</v>
       </c>
       <c r="AB176" s="3" t="n">
-        <v>827</v>
+        <v>773</v>
       </c>
       <c r="AC176" s="3" t="n">
         <v>84737</v>
@@ -21348,16 +21348,16 @@
         <v>0.002421</v>
       </c>
       <c r="Y177" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z177" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA177" s="3" t="n">
-        <v>857</v>
+        <v>645</v>
       </c>
       <c r="AB177" s="3" t="n">
-        <v>424</v>
+        <v>390</v>
       </c>
       <c r="AC177" s="3" t="n">
         <v>62421</v>
@@ -21458,16 +21458,16 @@
         <v>0.00214</v>
       </c>
       <c r="Y178" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z178" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA178" s="3" t="n">
-        <v>1559</v>
+        <v>1243</v>
       </c>
       <c r="AB178" s="3" t="n">
-        <v>623</v>
+        <v>584</v>
       </c>
       <c r="AC178" s="3" t="n">
         <v>60461</v>
@@ -21574,10 +21574,10 @@
         <v>0</v>
       </c>
       <c r="AA179" s="3" t="n">
-        <v>5398</v>
+        <v>4956</v>
       </c>
       <c r="AB179" s="3" t="n">
-        <v>5575</v>
+        <v>5202</v>
       </c>
       <c r="AC179" s="3" t="n">
         <v>103555</v>
@@ -21684,10 +21684,10 @@
         <v>0</v>
       </c>
       <c r="AA180" s="3" t="n">
-        <v>691</v>
+        <v>538</v>
       </c>
       <c r="AB180" s="3" t="n">
-        <v>787</v>
+        <v>738</v>
       </c>
       <c r="AC180" s="3" t="n">
         <v>101204</v>
@@ -21794,10 +21794,10 @@
         <v>0</v>
       </c>
       <c r="AA181" s="3" t="n">
-        <v>3769</v>
+        <v>3122</v>
       </c>
       <c r="AB181" s="3" t="n">
-        <v>527</v>
+        <v>475</v>
       </c>
       <c r="AC181" s="3" t="n">
         <v>55280</v>
@@ -21898,16 +21898,16 @@
         <v>0.002184</v>
       </c>
       <c r="Y182" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z182" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="Z182" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AA182" s="3" t="n">
-        <v>1727</v>
+        <v>1222</v>
       </c>
       <c r="AB182" s="3" t="n">
-        <v>977</v>
+        <v>922</v>
       </c>
       <c r="AC182" s="3" t="n">
         <v>78300</v>
@@ -22014,10 +22014,10 @@
         <v>-0</v>
       </c>
       <c r="AA183" s="3" t="n">
-        <v>1407</v>
+        <v>990</v>
       </c>
       <c r="AB183" s="3" t="n">
-        <v>931</v>
+        <v>849</v>
       </c>
       <c r="AC183" s="3" t="n">
         <v>96872</v>
@@ -22124,10 +22124,10 @@
         <v>0</v>
       </c>
       <c r="AA184" s="3" t="n">
-        <v>1085</v>
+        <v>913</v>
       </c>
       <c r="AB184" s="3" t="n">
-        <v>2976</v>
+        <v>2878</v>
       </c>
       <c r="AC184" s="3" t="n">
         <v>74782</v>
@@ -22228,16 +22228,16 @@
         <v>0.001842</v>
       </c>
       <c r="Y185" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z185" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA185" s="3" t="n">
-        <v>1124</v>
+        <v>806</v>
       </c>
       <c r="AB185" s="3" t="n">
-        <v>2118</v>
+        <v>1954</v>
       </c>
       <c r="AC185" s="3" t="n">
         <v>136683</v>
@@ -22344,10 +22344,10 @@
         <v>0</v>
       </c>
       <c r="AA186" s="3" t="n">
-        <v>1315</v>
+        <v>1158</v>
       </c>
       <c r="AB186" s="3" t="n">
-        <v>1526</v>
+        <v>1454</v>
       </c>
       <c r="AC186" s="3" t="n">
         <v>75683</v>
@@ -22454,10 +22454,10 @@
         <v>0</v>
       </c>
       <c r="AA187" s="3" t="n">
-        <v>1395</v>
+        <v>1119</v>
       </c>
       <c r="AB187" s="3" t="n">
-        <v>1873</v>
+        <v>1725</v>
       </c>
       <c r="AC187" s="3" t="n">
         <v>90787</v>
@@ -22564,10 +22564,10 @@
         <v>0</v>
       </c>
       <c r="AA188" s="3" t="n">
-        <v>902</v>
+        <v>802</v>
       </c>
       <c r="AB188" s="3" t="n">
-        <v>968</v>
+        <v>916</v>
       </c>
       <c r="AC188" s="3" t="n">
         <v>100854</v>
@@ -22674,10 +22674,10 @@
         <v>0</v>
       </c>
       <c r="AA189" s="3" t="n">
-        <v>1846</v>
+        <v>1453</v>
       </c>
       <c r="AB189" s="3" t="n">
-        <v>1020</v>
+        <v>986</v>
       </c>
       <c r="AC189" s="3" t="n">
         <v>47371</v>
@@ -22784,10 +22784,10 @@
         <v>0</v>
       </c>
       <c r="AA190" s="3" t="n">
-        <v>987</v>
+        <v>857</v>
       </c>
       <c r="AB190" s="3" t="n">
-        <v>860</v>
+        <v>805</v>
       </c>
       <c r="AC190" s="3" t="n">
         <v>87150</v>
@@ -22894,10 +22894,10 @@
         <v>0</v>
       </c>
       <c r="AA191" s="3" t="n">
-        <v>1858</v>
+        <v>1592</v>
       </c>
       <c r="AB191" s="3" t="n">
-        <v>1022</v>
+        <v>957</v>
       </c>
       <c r="AC191" s="3" t="n">
         <v>91821</v>
@@ -23004,10 +23004,10 @@
         <v>0</v>
       </c>
       <c r="AA192" s="3" t="n">
-        <v>963</v>
+        <v>824</v>
       </c>
       <c r="AB192" s="3" t="n">
-        <v>426</v>
+        <v>406</v>
       </c>
       <c r="AC192" s="3" t="n">
         <v>60331</v>
@@ -23111,13 +23111,13 @@
         <v>0</v>
       </c>
       <c r="Z193" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA193" s="3" t="n">
-        <v>1460</v>
+        <v>1221</v>
       </c>
       <c r="AB193" s="3" t="n">
-        <v>1734</v>
+        <v>1551</v>
       </c>
       <c r="AC193" s="3" t="n">
         <v>92026</v>
@@ -23224,10 +23224,10 @@
         <v>0</v>
       </c>
       <c r="AA194" s="3" t="n">
-        <v>1815</v>
+        <v>1425</v>
       </c>
       <c r="AB194" s="3" t="n">
-        <v>529</v>
+        <v>500</v>
       </c>
       <c r="AC194" s="3" t="n">
         <v>68724</v>
@@ -23334,10 +23334,10 @@
         <v>0</v>
       </c>
       <c r="AA195" s="3" t="n">
-        <v>2189</v>
+        <v>1891</v>
       </c>
       <c r="AB195" s="3" t="n">
-        <v>668</v>
+        <v>620</v>
       </c>
       <c r="AC195" s="3" t="n">
         <v>56642</v>
@@ -23444,10 +23444,10 @@
         <v>0</v>
       </c>
       <c r="AA196" s="3" t="n">
-        <v>3241</v>
+        <v>2760</v>
       </c>
       <c r="AB196" s="3" t="n">
-        <v>652</v>
+        <v>569</v>
       </c>
       <c r="AC196" s="3" t="n">
         <v>51170</v>
@@ -23554,10 +23554,10 @@
         <v>0</v>
       </c>
       <c r="AA197" s="3" t="n">
-        <v>484</v>
+        <v>387</v>
       </c>
       <c r="AB197" s="3" t="n">
-        <v>1284</v>
+        <v>1158</v>
       </c>
       <c r="AC197" s="3" t="n">
         <v>43733</v>
@@ -23664,10 +23664,10 @@
         <v>0</v>
       </c>
       <c r="AA198" s="3" t="n">
-        <v>1446</v>
+        <v>886</v>
       </c>
       <c r="AB198" s="3" t="n">
-        <v>692</v>
+        <v>644</v>
       </c>
       <c r="AC198" s="3" t="n">
         <v>70658</v>
@@ -23774,10 +23774,10 @@
         <v>0</v>
       </c>
       <c r="AA199" s="3" t="n">
-        <v>780</v>
+        <v>678</v>
       </c>
       <c r="AB199" s="3" t="n">
-        <v>369</v>
+        <v>346</v>
       </c>
       <c r="AC199" s="3" t="n">
         <v>65338</v>
@@ -23884,10 +23884,10 @@
         <v>0</v>
       </c>
       <c r="AA200" s="3" t="n">
-        <v>3840</v>
+        <v>3437</v>
       </c>
       <c r="AB200" s="3" t="n">
-        <v>4049</v>
+        <v>3869</v>
       </c>
       <c r="AC200" s="3" t="n">
         <v>79248</v>
@@ -23988,16 +23988,16 @@
         <v>0.001915</v>
       </c>
       <c r="Y201" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z201" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA201" s="3" t="n">
-        <v>1550</v>
+        <v>1194</v>
       </c>
       <c r="AB201" s="3" t="n">
-        <v>761</v>
+        <v>715</v>
       </c>
       <c r="AC201" s="3" t="n">
         <v>128199</v>
@@ -24104,10 +24104,10 @@
         <v>0</v>
       </c>
       <c r="AA202" s="3" t="n">
-        <v>1086</v>
+        <v>909</v>
       </c>
       <c r="AB202" s="3" t="n">
-        <v>766</v>
+        <v>704</v>
       </c>
       <c r="AC202" s="3" t="n">
         <v>74745</v>
@@ -24214,10 +24214,10 @@
         <v>0</v>
       </c>
       <c r="AA203" s="3" t="n">
-        <v>1654</v>
+        <v>1320</v>
       </c>
       <c r="AB203" s="3" t="n">
-        <v>951</v>
+        <v>889</v>
       </c>
       <c r="AC203" s="3" t="n">
         <v>66487</v>
@@ -24324,10 +24324,10 @@
         <v>5e-06</v>
       </c>
       <c r="AA204" s="3" t="n">
-        <v>5512</v>
+        <v>4986</v>
       </c>
       <c r="AB204" s="3" t="n">
-        <v>3394</v>
+        <v>3205</v>
       </c>
       <c r="AC204" s="3" t="n">
         <v>73611</v>
@@ -24434,10 +24434,10 @@
         <v>0</v>
       </c>
       <c r="AA205" s="3" t="n">
-        <v>952</v>
+        <v>771</v>
       </c>
       <c r="AB205" s="3" t="n">
-        <v>1489</v>
+        <v>1444</v>
       </c>
       <c r="AC205" s="3" t="n">
         <v>91933</v>
@@ -24538,16 +24538,16 @@
         <v>0.002033</v>
       </c>
       <c r="Y206" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z206" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA206" s="3" t="n">
-        <v>1846</v>
+        <v>1431</v>
       </c>
       <c r="AB206" s="3" t="n">
-        <v>928</v>
+        <v>857</v>
       </c>
       <c r="AC206" s="3" t="n">
         <v>75705</v>
@@ -24654,10 +24654,10 @@
         <v>0</v>
       </c>
       <c r="AA207" s="3" t="n">
-        <v>1057</v>
+        <v>912</v>
       </c>
       <c r="AB207" s="3" t="n">
-        <v>545</v>
+        <v>530</v>
       </c>
       <c r="AC207" s="3" t="n">
         <v>88701</v>
@@ -24764,10 +24764,10 @@
         <v>0</v>
       </c>
       <c r="AA208" s="3" t="n">
-        <v>3110</v>
+        <v>2547</v>
       </c>
       <c r="AB208" s="3" t="n">
-        <v>938</v>
+        <v>901</v>
       </c>
       <c r="AC208" s="3" t="n">
         <v>34605</v>
@@ -24874,10 +24874,10 @@
         <v>0</v>
       </c>
       <c r="AA209" s="3" t="n">
-        <v>1413</v>
+        <v>1138</v>
       </c>
       <c r="AB209" s="3" t="n">
-        <v>1065</v>
+        <v>1036</v>
       </c>
       <c r="AC209" s="3" t="n">
         <v>70248</v>
@@ -24984,10 +24984,10 @@
         <v>0</v>
       </c>
       <c r="AA210" s="3" t="n">
-        <v>855</v>
+        <v>525</v>
       </c>
       <c r="AB210" s="3" t="n">
-        <v>555</v>
+        <v>505</v>
       </c>
       <c r="AC210" s="3" t="n">
         <v>54199</v>
@@ -25088,16 +25088,16 @@
         <v>0.002032</v>
       </c>
       <c r="Y211" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z211" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AA211" s="3" t="n">
-        <v>1359</v>
+        <v>936</v>
       </c>
       <c r="AB211" s="3" t="n">
-        <v>455</v>
+        <v>432</v>
       </c>
       <c r="AC211" s="3" t="n">
         <v>63555</v>
@@ -25198,16 +25198,16 @@
         <v>0.001965</v>
       </c>
       <c r="Y212" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z212" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AA212" s="3" t="n">
-        <v>3507</v>
+        <v>2579</v>
       </c>
       <c r="AB212" s="3" t="n">
-        <v>1052</v>
+        <v>953</v>
       </c>
       <c r="AC212" s="3" t="n">
         <v>71665</v>
@@ -25314,10 +25314,10 @@
         <v>0</v>
       </c>
       <c r="AA213" s="3" t="n">
-        <v>3049</v>
+        <v>2322</v>
       </c>
       <c r="AB213" s="3" t="n">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="AC213" s="3" t="n">
         <v>68367</v>
@@ -25424,10 +25424,10 @@
         <v>0</v>
       </c>
       <c r="AA214" s="3" t="n">
-        <v>720</v>
+        <v>624</v>
       </c>
       <c r="AB214" s="3" t="n">
-        <v>1095</v>
+        <v>1047</v>
       </c>
       <c r="AC214" s="3" t="n">
         <v>84567</v>
@@ -25534,10 +25534,10 @@
         <v>0</v>
       </c>
       <c r="AA215" s="3" t="n">
-        <v>2159</v>
+        <v>1556</v>
       </c>
       <c r="AB215" s="3" t="n">
-        <v>606</v>
+        <v>573</v>
       </c>
       <c r="AC215" s="3" t="n">
         <v>69673</v>
@@ -25641,13 +25641,13 @@
         <v>0</v>
       </c>
       <c r="Z216" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA216" s="3" t="n">
-        <v>1816</v>
+        <v>1470</v>
       </c>
       <c r="AB216" s="3" t="n">
-        <v>1221</v>
+        <v>1166</v>
       </c>
       <c r="AC216" s="3" t="n">
         <v>63703</v>
@@ -25754,10 +25754,10 @@
         <v>0</v>
       </c>
       <c r="AA217" s="3" t="n">
-        <v>572</v>
+        <v>504</v>
       </c>
       <c r="AB217" s="3" t="n">
-        <v>2789</v>
+        <v>2644</v>
       </c>
       <c r="AC217" s="3" t="n">
         <v>43709</v>
@@ -25858,16 +25858,16 @@
         <v>0.001997</v>
       </c>
       <c r="Y218" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z218" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="AA218" s="3" t="n">
-        <v>1537</v>
+        <v>1283</v>
       </c>
       <c r="AB218" s="3" t="n">
-        <v>1084</v>
+        <v>1011</v>
       </c>
       <c r="AC218" s="3" t="n">
         <v>97317</v>
@@ -25974,10 +25974,10 @@
         <v>0</v>
       </c>
       <c r="AA219" s="3" t="n">
-        <v>759</v>
+        <v>658</v>
       </c>
       <c r="AB219" s="3" t="n">
-        <v>660</v>
+        <v>636</v>
       </c>
       <c r="AC219" s="3" t="n">
         <v>58675</v>
@@ -26084,10 +26084,10 @@
         <v>0</v>
       </c>
       <c r="AA220" s="3" t="n">
-        <v>2672</v>
+        <v>2023</v>
       </c>
       <c r="AB220" s="3" t="n">
-        <v>927</v>
+        <v>888</v>
       </c>
       <c r="AC220" s="3" t="n">
         <v>53387</v>
@@ -26188,16 +26188,16 @@
         <v>0.001669</v>
       </c>
       <c r="Y221" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z221" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA221" s="3" t="n">
-        <v>870</v>
+        <v>646</v>
       </c>
       <c r="AB221" s="3" t="n">
-        <v>1509</v>
+        <v>1440</v>
       </c>
       <c r="AC221" s="3" t="n">
         <v>104437</v>
@@ -26304,10 +26304,10 @@
         <v>0</v>
       </c>
       <c r="AA222" s="3" t="n">
-        <v>535</v>
+        <v>416</v>
       </c>
       <c r="AB222" s="3" t="n">
-        <v>1768</v>
+        <v>1711</v>
       </c>
       <c r="AC222" s="3" t="n">
         <v>68283</v>
@@ -26408,16 +26408,16 @@
         <v>0.001956</v>
       </c>
       <c r="Y223" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z223" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA223" s="3" t="n">
-        <v>2206</v>
+        <v>1671</v>
       </c>
       <c r="AB223" s="3" t="n">
-        <v>920</v>
+        <v>798</v>
       </c>
       <c r="AC223" s="3" t="n">
         <v>62984</v>
@@ -26524,10 +26524,10 @@
         <v>0</v>
       </c>
       <c r="AA224" s="3" t="n">
-        <v>1743</v>
+        <v>1231</v>
       </c>
       <c r="AB224" s="3" t="n">
-        <v>494</v>
+        <v>457</v>
       </c>
       <c r="AC224" s="3" t="n">
         <v>82993</v>
@@ -26634,10 +26634,10 @@
         <v>0</v>
       </c>
       <c r="AA225" s="3" t="n">
-        <v>981</v>
+        <v>676</v>
       </c>
       <c r="AB225" s="3" t="n">
-        <v>779</v>
+        <v>715</v>
       </c>
       <c r="AC225" s="3" t="n">
         <v>75153</v>
@@ -26738,16 +26738,16 @@
         <v>0.001914</v>
       </c>
       <c r="Y226" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z226" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA226" s="3" t="n">
-        <v>2347</v>
+        <v>1786</v>
       </c>
       <c r="AB226" s="3" t="n">
-        <v>682</v>
+        <v>643</v>
       </c>
       <c r="AC226" s="3" t="n">
         <v>64779</v>
@@ -26854,10 +26854,10 @@
         <v>0</v>
       </c>
       <c r="AA227" s="3" t="n">
-        <v>2201</v>
+        <v>1707</v>
       </c>
       <c r="AB227" s="3" t="n">
-        <v>584</v>
+        <v>539</v>
       </c>
       <c r="AC227" s="3" t="n">
         <v>62172</v>
@@ -26964,10 +26964,10 @@
         <v>0</v>
       </c>
       <c r="AA228" s="3" t="n">
-        <v>1862</v>
+        <v>1332</v>
       </c>
       <c r="AB228" s="3" t="n">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="AC228" s="3" t="n">
         <v>67491</v>
@@ -27074,10 +27074,10 @@
         <v>0</v>
       </c>
       <c r="AA229" s="3" t="n">
-        <v>2307</v>
+        <v>1988</v>
       </c>
       <c r="AB229" s="3" t="n">
-        <v>3900</v>
+        <v>3646</v>
       </c>
       <c r="AC229" s="3" t="n">
         <v>65546</v>
@@ -27184,10 +27184,10 @@
         <v>0</v>
       </c>
       <c r="AA230" s="3" t="n">
-        <v>2735</v>
+        <v>2324</v>
       </c>
       <c r="AB230" s="3" t="n">
-        <v>1637</v>
+        <v>1561</v>
       </c>
       <c r="AC230" s="3" t="n">
         <v>54773</v>
@@ -27288,16 +27288,16 @@
         <v>0.001953</v>
       </c>
       <c r="Y231" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z231" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA231" s="3" t="n">
-        <v>1481</v>
+        <v>1018</v>
       </c>
       <c r="AB231" s="3" t="n">
-        <v>1297</v>
+        <v>1208</v>
       </c>
       <c r="AC231" s="3" t="n">
         <v>68993</v>
@@ -27401,13 +27401,13 @@
         <v>0</v>
       </c>
       <c r="Z232" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA232" s="3" t="n">
-        <v>1390</v>
+        <v>1072</v>
       </c>
       <c r="AB232" s="3" t="n">
-        <v>874</v>
+        <v>818</v>
       </c>
       <c r="AC232" s="3" t="n">
         <v>73112</v>
@@ -27514,10 +27514,10 @@
         <v>0</v>
       </c>
       <c r="AA233" s="3" t="n">
-        <v>1699</v>
+        <v>1489</v>
       </c>
       <c r="AB233" s="3" t="n">
-        <v>3247</v>
+        <v>3078</v>
       </c>
       <c r="AC233" s="3" t="n">
         <v>69164</v>
@@ -27624,10 +27624,10 @@
         <v>0</v>
       </c>
       <c r="AA234" s="3" t="n">
-        <v>692</v>
+        <v>484</v>
       </c>
       <c r="AB234" s="3" t="n">
-        <v>1569</v>
+        <v>1456</v>
       </c>
       <c r="AC234" s="3" t="n">
         <v>78132</v>
@@ -27728,16 +27728,16 @@
         <v>0.001785</v>
       </c>
       <c r="Y235" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z235" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AA235" s="3" t="n">
-        <v>1929</v>
+        <v>1325</v>
       </c>
       <c r="AB235" s="3" t="n">
-        <v>617</v>
+        <v>555</v>
       </c>
       <c r="AC235" s="3" t="n">
         <v>77927</v>
@@ -27844,10 +27844,10 @@
         <v>0</v>
       </c>
       <c r="AA236" s="3" t="n">
-        <v>1275</v>
+        <v>1054</v>
       </c>
       <c r="AB236" s="3" t="n">
-        <v>527</v>
+        <v>501</v>
       </c>
       <c r="AC236" s="3" t="n">
         <v>52652</v>
@@ -27954,10 +27954,10 @@
         <v>0</v>
       </c>
       <c r="AA237" s="3" t="n">
-        <v>2894</v>
+        <v>2339</v>
       </c>
       <c r="AB237" s="3" t="n">
-        <v>2815</v>
+        <v>2699</v>
       </c>
       <c r="AC237" s="3" t="n">
         <v>113705</v>
@@ -28064,10 +28064,10 @@
         <v>0</v>
       </c>
       <c r="AA238" s="3" t="n">
-        <v>871</v>
+        <v>714</v>
       </c>
       <c r="AB238" s="3" t="n">
-        <v>639</v>
+        <v>611</v>
       </c>
       <c r="AC238" s="3" t="n">
         <v>57626</v>
@@ -28174,10 +28174,10 @@
         <v>0</v>
       </c>
       <c r="AA239" s="3" t="n">
-        <v>1996</v>
+        <v>1710</v>
       </c>
       <c r="AB239" s="3" t="n">
-        <v>408</v>
+        <v>372</v>
       </c>
       <c r="AC239" s="3" t="n">
         <v>39916</v>
@@ -28284,10 +28284,10 @@
         <v>0</v>
       </c>
       <c r="AA240" s="3" t="n">
-        <v>1611</v>
+        <v>1446</v>
       </c>
       <c r="AB240" s="3" t="n">
-        <v>866</v>
+        <v>814</v>
       </c>
       <c r="AC240" s="3" t="n">
         <v>43936</v>
@@ -28394,10 +28394,10 @@
         <v>0</v>
       </c>
       <c r="AA241" s="3" t="n">
-        <v>544</v>
+        <v>374</v>
       </c>
       <c r="AB241" s="3" t="n">
-        <v>1286</v>
+        <v>1219</v>
       </c>
       <c r="AC241" s="3" t="n">
         <v>71171</v>
@@ -28498,16 +28498,16 @@
         <v>0.001919</v>
       </c>
       <c r="Y242" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z242" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="AA242" s="3" t="n">
-        <v>552</v>
+        <v>374</v>
       </c>
       <c r="AB242" s="3" t="n">
-        <v>1098</v>
+        <v>974</v>
       </c>
       <c r="AC242" s="3" t="n">
         <v>66673</v>
@@ -28608,16 +28608,16 @@
         <v>0.001993</v>
       </c>
       <c r="Y243" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z243" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA243" s="3" t="n">
-        <v>1212</v>
+        <v>940</v>
       </c>
       <c r="AB243" s="3" t="n">
-        <v>543</v>
+        <v>501</v>
       </c>
       <c r="AC243" s="3" t="n">
         <v>61083</v>
@@ -28724,10 +28724,10 @@
         <v>0</v>
       </c>
       <c r="AA244" s="3" t="n">
-        <v>4141</v>
+        <v>3227</v>
       </c>
       <c r="AB244" s="3" t="n">
-        <v>605</v>
+        <v>504</v>
       </c>
       <c r="AC244" s="3" t="n">
         <v>60110</v>
@@ -28834,10 +28834,10 @@
         <v>0</v>
       </c>
       <c r="AA245" s="3" t="n">
-        <v>2071</v>
+        <v>1774</v>
       </c>
       <c r="AB245" s="3" t="n">
-        <v>5690</v>
+        <v>5200</v>
       </c>
       <c r="AC245" s="3" t="n">
         <v>78384</v>
@@ -28938,16 +28938,16 @@
         <v>0.001896</v>
       </c>
       <c r="Y246" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z246" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="AA246" s="3" t="n">
-        <v>941</v>
+        <v>744</v>
       </c>
       <c r="AB246" s="3" t="n">
-        <v>953</v>
+        <v>908</v>
       </c>
       <c r="AC246" s="3" t="n">
         <v>61371</v>
@@ -29054,10 +29054,10 @@
         <v>0</v>
       </c>
       <c r="AA247" s="3" t="n">
-        <v>5834</v>
+        <v>4652</v>
       </c>
       <c r="AB247" s="3" t="n">
-        <v>2261</v>
+        <v>2069</v>
       </c>
       <c r="AC247" s="3" t="n">
         <v>33739</v>
@@ -29164,10 +29164,10 @@
         <v>0</v>
       </c>
       <c r="AA248" s="3" t="n">
-        <v>1103</v>
+        <v>841</v>
       </c>
       <c r="AB248" s="3" t="n">
-        <v>543</v>
+        <v>509</v>
       </c>
       <c r="AC248" s="3" t="n">
         <v>91621</v>
@@ -29268,16 +29268,16 @@
         <v>0.001815</v>
       </c>
       <c r="Y249" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z249" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AA249" s="3" t="n">
-        <v>1523</v>
+        <v>1108</v>
       </c>
       <c r="AB249" s="3" t="n">
-        <v>446</v>
+        <v>401</v>
       </c>
       <c r="AC249" s="3" t="n">
         <v>59123</v>
@@ -29384,10 +29384,10 @@
         <v>0</v>
       </c>
       <c r="AA250" s="3" t="n">
-        <v>594</v>
+        <v>515</v>
       </c>
       <c r="AB250" s="3" t="n">
-        <v>961</v>
+        <v>884</v>
       </c>
       <c r="AC250" s="3" t="n">
         <v>77155</v>
@@ -29494,10 +29494,10 @@
         <v>-0</v>
       </c>
       <c r="AA251" s="3" t="n">
-        <v>348</v>
+        <v>169</v>
       </c>
       <c r="AB251" s="3" t="n">
-        <v>418</v>
+        <v>386</v>
       </c>
       <c r="AC251" s="3" t="n">
         <v>60145</v>
@@ -29598,16 +29598,16 @@
         <v>0.001608</v>
       </c>
       <c r="Y252" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z252" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AA252" s="3" t="n">
-        <v>1672</v>
+        <v>1250</v>
       </c>
       <c r="AB252" s="3" t="n">
-        <v>1417</v>
+        <v>1294</v>
       </c>
       <c r="AC252" s="3" t="n">
         <v>101685</v>
@@ -29714,10 +29714,10 @@
         <v>0</v>
       </c>
       <c r="AA253" s="3" t="n">
-        <v>1538</v>
+        <v>1195</v>
       </c>
       <c r="AB253" s="3" t="n">
-        <v>782</v>
+        <v>738</v>
       </c>
       <c r="AC253" s="3" t="n">
         <v>55330</v>
@@ -29821,13 +29821,13 @@
         <v>-0</v>
       </c>
       <c r="Z254" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA254" s="3" t="n">
-        <v>3118</v>
+        <v>2544</v>
       </c>
       <c r="AB254" s="3" t="n">
-        <v>796</v>
+        <v>753</v>
       </c>
       <c r="AC254" s="3" t="n">
         <v>83239</v>
@@ -29928,16 +29928,16 @@
         <v>0.001666</v>
       </c>
       <c r="Y255" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z255" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA255" s="3" t="n">
-        <v>2005</v>
+        <v>1345</v>
       </c>
       <c r="AB255" s="3" t="n">
-        <v>609</v>
+        <v>582</v>
       </c>
       <c r="AC255" s="3" t="n">
         <v>76021</v>
@@ -30038,16 +30038,16 @@
         <v>0.00163</v>
       </c>
       <c r="Y256" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z256" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA256" s="3" t="n">
-        <v>2337</v>
+        <v>1694</v>
       </c>
       <c r="AB256" s="3" t="n">
-        <v>1167</v>
+        <v>1122</v>
       </c>
       <c r="AC256" s="3" t="n">
         <v>86970</v>
@@ -30154,10 +30154,10 @@
         <v>0</v>
       </c>
       <c r="AA257" s="3" t="n">
-        <v>1259</v>
+        <v>1057</v>
       </c>
       <c r="AB257" s="3" t="n">
-        <v>2935</v>
+        <v>2639</v>
       </c>
       <c r="AC257" s="3" t="n">
         <v>79497</v>
@@ -30258,16 +30258,16 @@
         <v>0.00168</v>
       </c>
       <c r="Y258" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z258" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA258" s="3" t="n">
-        <v>1090</v>
+        <v>822</v>
       </c>
       <c r="AB258" s="3" t="n">
-        <v>1606</v>
+        <v>1525</v>
       </c>
       <c r="AC258" s="3" t="n">
         <v>55651</v>
@@ -30374,10 +30374,10 @@
         <v>0</v>
       </c>
       <c r="AA259" s="3" t="n">
-        <v>673</v>
+        <v>484</v>
       </c>
       <c r="AB259" s="3" t="n">
-        <v>430</v>
+        <v>401</v>
       </c>
       <c r="AC259" s="3" t="n">
         <v>59627</v>
@@ -30484,10 +30484,10 @@
         <v>0</v>
       </c>
       <c r="AA260" s="3" t="n">
-        <v>1315</v>
+        <v>1134</v>
       </c>
       <c r="AB260" s="3" t="n">
-        <v>1149</v>
+        <v>1072</v>
       </c>
       <c r="AC260" s="3" t="n">
         <v>64961</v>
@@ -30594,10 +30594,10 @@
         <v>0</v>
       </c>
       <c r="AA261" s="3" t="n">
-        <v>288</v>
+        <v>186</v>
       </c>
       <c r="AB261" s="3" t="n">
-        <v>548</v>
+        <v>458</v>
       </c>
       <c r="AC261" s="3" t="n">
         <v>54482</v>
@@ -30704,10 +30704,10 @@
         <v>0</v>
       </c>
       <c r="AA262" s="3" t="n">
-        <v>536</v>
+        <v>449</v>
       </c>
       <c r="AB262" s="3" t="n">
-        <v>490</v>
+        <v>432</v>
       </c>
       <c r="AC262" s="3" t="n">
         <v>42983</v>
@@ -30808,16 +30808,16 @@
         <v>0.001707</v>
       </c>
       <c r="Y263" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z263" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA263" s="3" t="n">
-        <v>745</v>
+        <v>535</v>
       </c>
       <c r="AB263" s="3" t="n">
-        <v>839</v>
+        <v>771</v>
       </c>
       <c r="AC263" s="3" t="n">
         <v>69534</v>
@@ -30924,10 +30924,10 @@
         <v>0</v>
       </c>
       <c r="AA264" s="3" t="n">
-        <v>477</v>
+        <v>409</v>
       </c>
       <c r="AB264" s="3" t="n">
-        <v>394</v>
+        <v>362</v>
       </c>
       <c r="AC264" s="3" t="n">
         <v>38005</v>
@@ -31028,16 +31028,16 @@
         <v>0.001646</v>
       </c>
       <c r="Y265" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z265" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA265" s="3" t="n">
-        <v>3450</v>
+        <v>2461</v>
       </c>
       <c r="AB265" s="3" t="n">
-        <v>826</v>
+        <v>748</v>
       </c>
       <c r="AC265" s="3" t="n">
         <v>61636</v>
@@ -31144,10 +31144,10 @@
         <v>0</v>
       </c>
       <c r="AA266" s="3" t="n">
-        <v>3225</v>
+        <v>2956</v>
       </c>
       <c r="AB266" s="3" t="n">
-        <v>2383</v>
+        <v>2175</v>
       </c>
       <c r="AC266" s="3" t="n">
         <v>39538</v>
@@ -31254,10 +31254,10 @@
         <v>0</v>
       </c>
       <c r="AA267" s="3" t="n">
-        <v>867</v>
+        <v>696</v>
       </c>
       <c r="AB267" s="3" t="n">
-        <v>1145</v>
+        <v>1056</v>
       </c>
       <c r="AC267" s="3" t="n">
         <v>59025</v>
@@ -31364,10 +31364,10 @@
         <v>0</v>
       </c>
       <c r="AA268" s="3" t="n">
-        <v>1537</v>
+        <v>1098</v>
       </c>
       <c r="AB268" s="3" t="n">
-        <v>921</v>
+        <v>820</v>
       </c>
       <c r="AC268" s="3" t="n">
         <v>62179</v>
@@ -31464,10 +31464,10 @@
         <v>0</v>
       </c>
       <c r="AA269" s="3" t="n">
-        <v>840</v>
+        <v>708</v>
       </c>
       <c r="AB269" s="3" t="n">
-        <v>538</v>
+        <v>483</v>
       </c>
       <c r="AC269" s="3" t="n">
         <v>36979</v>
@@ -31558,16 +31558,16 @@
         <v>0.001717</v>
       </c>
       <c r="Y270" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z270" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA270" s="3" t="n">
-        <v>1789</v>
+        <v>1501</v>
       </c>
       <c r="AB270" s="3" t="n">
-        <v>1032</v>
+        <v>997</v>
       </c>
       <c r="AC270" s="3" t="n">
         <v>60443</v>
@@ -31664,10 +31664,10 @@
         <v>0</v>
       </c>
       <c r="AA271" s="3" t="n">
-        <v>887</v>
+        <v>729</v>
       </c>
       <c r="AB271" s="3" t="n">
-        <v>577</v>
+        <v>540</v>
       </c>
       <c r="AC271" s="3" t="n">
         <v>46558</v>
@@ -31764,10 +31764,10 @@
         <v>0</v>
       </c>
       <c r="AA272" s="3" t="n">
-        <v>1174</v>
+        <v>1013</v>
       </c>
       <c r="AB272" s="3" t="n">
-        <v>1097</v>
+        <v>1033</v>
       </c>
       <c r="AC272" s="3" t="n">
         <v>70693</v>
@@ -31864,10 +31864,10 @@
         <v>0</v>
       </c>
       <c r="AA273" s="3" t="n">
-        <v>489</v>
+        <v>391</v>
       </c>
       <c r="AB273" s="3" t="n">
-        <v>584</v>
+        <v>541</v>
       </c>
       <c r="AC273" s="3" t="n">
         <v>57213</v>
@@ -31964,10 +31964,10 @@
         <v>0</v>
       </c>
       <c r="AA274" s="3" t="n">
-        <v>1359</v>
+        <v>969</v>
       </c>
       <c r="AB274" s="3" t="n">
-        <v>3351</v>
+        <v>3169</v>
       </c>
       <c r="AC274" s="3" t="n">
         <v>44505</v>
@@ -32064,10 +32064,10 @@
         <v>0</v>
       </c>
       <c r="AA275" s="3" t="n">
-        <v>1931</v>
+        <v>1694</v>
       </c>
       <c r="AB275" s="3" t="n">
-        <v>645</v>
+        <v>602</v>
       </c>
       <c r="AC275" s="3" t="n">
         <v>40995</v>
@@ -32164,10 +32164,10 @@
         <v>0.005486</v>
       </c>
       <c r="AA276" s="3" t="n">
-        <v>2294</v>
+        <v>1911</v>
       </c>
       <c r="AB276" s="3" t="n">
-        <v>1043</v>
+        <v>984</v>
       </c>
       <c r="AC276" s="3" t="n">
         <v>82908</v>
@@ -32264,10 +32264,10 @@
         <v>9e-06</v>
       </c>
       <c r="AA277" s="3" t="n">
-        <v>2918</v>
+        <v>2651</v>
       </c>
       <c r="AB277" s="3" t="n">
-        <v>2975</v>
+        <v>2805</v>
       </c>
       <c r="AC277" s="3" t="n">
         <v>47026</v>
@@ -32358,16 +32358,16 @@
         <v>0.001623</v>
       </c>
       <c r="Y278" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z278" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA278" s="3" t="n">
-        <v>1102</v>
+        <v>898</v>
       </c>
       <c r="AB278" s="3" t="n">
-        <v>635</v>
+        <v>594</v>
       </c>
       <c r="AC278" s="3" t="n">
         <v>67633</v>
@@ -32464,10 +32464,10 @@
         <v>0</v>
       </c>
       <c r="AA279" s="3" t="n">
-        <v>689</v>
+        <v>547</v>
       </c>
       <c r="AB279" s="3" t="n">
-        <v>1609</v>
+        <v>1476</v>
       </c>
       <c r="AC279" s="3" t="n">
         <v>87906</v>
@@ -32564,10 +32564,10 @@
         <v>0.00729</v>
       </c>
       <c r="AA280" s="3" t="n">
-        <v>4625</v>
+        <v>3967</v>
       </c>
       <c r="AB280" s="3" t="n">
-        <v>2269</v>
+        <v>2134</v>
       </c>
       <c r="AC280" s="3" t="n">
         <v>99588</v>
@@ -32664,10 +32664,10 @@
         <v>-0</v>
       </c>
       <c r="AA281" s="3" t="n">
-        <v>1622</v>
+        <v>1258</v>
       </c>
       <c r="AB281" s="3" t="n">
-        <v>1158</v>
+        <v>1070</v>
       </c>
       <c r="AC281" s="3" t="n">
         <v>72098</v>
@@ -32764,10 +32764,10 @@
         <v>0</v>
       </c>
       <c r="AA282" s="3" t="n">
-        <v>999</v>
+        <v>802</v>
       </c>
       <c r="AB282" s="3" t="n">
-        <v>415</v>
+        <v>391</v>
       </c>
       <c r="AC282" s="3" t="n">
         <v>55367</v>
@@ -32864,10 +32864,10 @@
         <v>0</v>
       </c>
       <c r="AA283" s="3" t="n">
-        <v>743</v>
+        <v>615</v>
       </c>
       <c r="AB283" s="3" t="n">
-        <v>1203</v>
+        <v>1114</v>
       </c>
       <c r="AC283" s="3" t="n">
         <v>80946</v>
@@ -32964,10 +32964,10 @@
         <v>0</v>
       </c>
       <c r="AA284" s="3" t="n">
-        <v>902</v>
+        <v>587</v>
       </c>
       <c r="AB284" s="3" t="n">
-        <v>1273</v>
+        <v>1187</v>
       </c>
       <c r="AC284" s="3" t="n">
         <v>88163</v>
@@ -33064,10 +33064,10 @@
         <v>0</v>
       </c>
       <c r="AA285" s="3" t="n">
-        <v>497</v>
+        <v>390</v>
       </c>
       <c r="AB285" s="3" t="n">
-        <v>728</v>
+        <v>674</v>
       </c>
       <c r="AC285" s="3" t="n">
         <v>63750</v>
@@ -33158,16 +33158,16 @@
         <v>0.001623</v>
       </c>
       <c r="Y286" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z286" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AA286" s="3" t="n">
-        <v>841</v>
+        <v>564</v>
       </c>
       <c r="AB286" s="3" t="n">
-        <v>757</v>
+        <v>701</v>
       </c>
       <c r="AC286" s="3" t="n">
         <v>68874</v>
@@ -33264,10 +33264,10 @@
         <v>0</v>
       </c>
       <c r="AA287" s="3" t="n">
-        <v>1960</v>
+        <v>1463</v>
       </c>
       <c r="AB287" s="3" t="n">
-        <v>443</v>
+        <v>408</v>
       </c>
       <c r="AC287" s="3" t="n">
         <v>39909</v>
@@ -33364,10 +33364,10 @@
         <v>0</v>
       </c>
       <c r="AA288" s="3" t="n">
-        <v>1615</v>
+        <v>1342</v>
       </c>
       <c r="AB288" s="3" t="n">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="AC288" s="3" t="n">
         <v>52585</v>
@@ -33464,10 +33464,10 @@
         <v>0</v>
       </c>
       <c r="AA289" s="3" t="n">
-        <v>313</v>
+        <v>245</v>
       </c>
       <c r="AB289" s="3" t="n">
-        <v>472</v>
+        <v>444</v>
       </c>
       <c r="AC289" s="3" t="n">
         <v>65922</v>
@@ -33564,10 +33564,10 @@
         <v>0</v>
       </c>
       <c r="AA290" s="3" t="n">
-        <v>1466</v>
+        <v>1121</v>
       </c>
       <c r="AB290" s="3" t="n">
-        <v>1484</v>
+        <v>1424</v>
       </c>
       <c r="AC290" s="3" t="n">
         <v>38083</v>
@@ -33664,10 +33664,10 @@
         <v>0</v>
       </c>
       <c r="AA291" s="3" t="n">
-        <v>3713</v>
+        <v>3034</v>
       </c>
       <c r="AB291" s="3" t="n">
-        <v>471</v>
+        <v>430</v>
       </c>
       <c r="AC291" s="3" t="n">
         <v>42174</v>
@@ -33764,10 +33764,10 @@
         <v>0</v>
       </c>
       <c r="AA292" s="3" t="n">
-        <v>786</v>
+        <v>603</v>
       </c>
       <c r="AB292" s="3" t="n">
-        <v>1339</v>
+        <v>1298</v>
       </c>
       <c r="AC292" s="3" t="n">
         <v>52905</v>
@@ -33864,10 +33864,10 @@
         <v>0.004628</v>
       </c>
       <c r="AA293" s="3" t="n">
-        <v>3348</v>
+        <v>2775</v>
       </c>
       <c r="AB293" s="3" t="n">
-        <v>3743</v>
+        <v>3406</v>
       </c>
       <c r="AC293" s="3" t="n">
         <v>86029</v>
@@ -33964,10 +33964,10 @@
         <v>0</v>
       </c>
       <c r="AA294" s="3" t="n">
-        <v>572</v>
+        <v>434</v>
       </c>
       <c r="AB294" s="3" t="n">
-        <v>1128</v>
+        <v>1032</v>
       </c>
       <c r="AC294" s="3" t="n">
         <v>56996</v>
@@ -34064,10 +34064,10 @@
         <v>0</v>
       </c>
       <c r="AA295" s="3" t="n">
-        <v>2825</v>
+        <v>2262</v>
       </c>
       <c r="AB295" s="3" t="n">
-        <v>520</v>
+        <v>472</v>
       </c>
       <c r="AC295" s="3" t="n">
         <v>43582</v>
@@ -34158,16 +34158,16 @@
         <v>0.001619</v>
       </c>
       <c r="Y296" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z296" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="AA296" s="3" t="n">
-        <v>916</v>
+        <v>734</v>
       </c>
       <c r="AB296" s="3" t="n">
-        <v>1012</v>
+        <v>973</v>
       </c>
       <c r="AC296" s="3" t="n">
         <v>47987</v>
@@ -34264,10 +34264,10 @@
         <v>0</v>
       </c>
       <c r="AA297" s="3" t="n">
-        <v>521</v>
+        <v>412</v>
       </c>
       <c r="AB297" s="3" t="n">
-        <v>485</v>
+        <v>463</v>
       </c>
       <c r="AC297" s="3" t="n">
         <v>69396</v>
@@ -34364,10 +34364,10 @@
         <v>0</v>
       </c>
       <c r="AA298" s="3" t="n">
-        <v>627</v>
+        <v>435</v>
       </c>
       <c r="AB298" s="3" t="n">
-        <v>784</v>
+        <v>730</v>
       </c>
       <c r="AC298" s="3" t="n">
         <v>48014</v>
@@ -34464,10 +34464,10 @@
         <v>0</v>
       </c>
       <c r="AA299" s="3" t="n">
-        <v>1436</v>
+        <v>1085</v>
       </c>
       <c r="AB299" s="3" t="n">
-        <v>409</v>
+        <v>362</v>
       </c>
       <c r="AC299" s="3" t="n">
         <v>47848</v>
@@ -34564,10 +34564,10 @@
         <v>0</v>
       </c>
       <c r="AA300" s="3" t="n">
-        <v>1455</v>
+        <v>1212</v>
       </c>
       <c r="AB300" s="3" t="n">
-        <v>3562</v>
+        <v>3421</v>
       </c>
       <c r="AC300" s="3" t="n">
         <v>40510</v>
@@ -34658,16 +34658,16 @@
         <v>0.001586</v>
       </c>
       <c r="Y301" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z301" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA301" s="3" t="n">
-        <v>1482</v>
+        <v>1123</v>
       </c>
       <c r="AB301" s="3" t="n">
-        <v>1048</v>
+        <v>1011</v>
       </c>
       <c r="AC301" s="3" t="n">
         <v>41421</v>
@@ -34764,10 +34764,10 @@
         <v>0.003494</v>
       </c>
       <c r="AA302" s="3" t="n">
-        <v>6019</v>
+        <v>5445</v>
       </c>
       <c r="AB302" s="3" t="n">
-        <v>3266</v>
+        <v>3113</v>
       </c>
       <c r="AC302" s="3" t="n">
         <v>54909</v>
@@ -34861,13 +34861,13 @@
         <v>0</v>
       </c>
       <c r="Z303" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA303" s="3" t="n">
-        <v>1844</v>
+        <v>1526</v>
       </c>
       <c r="AB303" s="3" t="n">
-        <v>956</v>
+        <v>896</v>
       </c>
       <c r="AC303" s="3" t="n">
         <v>45222</v>
@@ -34961,13 +34961,13 @@
         <v>0</v>
       </c>
       <c r="Z304" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA304" s="3" t="n">
-        <v>800</v>
+        <v>606</v>
       </c>
       <c r="AB304" s="3" t="n">
-        <v>801</v>
+        <v>773</v>
       </c>
       <c r="AC304" s="3" t="n">
         <v>55623</v>
@@ -35064,10 +35064,10 @@
         <v>0</v>
       </c>
       <c r="AA305" s="3" t="n">
-        <v>346</v>
+        <v>158</v>
       </c>
       <c r="AB305" s="3" t="n">
-        <v>2675</v>
+        <v>2530</v>
       </c>
       <c r="AC305" s="3" t="n">
         <v>48721</v>
@@ -35164,10 +35164,10 @@
         <v>0</v>
       </c>
       <c r="AA306" s="3" t="n">
-        <v>1358</v>
+        <v>1149</v>
       </c>
       <c r="AB306" s="3" t="n">
-        <v>1770</v>
+        <v>1671</v>
       </c>
       <c r="AC306" s="3" t="n">
         <v>46334</v>
@@ -35264,10 +35264,10 @@
         <v>0</v>
       </c>
       <c r="AA307" s="3" t="n">
-        <v>1829</v>
+        <v>1518</v>
       </c>
       <c r="AB307" s="3" t="n">
-        <v>644</v>
+        <v>596</v>
       </c>
       <c r="AC307" s="3" t="n">
         <v>77339</v>
@@ -35364,10 +35364,10 @@
         <v>0</v>
       </c>
       <c r="AA308" s="3" t="n">
-        <v>404</v>
+        <v>324</v>
       </c>
       <c r="AB308" s="3" t="n">
-        <v>567</v>
+        <v>513</v>
       </c>
       <c r="AC308" s="3" t="n">
         <v>47175</v>
@@ -35461,13 +35461,13 @@
         <v>0</v>
       </c>
       <c r="Z309" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA309" s="3" t="n">
-        <v>1535</v>
+        <v>1271</v>
       </c>
       <c r="AB309" s="3" t="n">
-        <v>1140</v>
+        <v>983</v>
       </c>
       <c r="AC309" s="3" t="n">
         <v>59415</v>
@@ -35564,10 +35564,10 @@
         <v>0</v>
       </c>
       <c r="AA310" s="3" t="n">
-        <v>778</v>
+        <v>611</v>
       </c>
       <c r="AB310" s="3" t="n">
-        <v>481</v>
+        <v>452</v>
       </c>
       <c r="AC310" s="3" t="n">
         <v>52021</v>
@@ -35658,16 +35658,16 @@
         <v>0.001535</v>
       </c>
       <c r="Y311" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z311" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA311" s="3" t="n">
-        <v>2054</v>
+        <v>1449</v>
       </c>
       <c r="AB311" s="3" t="n">
-        <v>555</v>
+        <v>494</v>
       </c>
       <c r="AC311" s="3" t="n">
         <v>53750</v>
@@ -35764,10 +35764,10 @@
         <v>0.008366999999999999</v>
       </c>
       <c r="AA312" s="3" t="n">
-        <v>3008</v>
+        <v>2554</v>
       </c>
       <c r="AB312" s="3" t="n">
-        <v>1591</v>
+        <v>1472</v>
       </c>
       <c r="AC312" s="3" t="n">
         <v>95059</v>
@@ -35864,10 +35864,10 @@
         <v>0</v>
       </c>
       <c r="AA313" s="3" t="n">
-        <v>627</v>
+        <v>485</v>
       </c>
       <c r="AB313" s="3" t="n">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="AC313" s="3" t="n">
         <v>51097</v>
@@ -35964,10 +35964,10 @@
         <v>4e-06</v>
       </c>
       <c r="AA314" s="3" t="n">
-        <v>1923</v>
+        <v>1559</v>
       </c>
       <c r="AB314" s="3" t="n">
-        <v>677</v>
+        <v>623</v>
       </c>
       <c r="AC314" s="3" t="n">
         <v>52529</v>
@@ -36064,10 +36064,10 @@
         <v>0</v>
       </c>
       <c r="AA315" s="3" t="n">
-        <v>941</v>
+        <v>708</v>
       </c>
       <c r="AB315" s="3" t="n">
-        <v>815</v>
+        <v>705</v>
       </c>
       <c r="AC315" s="3" t="n">
         <v>45453</v>
@@ -36158,16 +36158,16 @@
         <v>0.00142</v>
       </c>
       <c r="Y316" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z316" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AA316" s="3" t="n">
-        <v>877</v>
+        <v>668</v>
       </c>
       <c r="AB316" s="3" t="n">
-        <v>912</v>
+        <v>854</v>
       </c>
       <c r="AC316" s="3" t="n">
         <v>41042</v>
@@ -36264,10 +36264,10 @@
         <v>0</v>
       </c>
       <c r="AA317" s="3" t="n">
-        <v>1125</v>
+        <v>940</v>
       </c>
       <c r="AB317" s="3" t="n">
-        <v>749</v>
+        <v>665</v>
       </c>
       <c r="AC317" s="3" t="n">
         <v>72720</v>
@@ -36364,10 +36364,10 @@
         <v>0</v>
       </c>
       <c r="AA318" s="3" t="n">
-        <v>1150</v>
+        <v>913</v>
       </c>
       <c r="AB318" s="3" t="n">
-        <v>1464</v>
+        <v>1340</v>
       </c>
       <c r="AC318" s="3" t="n">
         <v>34432</v>
@@ -36464,10 +36464,10 @@
         <v>0</v>
       </c>
       <c r="AA319" s="3" t="n">
-        <v>3558</v>
+        <v>3075</v>
       </c>
       <c r="AB319" s="3" t="n">
-        <v>1425</v>
+        <v>1320</v>
       </c>
       <c r="AC319" s="3" t="n">
         <v>35418</v>
@@ -36564,10 +36564,10 @@
         <v>0</v>
       </c>
       <c r="AA320" s="3" t="n">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="AB320" s="3" t="n">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="AC320" s="3" t="n">
         <v>29697</v>
@@ -36664,10 +36664,10 @@
         <v>0</v>
       </c>
       <c r="AA321" s="3" t="n">
-        <v>569</v>
+        <v>495</v>
       </c>
       <c r="AB321" s="3" t="n">
-        <v>355</v>
+        <v>302</v>
       </c>
       <c r="AC321" s="3" t="n">
         <v>41715</v>
@@ -36764,10 +36764,10 @@
         <v>-0</v>
       </c>
       <c r="AA322" s="3" t="n">
-        <v>481</v>
+        <v>327</v>
       </c>
       <c r="AB322" s="3" t="n">
-        <v>768</v>
+        <v>722</v>
       </c>
       <c r="AC322" s="3" t="n">
         <v>56816</v>
@@ -36861,13 +36861,13 @@
         <v>0</v>
       </c>
       <c r="Z323" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA323" s="3" t="n">
-        <v>887</v>
+        <v>649</v>
       </c>
       <c r="AB323" s="3" t="n">
-        <v>799</v>
+        <v>740</v>
       </c>
       <c r="AC323" s="3" t="n">
         <v>70274</v>
@@ -36964,10 +36964,10 @@
         <v>0</v>
       </c>
       <c r="AA324" s="3" t="n">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="AB324" s="3" t="n">
-        <v>494</v>
+        <v>457</v>
       </c>
       <c r="AC324" s="3" t="n">
         <v>33998</v>
@@ -37064,10 +37064,10 @@
         <v>0</v>
       </c>
       <c r="AA325" s="3" t="n">
-        <v>1058</v>
+        <v>693</v>
       </c>
       <c r="AB325" s="3" t="n">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="AC325" s="3" t="n">
         <v>36599</v>
@@ -37164,10 +37164,10 @@
         <v>0</v>
       </c>
       <c r="AA326" s="3" t="n">
-        <v>669</v>
+        <v>574</v>
       </c>
       <c r="AB326" s="3" t="n">
-        <v>862</v>
+        <v>816</v>
       </c>
       <c r="AC326" s="3" t="n">
         <v>58667</v>
@@ -37264,10 +37264,10 @@
         <v>0.005951</v>
       </c>
       <c r="AA327" s="3" t="n">
-        <v>1307</v>
+        <v>1101</v>
       </c>
       <c r="AB327" s="3" t="n">
-        <v>2732</v>
+        <v>2594</v>
       </c>
       <c r="AC327" s="3" t="n">
         <v>82450</v>
@@ -37364,10 +37364,10 @@
         <v>0</v>
       </c>
       <c r="AA328" s="3" t="n">
-        <v>2839</v>
+        <v>2280</v>
       </c>
       <c r="AB328" s="3" t="n">
-        <v>564</v>
+        <v>503</v>
       </c>
       <c r="AC328" s="3" t="n">
         <v>27253</v>
@@ -37458,16 +37458,16 @@
         <v>0.001464</v>
       </c>
       <c r="Y329" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z329" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA329" s="3" t="n">
-        <v>1348</v>
+        <v>1113</v>
       </c>
       <c r="AB329" s="3" t="n">
-        <v>624</v>
+        <v>569</v>
       </c>
       <c r="AC329" s="3" t="n">
         <v>80276</v>
@@ -37564,10 +37564,10 @@
         <v>0.005432</v>
       </c>
       <c r="AA330" s="3" t="n">
-        <v>1917</v>
+        <v>1615</v>
       </c>
       <c r="AB330" s="3" t="n">
-        <v>2142</v>
+        <v>1936</v>
       </c>
       <c r="AC330" s="3" t="n">
         <v>85340</v>
@@ -37664,10 +37664,10 @@
         <v>0.007731</v>
       </c>
       <c r="AA331" s="3" t="n">
-        <v>2076</v>
+        <v>1594</v>
       </c>
       <c r="AB331" s="3" t="n">
-        <v>1741</v>
+        <v>1643</v>
       </c>
       <c r="AC331" s="3" t="n">
         <v>71766</v>
@@ -37764,10 +37764,10 @@
         <v>0</v>
       </c>
       <c r="AA332" s="3" t="n">
-        <v>1230</v>
+        <v>1091</v>
       </c>
       <c r="AB332" s="3" t="n">
-        <v>2094</v>
+        <v>2060</v>
       </c>
       <c r="AC332" s="3" t="n">
         <v>54328</v>
@@ -37864,10 +37864,10 @@
         <v>0</v>
       </c>
       <c r="AA333" s="3" t="n">
-        <v>2274</v>
+        <v>1882</v>
       </c>
       <c r="AB333" s="3" t="n">
-        <v>2027</v>
+        <v>1762</v>
       </c>
       <c r="AC333" s="3" t="n">
         <v>30737</v>
@@ -37964,10 +37964,10 @@
         <v>0</v>
       </c>
       <c r="AA334" s="3" t="n">
-        <v>1180</v>
+        <v>983</v>
       </c>
       <c r="AB334" s="3" t="n">
-        <v>841</v>
+        <v>788</v>
       </c>
       <c r="AC334" s="3" t="n">
         <v>48434</v>
@@ -38064,10 +38064,10 @@
         <v>0.005452</v>
       </c>
       <c r="AA335" s="3" t="n">
-        <v>1831</v>
+        <v>1570</v>
       </c>
       <c r="AB335" s="3" t="n">
-        <v>907</v>
+        <v>875</v>
       </c>
       <c r="AC335" s="3" t="n">
         <v>64936</v>
@@ -38164,10 +38164,10 @@
         <v>6e-06</v>
       </c>
       <c r="AA336" s="3" t="n">
-        <v>1613</v>
+        <v>1227</v>
       </c>
       <c r="AB336" s="3" t="n">
-        <v>1703</v>
+        <v>1579</v>
       </c>
       <c r="AC336" s="3" t="n">
         <v>58766</v>
@@ -38264,10 +38264,10 @@
         <v>0</v>
       </c>
       <c r="AA337" s="3" t="n">
-        <v>1523</v>
+        <v>1177</v>
       </c>
       <c r="AB337" s="3" t="n">
-        <v>1859</v>
+        <v>1784</v>
       </c>
       <c r="AC337" s="3" t="n">
         <v>28413</v>
@@ -38361,13 +38361,13 @@
         <v>0</v>
       </c>
       <c r="Z338" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA338" s="3" t="n">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="AB338" s="3" t="n">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="AC338" s="3" t="n">
         <v>39874</v>
@@ -38458,16 +38458,16 @@
         <v>0.00144</v>
       </c>
       <c r="Y339" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z339" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA339" s="3" t="n">
-        <v>622</v>
+        <v>399</v>
       </c>
       <c r="AB339" s="3" t="n">
-        <v>1349</v>
+        <v>1303</v>
       </c>
       <c r="AC339" s="3" t="n">
         <v>85402</v>
@@ -38564,10 +38564,10 @@
         <v>0</v>
       </c>
       <c r="AA340" s="3" t="n">
-        <v>955</v>
+        <v>749</v>
       </c>
       <c r="AB340" s="3" t="n">
-        <v>565</v>
+        <v>524</v>
       </c>
       <c r="AC340" s="3" t="n">
         <v>54049</v>
@@ -38664,10 +38664,10 @@
         <v>0</v>
       </c>
       <c r="AA341" s="3" t="n">
-        <v>1321</v>
+        <v>1121</v>
       </c>
       <c r="AB341" s="3" t="n">
-        <v>1069</v>
+        <v>940</v>
       </c>
       <c r="AC341" s="3" t="n">
         <v>39461</v>
@@ -38764,10 +38764,10 @@
         <v>0</v>
       </c>
       <c r="AA342" s="3" t="n">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="AB342" s="3" t="n">
-        <v>571</v>
+        <v>541</v>
       </c>
       <c r="AC342" s="3" t="n">
         <v>48660</v>
@@ -38864,10 +38864,10 @@
         <v>0</v>
       </c>
       <c r="AA343" s="3" t="n">
-        <v>1854</v>
+        <v>1579</v>
       </c>
       <c r="AB343" s="3" t="n">
-        <v>1310</v>
+        <v>1263</v>
       </c>
       <c r="AC343" s="3" t="n">
         <v>25407</v>
@@ -38964,10 +38964,10 @@
         <v>0</v>
       </c>
       <c r="AA344" s="3" t="n">
-        <v>211</v>
+        <v>175</v>
       </c>
       <c r="AB344" s="3" t="n">
-        <v>473</v>
+        <v>451</v>
       </c>
       <c r="AC344" s="3" t="n">
         <v>45993</v>
@@ -39061,13 +39061,13 @@
         <v>0</v>
       </c>
       <c r="Z345" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA345" s="3" t="n">
-        <v>1161</v>
+        <v>881</v>
       </c>
       <c r="AB345" s="3" t="n">
-        <v>551</v>
+        <v>520</v>
       </c>
       <c r="AC345" s="3" t="n">
         <v>55682</v>
@@ -39164,10 +39164,10 @@
         <v>9e-06</v>
       </c>
       <c r="AA346" s="3" t="n">
-        <v>1249</v>
+        <v>1001</v>
       </c>
       <c r="AB346" s="3" t="n">
-        <v>1391</v>
+        <v>1290</v>
       </c>
       <c r="AC346" s="3" t="n">
         <v>54650</v>
@@ -39264,10 +39264,10 @@
         <v>0</v>
       </c>
       <c r="AA347" s="3" t="n">
-        <v>849</v>
+        <v>678</v>
       </c>
       <c r="AB347" s="3" t="n">
-        <v>1257</v>
+        <v>1186</v>
       </c>
       <c r="AC347" s="3" t="n">
         <v>36336</v>
@@ -39364,10 +39364,10 @@
         <v>0</v>
       </c>
       <c r="AA348" s="3" t="n">
-        <v>716</v>
+        <v>530</v>
       </c>
       <c r="AB348" s="3" t="n">
-        <v>1159</v>
+        <v>1018</v>
       </c>
       <c r="AC348" s="3" t="n">
         <v>28712</v>
@@ -39461,13 +39461,13 @@
         <v>0</v>
       </c>
       <c r="Z349" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA349" s="3" t="n">
-        <v>953</v>
+        <v>773</v>
       </c>
       <c r="AB349" s="3" t="n">
-        <v>1209</v>
+        <v>1189</v>
       </c>
       <c r="AC349" s="3" t="n">
         <v>49942</v>
@@ -39564,10 +39564,10 @@
         <v>0</v>
       </c>
       <c r="AA350" s="3" t="n">
-        <v>211</v>
+        <v>147</v>
       </c>
       <c r="AB350" s="3" t="n">
-        <v>565</v>
+        <v>515</v>
       </c>
       <c r="AC350" s="3" t="n">
         <v>20661</v>
@@ -39664,10 +39664,10 @@
         <v>0</v>
       </c>
       <c r="AA351" s="3" t="n">
-        <v>3739</v>
+        <v>3131</v>
       </c>
       <c r="AB351" s="3" t="n">
-        <v>1637</v>
+        <v>1526</v>
       </c>
       <c r="AC351" s="3" t="n">
         <v>41701</v>
@@ -39764,10 +39764,10 @@
         <v>0</v>
       </c>
       <c r="AA352" s="3" t="n">
-        <v>696</v>
+        <v>592</v>
       </c>
       <c r="AB352" s="3" t="n">
-        <v>627</v>
+        <v>561</v>
       </c>
       <c r="AC352" s="3" t="n">
         <v>40035</v>
@@ -39864,10 +39864,10 @@
         <v>0</v>
       </c>
       <c r="AA353" s="3" t="n">
-        <v>2186</v>
+        <v>1634</v>
       </c>
       <c r="AB353" s="3" t="n">
-        <v>1653</v>
+        <v>1572</v>
       </c>
       <c r="AC353" s="3" t="n">
         <v>27549</v>
@@ -39964,10 +39964,10 @@
         <v>0</v>
       </c>
       <c r="AA354" s="3" t="n">
-        <v>1046</v>
+        <v>870</v>
       </c>
       <c r="AB354" s="3" t="n">
-        <v>771</v>
+        <v>742</v>
       </c>
       <c r="AC354" s="3" t="n">
         <v>41700</v>
@@ -40064,10 +40064,10 @@
         <v>0</v>
       </c>
       <c r="AA355" s="3" t="n">
-        <v>651</v>
+        <v>554</v>
       </c>
       <c r="AB355" s="3" t="n">
-        <v>338</v>
+        <v>311</v>
       </c>
       <c r="AC355" s="3" t="n">
         <v>48555</v>
@@ -40164,10 +40164,10 @@
         <v>0</v>
       </c>
       <c r="AA356" s="3" t="n">
-        <v>271</v>
+        <v>211</v>
       </c>
       <c r="AB356" s="3" t="n">
-        <v>695</v>
+        <v>660</v>
       </c>
       <c r="AC356" s="3" t="n">
         <v>53906</v>
@@ -40258,16 +40258,16 @@
         <v>0.001242</v>
       </c>
       <c r="Y357" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z357" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AA357" s="3" t="n">
-        <v>1209</v>
+        <v>1019</v>
       </c>
       <c r="AB357" s="3" t="n">
-        <v>1175</v>
+        <v>1154</v>
       </c>
       <c r="AC357" s="3" t="n">
         <v>49166</v>
@@ -40364,10 +40364,10 @@
         <v>0</v>
       </c>
       <c r="AA358" s="3" t="n">
-        <v>527</v>
+        <v>384</v>
       </c>
       <c r="AB358" s="3" t="n">
-        <v>963</v>
+        <v>850</v>
       </c>
       <c r="AC358" s="3" t="n">
         <v>52987</v>
@@ -40464,10 +40464,10 @@
         <v>0.005299</v>
       </c>
       <c r="AA359" s="3" t="n">
-        <v>3110</v>
+        <v>2649</v>
       </c>
       <c r="AB359" s="3" t="n">
-        <v>1687</v>
+        <v>1538</v>
       </c>
       <c r="AC359" s="3" t="n">
         <v>79585</v>
@@ -40564,10 +40564,10 @@
         <v>0</v>
       </c>
       <c r="AA360" s="3" t="n">
-        <v>2349</v>
+        <v>2019</v>
       </c>
       <c r="AB360" s="3" t="n">
-        <v>1055</v>
+        <v>1009</v>
       </c>
       <c r="AC360" s="3" t="n">
         <v>51041</v>
@@ -40658,16 +40658,16 @@
         <v>0.001262</v>
       </c>
       <c r="Y361" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z361" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="AA361" s="3" t="n">
-        <v>708</v>
+        <v>444</v>
       </c>
       <c r="AB361" s="3" t="n">
-        <v>761</v>
+        <v>716</v>
       </c>
       <c r="AC361" s="3" t="n">
         <v>40611</v>
@@ -40764,10 +40764,10 @@
         <v>5e-06</v>
       </c>
       <c r="AA362" s="3" t="n">
-        <v>2560</v>
+        <v>2315</v>
       </c>
       <c r="AB362" s="3" t="n">
-        <v>3334</v>
+        <v>3064</v>
       </c>
       <c r="AC362" s="3" t="n">
         <v>42141</v>
@@ -40864,10 +40864,10 @@
         <v>0</v>
       </c>
       <c r="AA363" s="3" t="n">
-        <v>372</v>
+        <v>314</v>
       </c>
       <c r="AB363" s="3" t="n">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AC363" s="3" t="n">
         <v>36022</v>
@@ -40958,13 +40958,13 @@
         <v>0.001378</v>
       </c>
       <c r="Y364" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z364" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA364" s="3" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AB364" s="3" t="n">
         <v>21</v>
@@ -41064,10 +41064,10 @@
         <v>6e-06</v>
       </c>
       <c r="AA365" s="3" t="n">
-        <v>3541</v>
+        <v>3280</v>
       </c>
       <c r="AB365" s="3" t="n">
-        <v>2267</v>
+        <v>2204</v>
       </c>
       <c r="AC365" s="3" t="n">
         <v>36088</v>
@@ -41164,10 +41164,10 @@
         <v>0.00343</v>
       </c>
       <c r="AA366" s="3" t="n">
-        <v>783</v>
+        <v>619</v>
       </c>
       <c r="AB366" s="3" t="n">
-        <v>1121</v>
+        <v>1027</v>
       </c>
       <c r="AC366" s="3" t="n">
         <v>49816</v>
@@ -41264,10 +41264,10 @@
         <v>0</v>
       </c>
       <c r="AA367" s="3" t="n">
-        <v>1466</v>
+        <v>1126</v>
       </c>
       <c r="AB367" s="3" t="n">
-        <v>290</v>
+        <v>252</v>
       </c>
       <c r="AC367" s="3" t="n">
         <v>23524</v>
@@ -41364,10 +41364,10 @@
         <v>0</v>
       </c>
       <c r="AA368" s="3" t="n">
-        <v>1190</v>
+        <v>972</v>
       </c>
       <c r="AB368" s="3" t="n">
-        <v>1070</v>
+        <v>1033</v>
       </c>
       <c r="AC368" s="3" t="n">
         <v>28949</v>
@@ -41464,10 +41464,10 @@
         <v>0</v>
       </c>
       <c r="AA369" s="3" t="n">
-        <v>761</v>
+        <v>592</v>
       </c>
       <c r="AB369" s="3" t="n">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="AC369" s="3" t="n">
         <v>23917</v>
@@ -41564,10 +41564,10 @@
         <v>0.001111</v>
       </c>
       <c r="AA370" s="3" t="n">
-        <v>740</v>
+        <v>584</v>
       </c>
       <c r="AB370" s="3" t="n">
-        <v>1307</v>
+        <v>1151</v>
       </c>
       <c r="AC370" s="3" t="n">
         <v>42958</v>
@@ -41658,16 +41658,16 @@
         <v>0.001213</v>
       </c>
       <c r="Y371" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z371" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="AA371" s="3" t="n">
-        <v>343</v>
+        <v>268</v>
       </c>
       <c r="AB371" s="3" t="n">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="AC371" s="3" t="n">
         <v>35423</v>
@@ -41764,10 +41764,10 @@
         <v>0</v>
       </c>
       <c r="AA372" s="3" t="n">
-        <v>1418</v>
+        <v>1195</v>
       </c>
       <c r="AB372" s="3" t="n">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="AC372" s="3" t="n">
         <v>23881</v>
@@ -41864,10 +41864,10 @@
         <v>2e-06</v>
       </c>
       <c r="AA373" s="3" t="n">
-        <v>771</v>
+        <v>682</v>
       </c>
       <c r="AB373" s="3" t="n">
-        <v>1620</v>
+        <v>1527</v>
       </c>
       <c r="AC373" s="3" t="n">
         <v>37740</v>
@@ -41964,10 +41964,10 @@
         <v>0</v>
       </c>
       <c r="AA374" s="3" t="n">
-        <v>293</v>
+        <v>247</v>
       </c>
       <c r="AB374" s="3" t="n">
-        <v>1128</v>
+        <v>966</v>
       </c>
       <c r="AC374" s="3" t="n">
         <v>32649</v>
@@ -42064,10 +42064,10 @@
         <v>1e-05</v>
       </c>
       <c r="AA375" s="3" t="n">
-        <v>1934</v>
+        <v>1617</v>
       </c>
       <c r="AB375" s="3" t="n">
-        <v>1829</v>
+        <v>1633</v>
       </c>
       <c r="AC375" s="3" t="n">
         <v>52072</v>
@@ -42164,10 +42164,10 @@
         <v>0</v>
       </c>
       <c r="AA376" s="3" t="n">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="AB376" s="3" t="n">
-        <v>396</v>
+        <v>344</v>
       </c>
       <c r="AC376" s="3" t="n">
         <v>37898</v>
@@ -42264,10 +42264,10 @@
         <v>0</v>
       </c>
       <c r="AA377" s="3" t="n">
-        <v>1235</v>
+        <v>1067</v>
       </c>
       <c r="AB377" s="3" t="n">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="AC377" s="3" t="n">
         <v>20826</v>
@@ -42364,10 +42364,10 @@
         <v>0</v>
       </c>
       <c r="AA378" s="3" t="n">
-        <v>607</v>
+        <v>456</v>
       </c>
       <c r="AB378" s="3" t="n">
-        <v>1020</v>
+        <v>933</v>
       </c>
       <c r="AC378" s="3" t="n">
         <v>51469</v>
@@ -42461,13 +42461,13 @@
         <v>0</v>
       </c>
       <c r="Z379" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA379" s="3" t="n">
-        <v>1642</v>
+        <v>1475</v>
       </c>
       <c r="AB379" s="3" t="n">
-        <v>677</v>
+        <v>624</v>
       </c>
       <c r="AC379" s="3" t="n">
         <v>36062</v>
@@ -42558,16 +42558,16 @@
         <v>0.001105</v>
       </c>
       <c r="Y380" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z380" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA380" s="3" t="n">
-        <v>247</v>
+        <v>169</v>
       </c>
       <c r="AB380" s="3" t="n">
-        <v>713</v>
+        <v>633</v>
       </c>
       <c r="AC380" s="3" t="n">
         <v>54026</v>
@@ -42664,10 +42664,10 @@
         <v>0</v>
       </c>
       <c r="AA381" s="3" t="n">
-        <v>272</v>
+        <v>229</v>
       </c>
       <c r="AB381" s="3" t="n">
-        <v>303</v>
+        <v>271</v>
       </c>
       <c r="AC381" s="3" t="n">
         <v>29349</v>
@@ -42764,10 +42764,10 @@
         <v>0</v>
       </c>
       <c r="AA382" s="3" t="n">
-        <v>792</v>
+        <v>616</v>
       </c>
       <c r="AB382" s="3" t="n">
-        <v>688</v>
+        <v>629</v>
       </c>
       <c r="AC382" s="3" t="n">
         <v>30764</v>
@@ -42864,10 +42864,10 @@
         <v>-0</v>
       </c>
       <c r="AA383" s="3" t="n">
-        <v>242</v>
+        <v>207</v>
       </c>
       <c r="AB383" s="3" t="n">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="AC383" s="3" t="n">
         <v>21057</v>
@@ -42961,13 +42961,13 @@
         <v>0</v>
       </c>
       <c r="Z384" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA384" s="3" t="n">
-        <v>428</v>
+        <v>326</v>
       </c>
       <c r="AB384" s="3" t="n">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="AC384" s="3" t="n">
         <v>24297</v>
@@ -43064,10 +43064,10 @@
         <v>0</v>
       </c>
       <c r="AA385" s="3" t="n">
-        <v>451</v>
+        <v>379</v>
       </c>
       <c r="AB385" s="3" t="n">
-        <v>783</v>
+        <v>717</v>
       </c>
       <c r="AC385" s="3" t="n">
         <v>32150</v>
@@ -43164,10 +43164,10 @@
         <v>-0</v>
       </c>
       <c r="AA386" s="3" t="n">
-        <v>562</v>
+        <v>452</v>
       </c>
       <c r="AB386" s="3" t="n">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="AC386" s="3" t="n">
         <v>24440</v>
@@ -43264,10 +43264,10 @@
         <v>0</v>
       </c>
       <c r="AA387" s="3" t="n">
-        <v>336</v>
+        <v>281</v>
       </c>
       <c r="AB387" s="3" t="n">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="AC387" s="3" t="n">
         <v>21752</v>
@@ -43358,16 +43358,16 @@
         <v>0.00098</v>
       </c>
       <c r="Y388" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z388" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="AA388" s="3" t="n">
-        <v>330</v>
+        <v>236</v>
       </c>
       <c r="AB388" s="3" t="n">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="AC388" s="3" t="n">
         <v>16300</v>
@@ -43464,10 +43464,10 @@
         <v>0</v>
       </c>
       <c r="AA389" s="3" t="n">
-        <v>380</v>
+        <v>329</v>
       </c>
       <c r="AB389" s="3" t="n">
-        <v>460</v>
+        <v>424</v>
       </c>
       <c r="AC389" s="3" t="n">
         <v>22787</v>
@@ -43558,16 +43558,16 @@
         <v>0.000957</v>
       </c>
       <c r="Y390" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z390" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AA390" s="3" t="n">
-        <v>1161</v>
+        <v>1028</v>
       </c>
       <c r="AB390" s="3" t="n">
-        <v>556</v>
+        <v>543</v>
       </c>
       <c r="AC390" s="3" t="n">
         <v>31327</v>
@@ -43658,16 +43658,16 @@
         <v>0.00102</v>
       </c>
       <c r="Y391" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z391" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA391" s="3" t="n">
-        <v>230</v>
+        <v>171</v>
       </c>
       <c r="AB391" s="3" t="n">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="AC391" s="3" t="n">
         <v>22069</v>
@@ -43761,13 +43761,13 @@
         <v>0</v>
       </c>
       <c r="Z392" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA392" s="3" t="n">
-        <v>502</v>
+        <v>423</v>
       </c>
       <c r="AB392" s="3" t="n">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="AC392" s="3" t="n">
         <v>24122</v>
@@ -43864,10 +43864,10 @@
         <v>0</v>
       </c>
       <c r="AA393" s="3" t="n">
-        <v>447</v>
+        <v>322</v>
       </c>
       <c r="AB393" s="3" t="n">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="AC393" s="3" t="n">
         <v>13209</v>
@@ -43964,10 +43964,10 @@
         <v>0</v>
       </c>
       <c r="AA394" s="3" t="n">
-        <v>506</v>
+        <v>402</v>
       </c>
       <c r="AB394" s="3" t="n">
-        <v>377</v>
+        <v>338</v>
       </c>
       <c r="AC394" s="3" t="n">
         <v>20397</v>
@@ -44064,10 +44064,10 @@
         <v>0.000597</v>
       </c>
       <c r="AA395" s="3" t="n">
-        <v>643</v>
+        <v>423</v>
       </c>
       <c r="AB395" s="3" t="n">
-        <v>615</v>
+        <v>580</v>
       </c>
       <c r="AC395" s="3" t="n">
         <v>29921</v>
@@ -44164,10 +44164,10 @@
         <v>0</v>
       </c>
       <c r="AA396" s="3" t="n">
-        <v>528</v>
+        <v>430</v>
       </c>
       <c r="AB396" s="3" t="n">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="AC396" s="3" t="n">
         <v>22479</v>
@@ -44258,16 +44258,16 @@
         <v>0.00096</v>
       </c>
       <c r="Y397" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z397" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AA397" s="3" t="n">
-        <v>648</v>
+        <v>503</v>
       </c>
       <c r="AB397" s="3" t="n">
-        <v>357</v>
+        <v>330</v>
       </c>
       <c r="AC397" s="3" t="n">
         <v>22037</v>
@@ -44364,10 +44364,10 @@
         <v>0</v>
       </c>
       <c r="AA398" s="3" t="n">
-        <v>247</v>
+        <v>206</v>
       </c>
       <c r="AB398" s="3" t="n">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="AC398" s="3" t="n">
         <v>22229</v>
@@ -44458,16 +44458,16 @@
         <v>0.000849</v>
       </c>
       <c r="Y399" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z399" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA399" s="3" t="n">
-        <v>690</v>
+        <v>598</v>
       </c>
       <c r="AB399" s="3" t="n">
-        <v>1531</v>
+        <v>1395</v>
       </c>
       <c r="AC399" s="3" t="n">
         <v>26404</v>
@@ -44558,16 +44558,16 @@
         <v>0.000806</v>
       </c>
       <c r="Y400" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z400" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA400" s="3" t="n">
-        <v>643</v>
+        <v>529</v>
       </c>
       <c r="AB400" s="3" t="n">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AC400" s="3" t="n">
         <v>15729</v>
@@ -44664,10 +44664,10 @@
         <v>0.000464</v>
       </c>
       <c r="AA401" s="3" t="n">
-        <v>1387</v>
+        <v>1220</v>
       </c>
       <c r="AB401" s="3" t="n">
-        <v>1804</v>
+        <v>1547</v>
       </c>
       <c r="AC401" s="3" t="n">
         <v>28979</v>
@@ -44696,16 +44696,16 @@
         </is>
       </c>
       <c r="X402" s="3" t="n">
-        <v>0.7063199999999999</v>
+        <v>0.706971</v>
       </c>
       <c r="Y402" s="3" t="n">
-        <v>0.733924</v>
+        <v>0.729348</v>
       </c>
       <c r="Z402" s="3" t="n">
-        <v>0.733855</v>
+        <v>0.729281</v>
       </c>
       <c r="AB402" s="3" t="n">
-        <v>0.746026</v>
+        <v>0.746174</v>
       </c>
     </row>
     <row r="403">
@@ -44731,16 +44731,16 @@
         </is>
       </c>
       <c r="X403" s="3" t="n">
-        <v>0.460874</v>
+        <v>0.460641</v>
       </c>
       <c r="Y403" s="3" t="n">
-        <v>0.281934</v>
+        <v>0.316663</v>
       </c>
       <c r="Z403" s="3" t="n">
-        <v>0.271601</v>
+        <v>0.313658</v>
       </c>
       <c r="AB403" s="3" t="n">
-        <v>0.504359</v>
+        <v>0.504062</v>
       </c>
     </row>
     <row r="404">
@@ -44750,7 +44750,7 @@
         </is>
       </c>
       <c r="I404" s="3" t="n">
-        <v>0.762508</v>
+        <v>0.754092</v>
       </c>
       <c r="O404" s="3" t="inlineStr">
         <is>
@@ -44766,16 +44766,16 @@
         </is>
       </c>
       <c r="X404" s="3" t="n">
-        <v>0.791898</v>
+        <v>0.773888</v>
       </c>
       <c r="Y404" s="3" t="n">
-        <v>0.467527</v>
+        <v>0.476367</v>
       </c>
       <c r="Z404" s="3" t="n">
-        <v>0.467574</v>
+        <v>0.476394</v>
       </c>
       <c r="AA404" s="3" t="n">
-        <v>0.807041</v>
+        <v>0.789425</v>
       </c>
     </row>
     <row r="405">
@@ -44785,7 +44785,7 @@
         </is>
       </c>
       <c r="I405" s="3" t="n">
-        <v>0.5601080000000001</v>
+        <v>0.544198</v>
       </c>
       <c r="W405" s="3" t="inlineStr">
         <is>
@@ -44793,16 +44793,16 @@
         </is>
       </c>
       <c r="X405" s="3" t="n">
-        <v>0.58377</v>
+        <v>0.567421</v>
       </c>
       <c r="Y405" s="3" t="n">
-        <v>0.099096</v>
+        <v>0.173345</v>
       </c>
       <c r="Z405" s="3" t="n">
-        <v>0.105628</v>
+        <v>0.185462</v>
       </c>
       <c r="AA405" s="3" t="n">
-        <v>0.613529</v>
+        <v>0.594836</v>
       </c>
     </row>
     <row r="406">
@@ -44834,10 +44834,10 @@
         <v>0.810408</v>
       </c>
       <c r="Y407" s="3" t="n">
-        <v>-0.110708</v>
+        <v>-0.054938</v>
       </c>
       <c r="Z407" s="3" t="n">
-        <v>-0.118676</v>
+        <v>-0.06784900000000001</v>
       </c>
       <c r="AC407" s="3" t="n">
         <v>0.872465</v>
@@ -44953,22 +44953,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.807041</v>
+        <v>0.789425</v>
       </c>
       <c r="D2" t="n">
-        <v>0.613529</v>
+        <v>0.594836</v>
       </c>
       <c r="E2" t="n">
-        <v>0.435329</v>
+        <v>0.419327</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6386554621848739</v>
+        <v>0.6410256410256411</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5671641791044776</v>
+        <v>0.5597014925373134</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6007905138339921</v>
+        <v>0.5976095617529881</v>
       </c>
     </row>
     <row r="3">
@@ -44983,22 +44983,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.746026</v>
+        <v>0.746174</v>
       </c>
       <c r="D3" t="n">
-        <v>0.504359</v>
+        <v>0.504062</v>
       </c>
       <c r="E3" t="n">
-        <v>0.351829</v>
+        <v>0.350601</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5673758865248227</v>
+        <v>0.572463768115942</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5970149253731343</v>
+        <v>0.5895522388059702</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5818181818181819</v>
+        <v>0.5808823529411764</v>
       </c>
     </row>
     <row r="4">
@@ -45043,22 +45043,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.791898</v>
+        <v>0.773888</v>
       </c>
       <c r="D5" t="n">
-        <v>0.58377</v>
+        <v>0.567421</v>
       </c>
       <c r="E5" t="n">
-        <v>0.410814</v>
+        <v>0.397669</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6134453781512605</v>
+        <v>0.6068376068376068</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5658914728682171</v>
+        <v>0.5503875968992248</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5887096774193549</v>
+        <v>0.5772357723577235</v>
       </c>
     </row>
     <row r="6">
@@ -45073,22 +45073,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.7063199999999999</v>
+        <v>0.706971</v>
       </c>
       <c r="D6" t="n">
-        <v>0.460874</v>
+        <v>0.460641</v>
       </c>
       <c r="E6" t="n">
-        <v>0.318464</v>
+        <v>0.317687</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5390070921985816</v>
+        <v>0.5434782608695652</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5891472868217055</v>
+        <v>0.5813953488372093</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5629629629629629</v>
+        <v>0.5617977528089888</v>
       </c>
     </row>
     <row r="7">
@@ -45133,13 +45133,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.467527</v>
+        <v>0.476367</v>
       </c>
       <c r="D8" t="n">
-        <v>0.099096</v>
+        <v>0.173345</v>
       </c>
       <c r="E8" t="n">
-        <v>0.063844</v>
+        <v>0.115485</v>
       </c>
       <c r="F8" t="n">
         <v/>
@@ -45163,13 +45163,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.733924</v>
+        <v>0.729348</v>
       </c>
       <c r="D9" t="n">
-        <v>0.281934</v>
+        <v>0.316663</v>
       </c>
       <c r="E9" t="n">
-        <v>0.182144</v>
+        <v>0.210621</v>
       </c>
       <c r="F9" t="n">
         <v/>
@@ -45196,10 +45196,10 @@
         <v>0.649212</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.110708</v>
+        <v>-0.054938</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.073985</v>
+        <v>-0.032707</v>
       </c>
       <c r="F10" t="n">
         <v/>
@@ -45223,13 +45223,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.467574</v>
+        <v>0.476394</v>
       </c>
       <c r="D11" t="n">
-        <v>0.105628</v>
+        <v>0.185462</v>
       </c>
       <c r="E11" t="n">
-        <v>0.069309</v>
+        <v>0.124334</v>
       </c>
       <c r="F11" t="n">
         <v/>
@@ -45253,13 +45253,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.733855</v>
+        <v>0.729281</v>
       </c>
       <c r="D12" t="n">
-        <v>0.271601</v>
+        <v>0.313658</v>
       </c>
       <c r="E12" t="n">
-        <v>0.174022</v>
+        <v>0.207037</v>
       </c>
       <c r="F12" t="n">
         <v/>
@@ -45286,10 +45286,10 @@
         <v>0.649384</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.118676</v>
+        <v>-0.06784900000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.078747</v>
+        <v>-0.040476</v>
       </c>
       <c r="F13" t="n">
         <v/>
@@ -45313,22 +45313,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.762508</v>
+        <v>0.754092</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5601080000000001</v>
+        <v>0.544198</v>
       </c>
       <c r="E14" t="n">
-        <v>0.395398</v>
+        <v>0.382628</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6302521008403361</v>
+        <v>0.6324786324786325</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5725190839694656</v>
+        <v>0.5648854961832062</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6</v>
+        <v>0.5967741935483871</v>
       </c>
     </row>
     <row r="15">
@@ -45343,22 +45343,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.837454</v>
+        <v>0.836743</v>
       </c>
       <c r="D15" t="n">
-        <v>0.633255</v>
+        <v>0.633263</v>
       </c>
       <c r="E15" t="n">
-        <v>0.459697</v>
+        <v>0.460048</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6312056737588653</v>
+        <v>0.6376811594202898</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6793893129770993</v>
+        <v>0.6717557251908397</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6544117647058824</v>
+        <v>0.654275092936803</v>
       </c>
     </row>
     <row r="16">

--- a/EpiRank_改_Germany/ERA_result_reverse_seqday_d_0.95_loops_310.xlsx
+++ b/EpiRank_改_Germany/ERA_result_reverse_seqday_d_0.95_loops_310.xlsx
@@ -859,10 +859,10 @@
         <v>0.019464</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" s="3" t="n">
         <v>24659</v>
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" s="3" t="n">
         <v>5711</v>
@@ -2548,10 +2548,10 @@
         <v>0.005667</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" s="3" t="n">
         <v>1298</v>
@@ -2668,10 +2668,10 @@
         <v>0.004953</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA16" s="3" t="n">
         <v>3161</v>
@@ -3031,7 +3031,7 @@
         <v>0</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="3" t="n">
         <v>1284</v>
@@ -3148,10 +3148,10 @@
         <v>0.004368</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA20" s="3" t="n">
         <v>3554</v>
@@ -3628,10 +3628,10 @@
         <v>0.005151</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA24" s="3" t="n">
         <v>2364</v>
@@ -3748,7 +3748,7 @@
         <v>0.004805</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>0</v>
@@ -4348,7 +4348,7 @@
         <v>0.004134</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>-0</v>
@@ -4708,10 +4708,10 @@
         <v>0.003865</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA33" s="3" t="n">
         <v>9262</v>
@@ -4831,7 +4831,7 @@
         <v>-0</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA34" s="3" t="n">
         <v>2634</v>
@@ -4948,10 +4948,10 @@
         <v>0.004087</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA35" s="3" t="n">
         <v>1916</v>
@@ -5191,7 +5191,7 @@
         <v>0</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA37" s="3" t="n">
         <v>1832</v>
@@ -5311,7 +5311,7 @@
         <v>0</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA38" s="3" t="n">
         <v>2305</v>
@@ -5428,10 +5428,10 @@
         <v>0.003686</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA39" s="3" t="n">
         <v>2255</v>
@@ -5548,10 +5548,10 @@
         <v>0.003755</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA40" s="3" t="n">
         <v>1545</v>
@@ -6388,10 +6388,10 @@
         <v>0.003516</v>
       </c>
       <c r="Y47" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z47" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA47" s="3" t="n">
         <v>1840</v>
@@ -6748,10 +6748,10 @@
         <v>0.00308</v>
       </c>
       <c r="Y50" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z50" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA50" s="3" t="n">
         <v>1112</v>
@@ -6988,10 +6988,10 @@
         <v>0.003143</v>
       </c>
       <c r="Y52" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z52" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA52" s="3" t="n">
         <v>1654</v>
@@ -7111,7 +7111,7 @@
         <v>0</v>
       </c>
       <c r="Z53" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA53" s="3" t="n">
         <v>677</v>
@@ -8308,10 +8308,10 @@
         <v>0.003147</v>
       </c>
       <c r="Y63" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z63" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA63" s="3" t="n">
         <v>2901</v>
@@ -8668,10 +8668,10 @@
         <v>0.00324</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA66" s="3" t="n">
         <v>1941</v>
@@ -8908,10 +8908,10 @@
         <v>0.00306</v>
       </c>
       <c r="Y68" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z68" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA68" s="3" t="n">
         <v>848</v>
@@ -9028,10 +9028,10 @@
         <v>0.002994</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA69" s="3" t="n">
         <v>2549</v>
@@ -9508,10 +9508,10 @@
         <v>0.003381</v>
       </c>
       <c r="Y73" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z73" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA73" s="3" t="n">
         <v>1053</v>
@@ -10951,7 +10951,7 @@
         <v>0</v>
       </c>
       <c r="Z85" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA85" s="3" t="n">
         <v>570</v>
@@ -11671,7 +11671,7 @@
         <v>0</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA91" s="3" t="n">
         <v>3281</v>
@@ -11788,10 +11788,10 @@
         <v>0.002739</v>
       </c>
       <c r="Y92" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z92" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA92" s="3" t="n">
         <v>2093</v>
@@ -12268,10 +12268,10 @@
         <v>0.002802</v>
       </c>
       <c r="Y96" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z96" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA96" s="3" t="n">
         <v>1472</v>
@@ -12508,10 +12508,10 @@
         <v>0.002646</v>
       </c>
       <c r="Y98" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z98" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA98" s="3" t="n">
         <v>3335</v>
@@ -13828,10 +13828,10 @@
         <v>0.002646</v>
       </c>
       <c r="Y109" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z109" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA109" s="3" t="n">
         <v>2324</v>
@@ -14418,7 +14418,7 @@
         <v>0.002503</v>
       </c>
       <c r="Y114" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z114" s="3" t="n">
         <v>-0</v>
@@ -14528,7 +14528,7 @@
         <v>0.003037</v>
       </c>
       <c r="Y115" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z115" s="3" t="n">
         <v>0</v>
@@ -14638,10 +14638,10 @@
         <v>0.002434</v>
       </c>
       <c r="Y116" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z116" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA116" s="3" t="n">
         <v>1466</v>
@@ -14861,7 +14861,7 @@
         <v>-0</v>
       </c>
       <c r="Z118" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA118" s="3" t="n">
         <v>3519</v>
@@ -17058,7 +17058,7 @@
         <v>0.002271</v>
       </c>
       <c r="Y138" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z138" s="3" t="n">
         <v>0</v>
@@ -17168,10 +17168,10 @@
         <v>0.002766</v>
       </c>
       <c r="Y139" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z139" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA139" s="3" t="n">
         <v>1490</v>
@@ -17391,7 +17391,7 @@
         <v>0</v>
       </c>
       <c r="Z141" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA141" s="3" t="n">
         <v>2679</v>
@@ -17498,7 +17498,7 @@
         <v>0.002515</v>
       </c>
       <c r="Y142" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z142" s="3" t="n">
         <v>0</v>
@@ -18268,7 +18268,7 @@
         <v>0.002226</v>
       </c>
       <c r="Y149" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z149" s="3" t="n">
         <v>0</v>
@@ -18708,10 +18708,10 @@
         <v>0.002399</v>
       </c>
       <c r="Y153" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z153" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA153" s="3" t="n">
         <v>2222</v>
@@ -19041,7 +19041,7 @@
         <v>-0</v>
       </c>
       <c r="Z156" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA156" s="3" t="n">
         <v>1490</v>
@@ -19811,7 +19811,7 @@
         <v>0</v>
       </c>
       <c r="Z163" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA163" s="3" t="n">
         <v>1586</v>
@@ -20578,10 +20578,10 @@
         <v>0.002054</v>
       </c>
       <c r="Y170" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z170" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA170" s="3" t="n">
         <v>1421</v>
@@ -21128,10 +21128,10 @@
         <v>0.002174</v>
       </c>
       <c r="Y175" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z175" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA175" s="3" t="n">
         <v>1591</v>
@@ -21348,10 +21348,10 @@
         <v>0.002421</v>
       </c>
       <c r="Y177" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z177" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA177" s="3" t="n">
         <v>645</v>
@@ -21461,7 +21461,7 @@
         <v>0</v>
       </c>
       <c r="Z178" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA178" s="3" t="n">
         <v>1243</v>
@@ -21898,7 +21898,7 @@
         <v>0.002184</v>
       </c>
       <c r="Y182" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z182" s="3" t="n">
         <v>-0</v>
@@ -22008,10 +22008,10 @@
         <v>0.002155</v>
       </c>
       <c r="Y183" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z183" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA183" s="3" t="n">
         <v>990</v>
@@ -22228,10 +22228,10 @@
         <v>0.001842</v>
       </c>
       <c r="Y185" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z185" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA185" s="3" t="n">
         <v>806</v>
@@ -23111,7 +23111,7 @@
         <v>0</v>
       </c>
       <c r="Z193" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA193" s="3" t="n">
         <v>1221</v>
@@ -23991,7 +23991,7 @@
         <v>0</v>
       </c>
       <c r="Z201" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA201" s="3" t="n">
         <v>1194</v>
@@ -24098,10 +24098,10 @@
         <v>0.001847</v>
       </c>
       <c r="Y202" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z202" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA202" s="3" t="n">
         <v>909</v>
@@ -24538,7 +24538,7 @@
         <v>0.002033</v>
       </c>
       <c r="Y206" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z206" s="3" t="n">
         <v>0</v>
@@ -25088,7 +25088,7 @@
         <v>0.002032</v>
       </c>
       <c r="Y211" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z211" s="3" t="n">
         <v>0</v>
@@ -25198,7 +25198,7 @@
         <v>0.001965</v>
       </c>
       <c r="Y212" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z212" s="3" t="n">
         <v>0</v>
@@ -25641,7 +25641,7 @@
         <v>0</v>
       </c>
       <c r="Z216" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA216" s="3" t="n">
         <v>1470</v>
@@ -25858,10 +25858,10 @@
         <v>0.001997</v>
       </c>
       <c r="Y218" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z218" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA218" s="3" t="n">
         <v>1283</v>
@@ -26188,10 +26188,10 @@
         <v>0.001669</v>
       </c>
       <c r="Y221" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z221" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA221" s="3" t="n">
         <v>646</v>
@@ -26408,7 +26408,7 @@
         <v>0.001956</v>
       </c>
       <c r="Y223" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z223" s="3" t="n">
         <v>0</v>
@@ -26738,10 +26738,10 @@
         <v>0.001914</v>
       </c>
       <c r="Y226" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z226" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA226" s="3" t="n">
         <v>1786</v>
@@ -27288,7 +27288,7 @@
         <v>0.001953</v>
       </c>
       <c r="Y231" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z231" s="3" t="n">
         <v>-0</v>
@@ -27728,7 +27728,7 @@
         <v>0.001785</v>
       </c>
       <c r="Y235" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z235" s="3" t="n">
         <v>0</v>
@@ -28278,10 +28278,10 @@
         <v>0.00183</v>
       </c>
       <c r="Y240" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z240" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA240" s="3" t="n">
         <v>1446</v>
@@ -28498,7 +28498,7 @@
         <v>0.001919</v>
       </c>
       <c r="Y242" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z242" s="3" t="n">
         <v>-0</v>
@@ -28608,7 +28608,7 @@
         <v>0.001993</v>
       </c>
       <c r="Y243" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z243" s="3" t="n">
         <v>-0</v>
@@ -28941,7 +28941,7 @@
         <v>0</v>
       </c>
       <c r="Z246" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA246" s="3" t="n">
         <v>744</v>
@@ -29268,10 +29268,10 @@
         <v>0.001815</v>
       </c>
       <c r="Y249" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z249" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA249" s="3" t="n">
         <v>1108</v>
@@ -29598,10 +29598,10 @@
         <v>0.001608</v>
       </c>
       <c r="Y252" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z252" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA252" s="3" t="n">
         <v>1250</v>
@@ -29708,10 +29708,10 @@
         <v>0.00162</v>
       </c>
       <c r="Y253" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z253" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA253" s="3" t="n">
         <v>1195</v>
@@ -29818,7 +29818,7 @@
         <v>0.001683</v>
       </c>
       <c r="Y254" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z254" s="3" t="n">
         <v>0</v>
@@ -29928,10 +29928,10 @@
         <v>0.001666</v>
       </c>
       <c r="Y255" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z255" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA255" s="3" t="n">
         <v>1345</v>
@@ -30038,7 +30038,7 @@
         <v>0.00163</v>
       </c>
       <c r="Y256" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z256" s="3" t="n">
         <v>0</v>
@@ -30258,10 +30258,10 @@
         <v>0.00168</v>
       </c>
       <c r="Y258" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z258" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA258" s="3" t="n">
         <v>822</v>
@@ -31028,10 +31028,10 @@
         <v>0.001646</v>
       </c>
       <c r="Y265" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z265" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA265" s="3" t="n">
         <v>2461</v>
@@ -32358,7 +32358,7 @@
         <v>0.001623</v>
       </c>
       <c r="Y278" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z278" s="3" t="n">
         <v>-0</v>
@@ -33158,10 +33158,10 @@
         <v>0.001623</v>
       </c>
       <c r="Y286" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z286" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z286" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA286" s="3" t="n">
         <v>564</v>
@@ -34158,7 +34158,7 @@
         <v>0.001619</v>
       </c>
       <c r="Y296" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z296" s="3" t="n">
         <v>-0</v>
@@ -34358,7 +34358,7 @@
         <v>0.001605</v>
       </c>
       <c r="Y298" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z298" s="3" t="n">
         <v>0</v>
@@ -34661,7 +34661,7 @@
         <v>0</v>
       </c>
       <c r="Z301" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA301" s="3" t="n">
         <v>1123</v>
@@ -34861,7 +34861,7 @@
         <v>0</v>
       </c>
       <c r="Z303" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA303" s="3" t="n">
         <v>1526</v>
@@ -34961,7 +34961,7 @@
         <v>0</v>
       </c>
       <c r="Z304" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA304" s="3" t="n">
         <v>606</v>
@@ -35658,10 +35658,10 @@
         <v>0.001535</v>
       </c>
       <c r="Y311" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z311" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA311" s="3" t="n">
         <v>1449</v>
@@ -36158,7 +36158,7 @@
         <v>0.00142</v>
       </c>
       <c r="Y316" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z316" s="3" t="n">
         <v>0</v>
@@ -39061,7 +39061,7 @@
         <v>0</v>
       </c>
       <c r="Z345" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA345" s="3" t="n">
         <v>881</v>
@@ -40258,10 +40258,10 @@
         <v>0.001242</v>
       </c>
       <c r="Y357" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z357" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA357" s="3" t="n">
         <v>1019</v>
@@ -40561,7 +40561,7 @@
         <v>0</v>
       </c>
       <c r="Z360" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA360" s="3" t="n">
         <v>2019</v>
@@ -40658,7 +40658,7 @@
         <v>0.001262</v>
       </c>
       <c r="Y361" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z361" s="3" t="n">
         <v>-0</v>
@@ -41658,10 +41658,10 @@
         <v>0.001213</v>
       </c>
       <c r="Y371" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z371" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA371" s="3" t="n">
         <v>268</v>
@@ -42958,10 +42958,10 @@
         <v>0.001105</v>
       </c>
       <c r="Y384" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z384" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA384" s="3" t="n">
         <v>326</v>
@@ -43161,7 +43161,7 @@
         <v>-0</v>
       </c>
       <c r="Z386" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA386" s="3" t="n">
         <v>452</v>
@@ -43358,7 +43358,7 @@
         <v>0.00098</v>
       </c>
       <c r="Y388" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z388" s="3" t="n">
         <v>-0</v>
@@ -43558,10 +43558,10 @@
         <v>0.000957</v>
       </c>
       <c r="Y390" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z390" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA390" s="3" t="n">
         <v>1028</v>
@@ -43758,7 +43758,7 @@
         <v>0.000975</v>
       </c>
       <c r="Y392" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z392" s="3" t="n">
         <v>0</v>
@@ -43958,7 +43958,7 @@
         <v>0.001072</v>
       </c>
       <c r="Y394" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z394" s="3" t="n">
         <v>0</v>
@@ -44258,10 +44258,10 @@
         <v>0.00096</v>
       </c>
       <c r="Y397" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z397" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA397" s="3" t="n">
         <v>503</v>
@@ -44734,10 +44734,10 @@
         <v>0.460641</v>
       </c>
       <c r="Y403" s="3" t="n">
-        <v>0.316663</v>
+        <v>0.282812</v>
       </c>
       <c r="Z403" s="3" t="n">
-        <v>0.313658</v>
+        <v>0.274879</v>
       </c>
       <c r="AB403" s="3" t="n">
         <v>0.504062</v>
@@ -44796,10 +44796,10 @@
         <v>0.567421</v>
       </c>
       <c r="Y405" s="3" t="n">
-        <v>0.173345</v>
+        <v>0.137268</v>
       </c>
       <c r="Z405" s="3" t="n">
-        <v>0.185462</v>
+        <v>0.145884</v>
       </c>
       <c r="AA405" s="3" t="n">
         <v>0.594836</v>
@@ -44834,10 +44834,10 @@
         <v>0.810408</v>
       </c>
       <c r="Y407" s="3" t="n">
-        <v>-0.054938</v>
+        <v>-0.09452099999999999</v>
       </c>
       <c r="Z407" s="3" t="n">
-        <v>-0.06784900000000001</v>
+        <v>-0.110668</v>
       </c>
       <c r="AC407" s="3" t="n">
         <v>0.872465</v>
@@ -45136,10 +45136,10 @@
         <v>0.476367</v>
       </c>
       <c r="D8" t="n">
-        <v>0.173345</v>
+        <v>0.137268</v>
       </c>
       <c r="E8" t="n">
-        <v>0.115485</v>
+        <v>0.087911</v>
       </c>
       <c r="F8" t="n">
         <v/>
@@ -45166,10 +45166,10 @@
         <v>0.729348</v>
       </c>
       <c r="D9" t="n">
-        <v>0.316663</v>
+        <v>0.282812</v>
       </c>
       <c r="E9" t="n">
-        <v>0.210621</v>
+        <v>0.183573</v>
       </c>
       <c r="F9" t="n">
         <v/>
@@ -45196,10 +45196,10 @@
         <v>0.649212</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.054938</v>
+        <v>-0.09452099999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.032707</v>
+        <v>-0.064586</v>
       </c>
       <c r="F10" t="n">
         <v/>
@@ -45226,10 +45226,10 @@
         <v>0.476394</v>
       </c>
       <c r="D11" t="n">
-        <v>0.185462</v>
+        <v>0.145884</v>
       </c>
       <c r="E11" t="n">
-        <v>0.124334</v>
+        <v>0.09460399999999999</v>
       </c>
       <c r="F11" t="n">
         <v/>
@@ -45256,10 +45256,10 @@
         <v>0.729281</v>
       </c>
       <c r="D12" t="n">
-        <v>0.313658</v>
+        <v>0.274879</v>
       </c>
       <c r="E12" t="n">
-        <v>0.207037</v>
+        <v>0.18059</v>
       </c>
       <c r="F12" t="n">
         <v/>
@@ -45286,10 +45286,10 @@
         <v>0.649384</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.06784900000000001</v>
+        <v>-0.110668</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.040476</v>
+        <v>-0.074962</v>
       </c>
       <c r="F13" t="n">
         <v/>

--- a/EpiRank_改_Germany/ERA_result_reverse_seqday_d_0.95_loops_310.xlsx
+++ b/EpiRank_改_Germany/ERA_result_reverse_seqday_d_0.95_loops_310.xlsx
@@ -859,10 +859,10 @@
         <v>0.019464</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA3" s="3" t="n">
         <v>24659</v>
@@ -1294,10 +1294,10 @@
         <v>0.01118</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" s="3" t="n">
         <v>5644</v>
@@ -2428,10 +2428,10 @@
         <v>0.005871</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="n">
         <v>3321</v>
@@ -2548,10 +2548,10 @@
         <v>0.005667</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" s="3" t="n">
         <v>1298</v>
@@ -3028,10 +3028,10 @@
         <v>0.005427</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="3" t="n">
         <v>1284</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA20" s="3" t="n">
         <v>3554</v>
@@ -3508,10 +3508,10 @@
         <v>0.004559</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA23" s="3" t="n">
         <v>3443</v>
@@ -3751,7 +3751,7 @@
         <v>-0</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA25" s="3" t="n">
         <v>1048</v>
@@ -3868,10 +3868,10 @@
         <v>0.003699</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA26" s="3" t="n">
         <v>1799</v>
@@ -4348,10 +4348,10 @@
         <v>0.004134</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA30" s="3" t="n">
         <v>3044</v>
@@ -4468,7 +4468,7 @@
         <v>0.004758</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>-0</v>
@@ -4708,10 +4708,10 @@
         <v>0.003865</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA33" s="3" t="n">
         <v>9262</v>
@@ -4948,10 +4948,10 @@
         <v>0.004087</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA35" s="3" t="n">
         <v>1916</v>
@@ -5191,7 +5191,7 @@
         <v>0</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA37" s="3" t="n">
         <v>1832</v>
@@ -5308,10 +5308,10 @@
         <v>0.003994</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA38" s="3" t="n">
         <v>2305</v>
@@ -5428,10 +5428,10 @@
         <v>0.003686</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA39" s="3" t="n">
         <v>2255</v>
@@ -5548,10 +5548,10 @@
         <v>0.003755</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA40" s="3" t="n">
         <v>1545</v>
@@ -5668,10 +5668,10 @@
         <v>0.004055</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA41" s="3" t="n">
         <v>1589</v>
@@ -6388,10 +6388,10 @@
         <v>0.003516</v>
       </c>
       <c r="Y47" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z47" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA47" s="3" t="n">
         <v>1840</v>
@@ -6628,10 +6628,10 @@
         <v>0.003305</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA49" s="3" t="n">
         <v>5738</v>
@@ -6991,7 +6991,7 @@
         <v>0</v>
       </c>
       <c r="Z52" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA52" s="3" t="n">
         <v>1654</v>
@@ -7108,10 +7108,10 @@
         <v>0.003434</v>
       </c>
       <c r="Y53" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z53" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA53" s="3" t="n">
         <v>677</v>
@@ -7831,7 +7831,7 @@
         <v>0</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA59" s="3" t="n">
         <v>2054</v>
@@ -8191,7 +8191,7 @@
         <v>0</v>
       </c>
       <c r="Z62" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA62" s="3" t="n">
         <v>1780</v>
@@ -8308,10 +8308,10 @@
         <v>0.003147</v>
       </c>
       <c r="Y63" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z63" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA63" s="3" t="n">
         <v>2901</v>
@@ -9028,7 +9028,7 @@
         <v>0.002994</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z69" s="3" t="n">
         <v>-0</v>
@@ -10591,7 +10591,7 @@
         <v>0</v>
       </c>
       <c r="Z82" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA82" s="3" t="n">
         <v>3152</v>
@@ -10831,7 +10831,7 @@
         <v>0</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA84" s="3" t="n">
         <v>1340</v>
@@ -10948,10 +10948,10 @@
         <v>0.003086</v>
       </c>
       <c r="Y85" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z85" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA85" s="3" t="n">
         <v>570</v>
@@ -11188,7 +11188,7 @@
         <v>0.003072</v>
       </c>
       <c r="Y87" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z87" s="3" t="n">
         <v>-0</v>
@@ -11668,10 +11668,10 @@
         <v>0.002422</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA91" s="3" t="n">
         <v>3281</v>
@@ -11788,10 +11788,10 @@
         <v>0.002739</v>
       </c>
       <c r="Y92" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z92" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA92" s="3" t="n">
         <v>2093</v>
@@ -12028,10 +12028,10 @@
         <v>0.003001</v>
       </c>
       <c r="Y94" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z94" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA94" s="3" t="n">
         <v>3105</v>
@@ -12388,10 +12388,10 @@
         <v>0.002932</v>
       </c>
       <c r="Y97" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z97" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA97" s="3" t="n">
         <v>1230</v>
@@ -12508,10 +12508,10 @@
         <v>0.002646</v>
       </c>
       <c r="Y98" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z98" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA98" s="3" t="n">
         <v>3335</v>
@@ -12871,7 +12871,7 @@
         <v>0</v>
       </c>
       <c r="Z101" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA101" s="3" t="n">
         <v>733</v>
@@ -12988,7 +12988,7 @@
         <v>0.002894</v>
       </c>
       <c r="Y102" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z102" s="3" t="n">
         <v>0</v>
@@ -14308,10 +14308,10 @@
         <v>0.002608</v>
       </c>
       <c r="Y113" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z113" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA113" s="3" t="n">
         <v>2830</v>
@@ -14528,10 +14528,10 @@
         <v>0.003037</v>
       </c>
       <c r="Y115" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z115" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA115" s="3" t="n">
         <v>1848</v>
@@ -15188,10 +15188,10 @@
         <v>0.002564</v>
       </c>
       <c r="Y121" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z121" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA121" s="3" t="n">
         <v>2194</v>
@@ -15741,7 +15741,7 @@
         <v>-0</v>
       </c>
       <c r="Z126" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA126" s="3" t="n">
         <v>2024</v>
@@ -17058,7 +17058,7 @@
         <v>0.002271</v>
       </c>
       <c r="Y138" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z138" s="3" t="n">
         <v>-0</v>
@@ -17171,7 +17171,7 @@
         <v>0</v>
       </c>
       <c r="Z139" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA139" s="3" t="n">
         <v>1490</v>
@@ -17388,7 +17388,7 @@
         <v>0.002383</v>
       </c>
       <c r="Y141" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z141" s="3" t="n">
         <v>-0</v>
@@ -17498,10 +17498,10 @@
         <v>0.002515</v>
       </c>
       <c r="Y142" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z142" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA142" s="3" t="n">
         <v>488</v>
@@ -18268,7 +18268,7 @@
         <v>0.002226</v>
       </c>
       <c r="Y149" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z149" s="3" t="n">
         <v>0</v>
@@ -18488,10 +18488,10 @@
         <v>0.002324</v>
       </c>
       <c r="Y151" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z151" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA151" s="3" t="n">
         <v>1138</v>
@@ -18708,10 +18708,10 @@
         <v>0.002399</v>
       </c>
       <c r="Y153" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z153" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA153" s="3" t="n">
         <v>2222</v>
@@ -19481,7 +19481,7 @@
         <v>0</v>
       </c>
       <c r="Z160" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA160" s="3" t="n">
         <v>1043</v>
@@ -19698,10 +19698,10 @@
         <v>0.002359</v>
       </c>
       <c r="Y162" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z162" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA162" s="3" t="n">
         <v>1798</v>
@@ -19808,10 +19808,10 @@
         <v>0.002078</v>
       </c>
       <c r="Y163" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z163" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA163" s="3" t="n">
         <v>1586</v>
@@ -20138,7 +20138,7 @@
         <v>0.002434</v>
       </c>
       <c r="Y166" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z166" s="3" t="n">
         <v>-0</v>
@@ -20578,10 +20578,10 @@
         <v>0.002054</v>
       </c>
       <c r="Y170" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z170" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA170" s="3" t="n">
         <v>1421</v>
@@ -20801,7 +20801,7 @@
         <v>-0</v>
       </c>
       <c r="Z172" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA172" s="3" t="n">
         <v>1038</v>
@@ -20911,7 +20911,7 @@
         <v>0</v>
       </c>
       <c r="Z173" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA173" s="3" t="n">
         <v>1054</v>
@@ -21898,10 +21898,10 @@
         <v>0.002184</v>
       </c>
       <c r="Y182" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z182" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA182" s="3" t="n">
         <v>1222</v>
@@ -22451,7 +22451,7 @@
         <v>0</v>
       </c>
       <c r="Z187" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA187" s="3" t="n">
         <v>1119</v>
@@ -24098,10 +24098,10 @@
         <v>0.001847</v>
       </c>
       <c r="Y202" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z202" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA202" s="3" t="n">
         <v>909</v>
@@ -24428,7 +24428,7 @@
         <v>0.001952</v>
       </c>
       <c r="Y205" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z205" s="3" t="n">
         <v>-0</v>
@@ -24538,10 +24538,10 @@
         <v>0.002033</v>
       </c>
       <c r="Y206" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z206" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA206" s="3" t="n">
         <v>1431</v>
@@ -24871,7 +24871,7 @@
         <v>0</v>
       </c>
       <c r="Z209" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA209" s="3" t="n">
         <v>1138</v>
@@ -25088,7 +25088,7 @@
         <v>0.002032</v>
       </c>
       <c r="Y211" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z211" s="3" t="n">
         <v>0</v>
@@ -25198,10 +25198,10 @@
         <v>0.001965</v>
       </c>
       <c r="Y212" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z212" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA212" s="3" t="n">
         <v>2579</v>
@@ -25858,10 +25858,10 @@
         <v>0.001997</v>
       </c>
       <c r="Y218" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z218" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA218" s="3" t="n">
         <v>1283</v>
@@ -26191,7 +26191,7 @@
         <v>-0</v>
       </c>
       <c r="Z221" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA221" s="3" t="n">
         <v>646</v>
@@ -26408,7 +26408,7 @@
         <v>0.001956</v>
       </c>
       <c r="Y223" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z223" s="3" t="n">
         <v>0</v>
@@ -26631,7 +26631,7 @@
         <v>0</v>
       </c>
       <c r="Z225" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA225" s="3" t="n">
         <v>676</v>
@@ -26741,7 +26741,7 @@
         <v>0</v>
       </c>
       <c r="Z226" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA226" s="3" t="n">
         <v>1786</v>
@@ -27728,7 +27728,7 @@
         <v>0.001785</v>
       </c>
       <c r="Y235" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z235" s="3" t="n">
         <v>0</v>
@@ -27841,7 +27841,7 @@
         <v>0</v>
       </c>
       <c r="Z236" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA236" s="3" t="n">
         <v>1054</v>
@@ -28278,10 +28278,10 @@
         <v>0.00183</v>
       </c>
       <c r="Y240" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z240" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA240" s="3" t="n">
         <v>1446</v>
@@ -28498,10 +28498,10 @@
         <v>0.001919</v>
       </c>
       <c r="Y242" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z242" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA242" s="3" t="n">
         <v>374</v>
@@ -28608,10 +28608,10 @@
         <v>0.001993</v>
       </c>
       <c r="Y243" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z243" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA243" s="3" t="n">
         <v>940</v>
@@ -28938,10 +28938,10 @@
         <v>0.001896</v>
       </c>
       <c r="Y246" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z246" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA246" s="3" t="n">
         <v>744</v>
@@ -29268,7 +29268,7 @@
         <v>0.001815</v>
       </c>
       <c r="Y249" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z249" s="3" t="n">
         <v>0</v>
@@ -29601,7 +29601,7 @@
         <v>0</v>
       </c>
       <c r="Z252" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA252" s="3" t="n">
         <v>1250</v>
@@ -29708,10 +29708,10 @@
         <v>0.00162</v>
       </c>
       <c r="Y253" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z253" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA253" s="3" t="n">
         <v>1195</v>
@@ -29928,10 +29928,10 @@
         <v>0.001666</v>
       </c>
       <c r="Y255" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z255" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA255" s="3" t="n">
         <v>1345</v>
@@ -30038,7 +30038,7 @@
         <v>0.00163</v>
       </c>
       <c r="Y256" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z256" s="3" t="n">
         <v>0</v>
@@ -30261,7 +30261,7 @@
         <v>-0</v>
       </c>
       <c r="Z258" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA258" s="3" t="n">
         <v>822</v>
@@ -31028,10 +31028,10 @@
         <v>0.001646</v>
       </c>
       <c r="Y265" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z265" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA265" s="3" t="n">
         <v>2461</v>
@@ -31358,10 +31358,10 @@
         <v>0.001896</v>
       </c>
       <c r="Y268" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z268" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA268" s="3" t="n">
         <v>1098</v>
@@ -31558,10 +31558,10 @@
         <v>0.001717</v>
       </c>
       <c r="Y270" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z270" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA270" s="3" t="n">
         <v>1501</v>
@@ -32358,10 +32358,10 @@
         <v>0.001623</v>
       </c>
       <c r="Y278" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z278" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA278" s="3" t="n">
         <v>898</v>
@@ -32461,7 +32461,7 @@
         <v>0</v>
       </c>
       <c r="Z279" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA279" s="3" t="n">
         <v>547</v>
@@ -32658,10 +32658,10 @@
         <v>0.001582</v>
       </c>
       <c r="Y281" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z281" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA281" s="3" t="n">
         <v>1258</v>
@@ -33158,10 +33158,10 @@
         <v>0.001623</v>
       </c>
       <c r="Y286" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z286" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA286" s="3" t="n">
         <v>564</v>
@@ -34158,10 +34158,10 @@
         <v>0.001619</v>
       </c>
       <c r="Y296" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z296" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA296" s="3" t="n">
         <v>734</v>
@@ -34658,10 +34658,10 @@
         <v>0.001586</v>
       </c>
       <c r="Y301" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z301" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA301" s="3" t="n">
         <v>1123</v>
@@ -34858,7 +34858,7 @@
         <v>0.001426</v>
       </c>
       <c r="Y303" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z303" s="3" t="n">
         <v>-0</v>
@@ -35658,10 +35658,10 @@
         <v>0.001535</v>
       </c>
       <c r="Y311" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z311" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA311" s="3" t="n">
         <v>1449</v>
@@ -36158,7 +36158,7 @@
         <v>0.00142</v>
       </c>
       <c r="Y316" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z316" s="3" t="n">
         <v>0</v>
@@ -36358,10 +36358,10 @@
         <v>0.001396</v>
       </c>
       <c r="Y318" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z318" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA318" s="3" t="n">
         <v>913</v>
@@ -36758,10 +36758,10 @@
         <v>0.001423</v>
       </c>
       <c r="Y322" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z322" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA322" s="3" t="n">
         <v>327</v>
@@ -36861,7 +36861,7 @@
         <v>0</v>
       </c>
       <c r="Z323" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA323" s="3" t="n">
         <v>649</v>
@@ -37358,10 +37358,10 @@
         <v>0.001552</v>
       </c>
       <c r="Y328" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z328" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA328" s="3" t="n">
         <v>2280</v>
@@ -37461,7 +37461,7 @@
         <v>0</v>
       </c>
       <c r="Z329" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA329" s="3" t="n">
         <v>1113</v>
@@ -38358,7 +38358,7 @@
         <v>0.001476</v>
       </c>
       <c r="Y338" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z338" s="3" t="n">
         <v>0</v>
@@ -38461,7 +38461,7 @@
         <v>0</v>
       </c>
       <c r="Z339" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA339" s="3" t="n">
         <v>399</v>
@@ -40861,7 +40861,7 @@
         <v>0</v>
       </c>
       <c r="Z363" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA363" s="3" t="n">
         <v>314</v>
@@ -40958,10 +40958,10 @@
         <v>0.001378</v>
       </c>
       <c r="Y364" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z364" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA364" s="3" t="n">
         <v>82</v>
@@ -41658,7 +41658,7 @@
         <v>0.001213</v>
       </c>
       <c r="Y371" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z371" s="3" t="n">
         <v>0</v>
@@ -42458,7 +42458,7 @@
         <v>0.000982</v>
       </c>
       <c r="Y379" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z379" s="3" t="n">
         <v>-0</v>
@@ -42561,7 +42561,7 @@
         <v>0</v>
       </c>
       <c r="Z380" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA380" s="3" t="n">
         <v>169</v>
@@ -42758,10 +42758,10 @@
         <v>0.00096</v>
       </c>
       <c r="Y382" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z382" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA382" s="3" t="n">
         <v>616</v>
@@ -42858,10 +42858,10 @@
         <v>0.001039</v>
       </c>
       <c r="Y383" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z383" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA383" s="3" t="n">
         <v>207</v>
@@ -43158,10 +43158,10 @@
         <v>0.0009810000000000001</v>
       </c>
       <c r="Y386" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z386" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA386" s="3" t="n">
         <v>452</v>
@@ -43358,7 +43358,7 @@
         <v>0.00098</v>
       </c>
       <c r="Y388" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z388" s="3" t="n">
         <v>-0</v>
@@ -43561,7 +43561,7 @@
         <v>0</v>
       </c>
       <c r="Z390" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA390" s="3" t="n">
         <v>1028</v>
@@ -43758,10 +43758,10 @@
         <v>0.000975</v>
       </c>
       <c r="Y392" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z392" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA392" s="3" t="n">
         <v>423</v>
@@ -43958,7 +43958,7 @@
         <v>0.001072</v>
       </c>
       <c r="Y394" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z394" s="3" t="n">
         <v>-0</v>
@@ -44258,10 +44258,10 @@
         <v>0.00096</v>
       </c>
       <c r="Y397" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z397" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA397" s="3" t="n">
         <v>503</v>
@@ -44558,10 +44558,10 @@
         <v>0.000806</v>
       </c>
       <c r="Y400" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z400" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA400" s="3" t="n">
         <v>529</v>
@@ -44734,10 +44734,10 @@
         <v>0.460641</v>
       </c>
       <c r="Y403" s="3" t="n">
-        <v>0.279884</v>
+        <v>0.295791</v>
       </c>
       <c r="Z403" s="3" t="n">
-        <v>0.268647</v>
+        <v>0.278281</v>
       </c>
       <c r="AB403" s="3" t="n">
         <v>0.504062</v>
@@ -44796,10 +44796,10 @@
         <v>0.567421</v>
       </c>
       <c r="Y405" s="3" t="n">
-        <v>0.142253</v>
+        <v>0.161547</v>
       </c>
       <c r="Z405" s="3" t="n">
-        <v>0.136602</v>
+        <v>0.1651</v>
       </c>
       <c r="AA405" s="3" t="n">
         <v>0.594836</v>
@@ -44834,10 +44834,10 @@
         <v>0.810408</v>
       </c>
       <c r="Y407" s="3" t="n">
-        <v>-0.09521300000000001</v>
+        <v>-0.092283</v>
       </c>
       <c r="Z407" s="3" t="n">
-        <v>-0.118604</v>
+        <v>-0.113733</v>
       </c>
       <c r="AC407" s="3" t="n">
         <v>0.872465</v>
@@ -44886,7 +44886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -44897,6 +44897,8 @@
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -44927,15 +44929,25 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
+          <t>Pearson_partial_r</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Spearman_partial_rho</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
           <t>Recall</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
@@ -44962,12 +44974,18 @@
         <v>0.419327</v>
       </c>
       <c r="F2" t="n">
+        <v>0.281473</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.297348</v>
+      </c>
+      <c r="H2" t="n">
         <v>0.6410256410256411</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>0.5597014925373134</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0.5976095617529881</v>
       </c>
     </row>
@@ -44992,12 +45010,18 @@
         <v>0.350601</v>
       </c>
       <c r="F3" t="n">
+        <v>-0.127758</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.095529</v>
+      </c>
+      <c r="H3" t="n">
         <v>0.572463768115942</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>0.5895522388059702</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>0.5808823529411764</v>
       </c>
     </row>
@@ -45022,12 +45046,18 @@
         <v>0.69782</v>
       </c>
       <c r="F4" t="n">
+        <v>0.281756</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="H4" t="n">
         <v>0.816793893129771</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>0.7985074626865671</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>0.8075471698113207</v>
       </c>
     </row>
@@ -45052,12 +45082,18 @@
         <v>0.397669</v>
       </c>
       <c r="F5" t="n">
+        <v>0.234339</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.266093</v>
+      </c>
+      <c r="H5" t="n">
         <v>0.6068376068376068</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>0.5503875968992248</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>0.5772357723577235</v>
       </c>
     </row>
@@ -45082,12 +45118,18 @@
         <v>0.317687</v>
       </c>
       <c r="F6" t="n">
+        <v>-0.127341</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.08730599999999999</v>
+      </c>
+      <c r="H6" t="n">
         <v>0.5434782608695652</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>0.5813953488372093</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>0.5617977528089888</v>
       </c>
     </row>
@@ -45112,12 +45154,18 @@
         <v>0.624937</v>
       </c>
       <c r="F7" t="n">
+        <v>0.225468</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.27871</v>
+      </c>
+      <c r="H7" t="n">
         <v>0.7633587786259542</v>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
         <v>0.7751937984496124</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>0.7692307692307694</v>
       </c>
     </row>
@@ -45136,18 +45184,24 @@
         <v>0.476367</v>
       </c>
       <c r="D8" t="n">
-        <v>0.142253</v>
+        <v>0.161547</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08944000000000001</v>
+        <v>0.105308</v>
       </c>
       <c r="F8" t="n">
+        <v>0.034656</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.231448</v>
+      </c>
+      <c r="H8" t="n">
         <v/>
       </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
         <v/>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v/>
       </c>
     </row>
@@ -45166,18 +45220,24 @@
         <v>0.729348</v>
       </c>
       <c r="D9" t="n">
-        <v>0.279884</v>
+        <v>0.295791</v>
       </c>
       <c r="E9" t="n">
-        <v>0.183423</v>
+        <v>0.193425</v>
       </c>
       <c r="F9" t="n">
+        <v>0.057095</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.431494</v>
+      </c>
+      <c r="H9" t="n">
         <v/>
       </c>
-      <c r="G9" t="n">
+      <c r="I9" t="n">
         <v/>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v/>
       </c>
     </row>
@@ -45196,18 +45256,24 @@
         <v>0.649212</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.09521300000000001</v>
+        <v>-0.092283</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.063509</v>
+        <v>-0.060576</v>
       </c>
       <c r="F10" t="n">
+        <v>-0.049183</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.175765</v>
+      </c>
+      <c r="H10" t="n">
         <v/>
       </c>
-      <c r="G10" t="n">
+      <c r="I10" t="n">
         <v/>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v/>
       </c>
     </row>
@@ -45226,18 +45292,24 @@
         <v>0.476394</v>
       </c>
       <c r="D11" t="n">
-        <v>0.136602</v>
+        <v>0.1651</v>
       </c>
       <c r="E11" t="n">
-        <v>0.085204</v>
+        <v>0.108266</v>
       </c>
       <c r="F11" t="n">
+        <v>0.03417</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.248974</v>
+      </c>
+      <c r="H11" t="n">
         <v/>
       </c>
-      <c r="G11" t="n">
+      <c r="I11" t="n">
         <v/>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v/>
       </c>
     </row>
@@ -45256,18 +45328,24 @@
         <v>0.729281</v>
       </c>
       <c r="D12" t="n">
-        <v>0.268647</v>
+        <v>0.278281</v>
       </c>
       <c r="E12" t="n">
-        <v>0.17515</v>
+        <v>0.176303</v>
       </c>
       <c r="F12" t="n">
+        <v>0.056447</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.425741</v>
+      </c>
+      <c r="H12" t="n">
         <v/>
       </c>
-      <c r="G12" t="n">
+      <c r="I12" t="n">
         <v/>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v/>
       </c>
     </row>
@@ -45286,18 +45364,24 @@
         <v>0.649384</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.118604</v>
+        <v>-0.113733</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.081178</v>
+        <v>-0.07634100000000001</v>
       </c>
       <c r="F13" t="n">
+        <v>-0.048474</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.185913</v>
+      </c>
+      <c r="H13" t="n">
         <v/>
       </c>
-      <c r="G13" t="n">
+      <c r="I13" t="n">
         <v/>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v/>
       </c>
     </row>
@@ -45322,12 +45406,18 @@
         <v>0.382628</v>
       </c>
       <c r="F14" t="n">
+        <v/>
+      </c>
+      <c r="G14" t="n">
+        <v/>
+      </c>
+      <c r="H14" t="n">
         <v>0.6324786324786325</v>
       </c>
-      <c r="G14" t="n">
+      <c r="I14" t="n">
         <v>0.5648854961832062</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>0.5967741935483871</v>
       </c>
     </row>
@@ -45352,12 +45442,18 @@
         <v>0.460048</v>
       </c>
       <c r="F15" t="n">
+        <v/>
+      </c>
+      <c r="G15" t="n">
+        <v/>
+      </c>
+      <c r="H15" t="n">
         <v>0.6376811594202898</v>
       </c>
-      <c r="G15" t="n">
+      <c r="I15" t="n">
         <v>0.6717557251908397</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>0.654275092936803</v>
       </c>
     </row>
@@ -45382,12 +45478,18 @@
         <v>0.88604</v>
       </c>
       <c r="F16" t="n">
+        <v/>
+      </c>
+      <c r="G16" t="n">
+        <v/>
+      </c>
+      <c r="H16" t="n">
         <v>0.9236641221374046</v>
       </c>
-      <c r="G16" t="n">
+      <c r="I16" t="n">
         <v>0.9236641221374046</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>0.9236641221374046</v>
       </c>
     </row>
